--- a/finance/Компас_финмодель_24м.xlsx
+++ b/finance/Компас_финмодель_24м.xlsx
@@ -451,7 +451,7 @@
     <t xml:space="preserve">Стоимость одного вопроса, ₽</t>
   </si>
   <si>
-    <t xml:space="preserve">ИЗМЕРЕНО 23 сентября 2026 на пяти настоящих вопросах через наш же код: в модель уходит в среднем 8 880 знаков (промпт 2 910 + до 12 карточек сделок), ответ до 700 токенов плюс 800 на размышление. При 0,3 ₽ за 1000 токенов выходит 1,3–1,8 ₽ за вопрос. В веб-режиме дороже — там ещё выдача поиска.</t>
+    <t xml:space="preserve">ИЗМЕРЕНО 23 сентября 2026 настоящим токенизатором (o200k, семейство gpt-oss) на 50 вопросах, собранных из живой базы — имена компаний, отрасли, заголовки сделок. В обычном режиме вход в среднем 2 220 токенов (медиана 1 305), в веб-режиме 3 373 — там добавляется выдача поиска на 897 токенов. Выход — ответ плюс рассуждение. При 0,3 ₽ за 1000 токенов: обычный вопрос 0,80–1,12 ₽, веб-вопрос 1,19–1,67 ₽, смесь 80/20 — 1,04 ₽. Прежняя оценка 1,6 ₽ была завышена: я делил знаки на 2,5, а в наших текстах выходит 3,41 знака на токен.</t>
   </si>
   <si>
     <t xml:space="preserve">Расходы, ₽ в месяц — мои прикидки, их надо заменить счетами</t>
@@ -1609,15 +1609,15 @@
       </c>
       <c r="B6" s="7" t="n">
         <f aca="false">'Единица экономики'!$B$10</f>
-        <v>717.738333333333</v>
+        <v>724.938333333333</v>
       </c>
       <c r="C6" s="7" t="n">
         <f aca="false">'Единица экономики'!$C$10</f>
-        <v>900.64365</v>
+        <v>907.84365</v>
       </c>
       <c r="D6" s="7" t="n">
         <f aca="false">'Единица экономики'!$D$10</f>
-        <v>1339.4094</v>
+        <v>1349.9094</v>
       </c>
       <c r="E6" s="8" t="s">
         <v>9</v>
@@ -1629,15 +1629,15 @@
       </c>
       <c r="B7" s="7" t="n">
         <f aca="false">'Единица экономики'!$B$14</f>
-        <v>6524.89393939394</v>
+        <v>6590.34848484849</v>
       </c>
       <c r="C7" s="7" t="n">
         <f aca="false">'Единица экономики'!$C$14</f>
-        <v>9006.4365</v>
+        <v>9078.4365</v>
       </c>
       <c r="D7" s="7" t="n">
         <f aca="false">'Единица экономики'!$D$14</f>
-        <v>15757.7576470588</v>
+        <v>15881.2870588235</v>
       </c>
       <c r="E7" s="8" t="s">
         <v>11</v>
@@ -1669,15 +1669,15 @@
       </c>
       <c r="B9" s="9" t="n">
         <f aca="false">'Единица экономики'!$B$16</f>
-        <v>0.734050568181818</v>
+        <v>0.741414204545455</v>
       </c>
       <c r="C9" s="9" t="n">
         <f aca="false">'Единица экономики'!$C$16</f>
-        <v>0.78806319375</v>
+        <v>0.79436319375</v>
       </c>
       <c r="D9" s="9" t="n">
         <f aca="false">'Единица экономики'!$D$16</f>
-        <v>0.787887882352941</v>
+        <v>0.794064352941177</v>
       </c>
       <c r="E9" s="8" t="s">
         <v>15</v>
@@ -1689,7 +1689,7 @@
       </c>
       <c r="B10" s="10" t="n">
         <f aca="false">'Единица экономики'!$B$22</f>
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="C10" s="10" t="n">
         <f aca="false">'Единица экономики'!$C$22</f>
@@ -1709,11 +1709,11 @@
       </c>
       <c r="B11" s="11" t="n">
         <f aca="false">'Единица экономики'!$B$23</f>
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="C11" s="11" t="n">
         <f aca="false">'Единица экономики'!$C$23</f>
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D11" s="11" t="n">
         <f aca="false">'Единица экономики'!$D$23</f>
@@ -1729,15 +1729,15 @@
       </c>
       <c r="B12" s="12" t="n">
         <f aca="false">'Единица экономики'!$B$24</f>
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="C12" s="12" t="n">
         <f aca="false">'Единица экономики'!$C$24</f>
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="D12" s="12" t="n">
         <f aca="false">'Единица экономики'!$D$24</f>
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="E12" s="8" t="s">
         <v>21</v>
@@ -1869,15 +1869,15 @@
       </c>
       <c r="B21" s="7" t="n">
         <f aca="false">SUM('Расчёт 790 ₽'!B32:Y32)</f>
-        <v>4112647.60148615</v>
+        <v>4103757.67056185</v>
       </c>
       <c r="C21" s="7" t="n">
         <f aca="false">SUM('Расчёт 990 ₽'!B32:Y32)</f>
-        <v>4109313.2457211</v>
+        <v>4102096.66991641</v>
       </c>
       <c r="D21" s="7" t="n">
         <f aca="false">SUM('Расчёт 1490 ₽'!B32:Y32)</f>
-        <v>4102029.31845104</v>
+        <v>4096055.39140354</v>
       </c>
       <c r="E21" s="8"/>
     </row>
@@ -1927,15 +1927,15 @@
       </c>
       <c r="B24" s="14" t="n">
         <f aca="false">SUM('Расчёт 790 ₽'!B41:Y41)</f>
-        <v>-3187648.72187937</v>
+        <v>-3178758.79095507</v>
       </c>
       <c r="C24" s="14" t="n">
         <f aca="false">SUM('Расчёт 990 ₽'!B41:Y41)</f>
-        <v>-3170556.64824606</v>
+        <v>-3163340.07244137</v>
       </c>
       <c r="D24" s="14" t="n">
         <f aca="false">SUM('Расчёт 1490 ₽'!B41:Y41)</f>
-        <v>-3305968.38929792</v>
+        <v>-3299994.46225042</v>
       </c>
       <c r="E24" s="8"/>
     </row>
@@ -1945,15 +1945,15 @@
       </c>
       <c r="B25" s="14" t="n">
         <f aca="false">'Расчёт 790 ₽'!Y43</f>
-        <v>-2488201.15243493</v>
+        <v>-2479311.22151063</v>
       </c>
       <c r="C25" s="14" t="n">
         <f aca="false">'Расчёт 990 ₽'!Y43</f>
-        <v>-2458844.46074606</v>
+        <v>-2451627.88494137</v>
       </c>
       <c r="D25" s="14" t="n">
         <f aca="false">'Расчёт 1490 ₽'!Y43</f>
-        <v>-2591487.02818681</v>
+        <v>-2585513.10113931</v>
       </c>
       <c r="E25" s="8" t="s">
         <v>37</v>
@@ -2031,15 +2031,15 @@
       </c>
       <c r="B31" s="15" t="n">
         <f aca="false">MAX(0,-MIN('Расчёт 790 ₽'!B43:Y43))</f>
-        <v>2488201.15243493</v>
+        <v>2479311.22151063</v>
       </c>
       <c r="C31" s="15" t="n">
         <f aca="false">MAX(0,-MIN('Расчёт 990 ₽'!B43:Y43))</f>
-        <v>2458844.46074606</v>
+        <v>2451627.88494137</v>
       </c>
       <c r="D31" s="15" t="n">
         <f aca="false">MAX(0,-MIN('Расчёт 1490 ₽'!B43:Y43))</f>
-        <v>2591487.02818681</v>
+        <v>2585513.10113931</v>
       </c>
       <c r="E31" s="8" t="s">
         <v>44</v>
@@ -2238,15 +2238,15 @@
       </c>
       <c r="B9" s="7" t="n">
         <f aca="false">-Допущения!$B$28*Допущения!$B$29</f>
-        <v>-19.2</v>
+        <v>-12</v>
       </c>
       <c r="C9" s="7" t="n">
         <f aca="false">-Допущения!$C$28*Допущения!$C$29</f>
-        <v>-19.2</v>
+        <v>-12</v>
       </c>
       <c r="D9" s="7" t="n">
         <f aca="false">-Допущения!$D$28*Допущения!$D$29</f>
-        <v>-28.5</v>
+        <v>-18</v>
       </c>
       <c r="E9" s="8" t="s">
         <v>63</v>
@@ -2258,15 +2258,15 @@
       </c>
       <c r="B10" s="14" t="n">
         <f aca="false">$B$6+$B$7+$B$8+$B$9</f>
-        <v>717.738333333333</v>
+        <v>724.938333333333</v>
       </c>
       <c r="C10" s="14" t="n">
         <f aca="false">$C$6+$C$7+$C$8+$C$9</f>
-        <v>900.64365</v>
+        <v>907.84365</v>
       </c>
       <c r="D10" s="14" t="n">
         <f aca="false">$D$6+$D$7+$D$8+$D$9</f>
-        <v>1339.4094</v>
+        <v>1349.9094</v>
       </c>
       <c r="E10" s="8" t="s">
         <v>65</v>
@@ -2307,15 +2307,15 @@
       </c>
       <c r="B14" s="7" t="n">
         <f aca="false">$B$10/Допущения!$B$12</f>
-        <v>6524.89393939394</v>
+        <v>6590.34848484849</v>
       </c>
       <c r="C14" s="7" t="n">
         <f aca="false">$C$10/Допущения!$C$12</f>
-        <v>9006.4365</v>
+        <v>9078.4365</v>
       </c>
       <c r="D14" s="7" t="n">
         <f aca="false">$D$10/Допущения!$D$12</f>
-        <v>15757.7576470588</v>
+        <v>15881.2870588235</v>
       </c>
       <c r="E14" s="8" t="s">
         <v>69</v>
@@ -2347,15 +2347,15 @@
       </c>
       <c r="B16" s="22" t="n">
         <f aca="false">$B$14/$B$15</f>
-        <v>0.734050568181818</v>
+        <v>0.741414204545455</v>
       </c>
       <c r="C16" s="22" t="n">
         <f aca="false">$C$14/$C$15</f>
-        <v>0.78806319375</v>
+        <v>0.79436319375</v>
       </c>
       <c r="D16" s="22" t="n">
         <f aca="false">$D$14/$D$15</f>
-        <v>0.787887882352941</v>
+        <v>0.794064352941177</v>
       </c>
       <c r="E16" s="8" t="s">
         <v>72</v>
@@ -2367,15 +2367,15 @@
       </c>
       <c r="B17" s="21" t="n">
         <f aca="false">IF($B$10&gt;0,$B$15/$B$10,"—")</f>
-        <v>12.38458150564</v>
+        <v>12.2615793373996</v>
       </c>
       <c r="C17" s="21" t="n">
         <f aca="false">IF($C$10&gt;0,$C$15/$C$10,"—")</f>
-        <v>12.6893377070625</v>
+        <v>12.5887000791066</v>
       </c>
       <c r="D17" s="21" t="n">
         <f aca="false">IF($D$10&gt;0,$D$15/$D$10,"—")</f>
-        <v>14.9319543374864</v>
+        <v>14.8158091202269</v>
       </c>
       <c r="E17" s="8" t="s">
         <v>74</v>
@@ -2387,15 +2387,15 @@
       </c>
       <c r="B18" s="15" t="n">
         <f aca="false">$B$14*Допущения!$B$20/3</f>
-        <v>195.746818181818</v>
+        <v>197.710454545455</v>
       </c>
       <c r="C18" s="15" t="n">
         <f aca="false">$C$14*Допущения!$C$20/3</f>
-        <v>210.150185</v>
+        <v>211.830185</v>
       </c>
       <c r="D18" s="15" t="n">
         <f aca="false">$D$14*Допущения!$D$20/3</f>
-        <v>236.366364705882</v>
+        <v>238.219305882353</v>
       </c>
       <c r="E18" s="8" t="s">
         <v>76</v>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="B22" s="10" t="n">
         <f aca="false">ROUNDUP($B$21/$B$10,0)</f>
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="C22" s="10" t="n">
         <f aca="false">ROUNDUP($C$21/$C$10,0)</f>
@@ -2456,11 +2456,11 @@
       </c>
       <c r="B23" s="11" t="n">
         <f aca="false">ROUNDUP(($B$21+Допущения!$B$41)/$B$10,0)</f>
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="C23" s="11" t="n">
         <f aca="false">ROUNDUP(($C$21+Допущения!$C$41)/$C$10,0)</f>
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D23" s="11" t="n">
         <f aca="false">ROUNDUP(($D$21+Допущения!$D$41)/$D$10,0)</f>
@@ -2476,15 +2476,15 @@
       </c>
       <c r="B24" s="12" t="n">
         <f aca="false">ROUNDUP(($B$21+Допущения!$B$43)/$B$10,0)</f>
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="C24" s="12" t="n">
         <f aca="false">ROUNDUP(($C$21+Допущения!$C$43)/$C$10,0)</f>
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="D24" s="12" t="n">
         <f aca="false">ROUNDUP(($D$21+Допущения!$D$43)/$D$10,0)</f>
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="E24" s="8" t="s">
         <v>85</v>
@@ -2496,7 +2496,7 @@
       </c>
       <c r="B25" s="7" t="n">
         <f aca="false">$B$22*$B$6</f>
-        <v>106913.333333333</v>
+        <v>105386</v>
       </c>
       <c r="C25" s="7" t="n">
         <f aca="false">$C$22*$C$6</f>
@@ -3003,13 +3003,13 @@
         <v>140</v>
       </c>
       <c r="B29" s="25" t="n">
-        <v>1.6</v>
+        <v>1</v>
       </c>
       <c r="C29" s="25" t="n">
-        <v>1.6</v>
+        <v>1</v>
       </c>
       <c r="D29" s="25" t="n">
-        <v>1.9</v>
+        <v>1.2</v>
       </c>
       <c r="E29" s="8" t="s">
         <v>141</v>
@@ -4740,91 +4740,91 @@
       </c>
       <c r="D17" s="7" t="n">
         <f aca="false">Допущения!$B$24+D10*Допущения!$B$28*Допущения!$B$29</f>
-        <v>7115.2</v>
+        <v>7072</v>
       </c>
       <c r="E17" s="7" t="n">
         <f aca="false">Допущения!$B$24+E10*Допущения!$B$28*Допущения!$B$29</f>
-        <v>7218.0448</v>
+        <v>7136.278</v>
       </c>
       <c r="F17" s="7" t="n">
         <f aca="false">Допущения!$B$24+F10*Допущения!$B$28*Допущения!$B$29</f>
-        <v>7310.0593696</v>
+        <v>7193.787106</v>
       </c>
       <c r="G17" s="7" t="n">
         <f aca="false">Допущения!$B$24+G10*Допущения!$B$28*Допущения!$B$29</f>
-        <v>7392.573944388</v>
+        <v>7245.3587152425</v>
       </c>
       <c r="H17" s="7" t="n">
         <f aca="false">Допущения!$B$24+H10*Допущения!$B$28*Допущения!$B$29</f>
-        <v>7485.94996719945</v>
+        <v>7303.71872949966</v>
       </c>
       <c r="I17" s="7" t="n">
         <f aca="false">Допущения!$B$24+I10*Допущения!$B$28*Допущения!$B$29</f>
-        <v>7570.01364976371</v>
+        <v>7356.25853110232</v>
       </c>
       <c r="J17" s="7" t="n">
         <f aca="false">Допущения!$B$24+J10*Допущения!$B$28*Допущения!$B$29</f>
-        <v>7645.89224838797</v>
+        <v>7403.68265524248</v>
       </c>
       <c r="K17" s="7" t="n">
         <f aca="false">Допущения!$B$24+K10*Допущения!$B$28*Допущения!$B$29</f>
-        <v>7733.77271211449</v>
+        <v>7458.60794507156</v>
       </c>
       <c r="L17" s="7" t="n">
         <f aca="false">Допущения!$B$24+L10*Допущения!$B$28*Допущения!$B$29</f>
-        <v>7813.38396364295</v>
+        <v>7508.36497727684</v>
       </c>
       <c r="M17" s="7" t="n">
         <f aca="false">Допущения!$B$24+M10*Допущения!$B$28*Допущения!$B$29</f>
-        <v>7885.71334927563</v>
+        <v>7553.57084329727</v>
       </c>
       <c r="N17" s="7" t="n">
         <f aca="false">Допущения!$B$24+N10*Допущения!$B$28*Допущения!$B$29</f>
-        <v>7970.82772769734</v>
+        <v>7606.76732981084</v>
       </c>
       <c r="O17" s="7" t="n">
         <f aca="false">Допущения!$B$24+O10*Допущения!$B$28*Допущения!$B$29</f>
-        <v>8048.40570807236</v>
+        <v>7655.25356754522</v>
       </c>
       <c r="P17" s="7" t="n">
         <f aca="false">Допущения!$B$24+P10*Допущения!$B$28*Допущения!$B$29</f>
-        <v>8138.53562010466</v>
+        <v>7711.58476256541</v>
       </c>
       <c r="Q17" s="7" t="n">
         <f aca="false">Допущения!$B$24+Q10*Допущения!$B$28*Допущения!$B$29</f>
-        <v>8240.15156666959</v>
+        <v>7775.09472916849</v>
       </c>
       <c r="R17" s="7" t="n">
         <f aca="false">Допущения!$B$24+R10*Допущения!$B$28*Допущения!$B$29</f>
-        <v>8333.12378398042</v>
+        <v>7833.20236498776</v>
       </c>
       <c r="S17" s="7" t="n">
         <f aca="false">Допущения!$B$24+S10*Допущения!$B$28*Допущения!$B$29</f>
-        <v>8437.65468004294</v>
+        <v>7898.53417502683</v>
       </c>
       <c r="T17" s="7" t="n">
         <f aca="false">Допущения!$B$24+T10*Допущения!$B$28*Допущения!$B$29</f>
-        <v>8552.83396745892</v>
+        <v>7970.52122966183</v>
       </c>
       <c r="U17" s="7" t="n">
         <f aca="false">Допущения!$B$24+U10*Допущения!$B$28*Допущения!$B$29</f>
-        <v>8677.86742263835</v>
+        <v>8048.66713914897</v>
       </c>
       <c r="V17" s="7" t="n">
         <f aca="false">Допущения!$B$24+V10*Допущения!$B$28*Допущения!$B$29</f>
-        <v>8812.0629088965</v>
+        <v>8132.53931806031</v>
       </c>
       <c r="W17" s="7" t="n">
         <f aca="false">Допущения!$B$24+W10*Допущения!$B$28*Допущения!$B$29</f>
-        <v>8954.81819991414</v>
+        <v>8221.76137494634</v>
       </c>
       <c r="X17" s="7" t="n">
         <f aca="false">Допущения!$B$24+X10*Допущения!$B$28*Допущения!$B$29</f>
-        <v>9105.61036495519</v>
+        <v>8316.00647809699</v>
       </c>
       <c r="Y17" s="7" t="n">
         <f aca="false">Допущения!$B$24+Y10*Допущения!$B$28*Допущения!$B$29</f>
-        <v>9263.98651000459</v>
+        <v>8414.99156875287</v>
       </c>
       <c r="Z17" s="8" t="s">
         <v>243</v>
@@ -6270,91 +6270,91 @@
       </c>
       <c r="D32" s="14" t="n">
         <f aca="false">SUM(D16:D31)</f>
-        <v>100253.063333333</v>
+        <v>100209.863333333</v>
       </c>
       <c r="E32" s="14" t="n">
         <f aca="false">SUM(E16:E31)</f>
-        <v>150502.868228958</v>
+        <v>150421.101428958</v>
       </c>
       <c r="F32" s="14" t="n">
         <f aca="false">SUM(F16:F31)</f>
-        <v>150728.195962093</v>
+        <v>150611.923698493</v>
       </c>
       <c r="G32" s="14" t="n">
         <f aca="false">SUM(G16:G31)</f>
-        <v>150932.063077391</v>
+        <v>150784.847848245</v>
       </c>
       <c r="H32" s="14" t="n">
         <f aca="false">SUM(H16:H31)</f>
-        <v>151180.541587205</v>
+        <v>150998.310349505</v>
       </c>
       <c r="I32" s="14" t="n">
         <f aca="false">SUM(I16:I31)</f>
-        <v>151390.723173423</v>
+        <v>151176.968054762</v>
       </c>
       <c r="J32" s="14" t="n">
         <f aca="false">SUM(J16:J31)</f>
-        <v>151582.440234224</v>
+        <v>151340.230641079</v>
       </c>
       <c r="K32" s="14" t="n">
         <f aca="false">SUM(K16:K31)</f>
-        <v>151831.63485332</v>
+        <v>151556.470086277</v>
       </c>
       <c r="L32" s="14" t="n">
         <f aca="false">SUM(L16:L31)</f>
-        <v>152034.543393346</v>
+        <v>151729.52440698</v>
       </c>
       <c r="M32" s="14" t="n">
         <f aca="false">SUM(M16:M31)</f>
-        <v>152221.045866773</v>
+        <v>151888.903360795</v>
       </c>
       <c r="N32" s="14" t="n">
         <f aca="false">SUM(N16:N31)</f>
-        <v>202477.078779467</v>
+        <v>202113.018381581</v>
       </c>
       <c r="O32" s="14" t="n">
         <f aca="false">SUM(O16:O31)</f>
-        <v>202678.129927104</v>
+        <v>202284.977786577</v>
       </c>
       <c r="P32" s="14" t="n">
         <f aca="false">SUM(P16:P31)</f>
-        <v>202955.047027998</v>
+        <v>202528.096170459</v>
       </c>
       <c r="Q32" s="14" t="n">
         <f aca="false">SUM(Q16:Q31)</f>
-        <v>203263.936321567</v>
+        <v>202798.879484066</v>
       </c>
       <c r="R32" s="14" t="n">
         <f aca="false">SUM(R16:R31)</f>
-        <v>203505.013462146</v>
+        <v>203005.092043153</v>
       </c>
       <c r="S32" s="14" t="n">
         <f aca="false">SUM(S16:S31)</f>
-        <v>203830.017613323</v>
+        <v>203290.897108307</v>
       </c>
       <c r="T32" s="14" t="n">
         <f aca="false">SUM(T16:T31)</f>
-        <v>204185.03974366</v>
+        <v>203602.727005863</v>
       </c>
       <c r="U32" s="14" t="n">
         <f aca="false">SUM(U16:U31)</f>
-        <v>204568.276363573</v>
+        <v>203939.076080084</v>
       </c>
       <c r="V32" s="14" t="n">
         <f aca="false">SUM(V16:V31)</f>
-        <v>204978.154030033</v>
+        <v>204298.630439197</v>
       </c>
       <c r="W32" s="14" t="n">
         <f aca="false">SUM(W16:W31)</f>
-        <v>205413.301702897</v>
+        <v>204680.244877929</v>
       </c>
       <c r="X32" s="14" t="n">
         <f aca="false">SUM(X16:X31)</f>
-        <v>205872.52665715</v>
+        <v>205082.922770292</v>
       </c>
       <c r="Y32" s="14" t="n">
         <f aca="false">SUM(Y16:Y31)</f>
-        <v>206354.793480499</v>
+        <v>205505.798539247</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6608,91 +6608,91 @@
       </c>
       <c r="D36" s="7" t="n">
         <f aca="false">D12-D32-D35</f>
-        <v>-95526.23</v>
+        <v>-95483.03</v>
       </c>
       <c r="E36" s="7" t="n">
         <f aca="false">E12-E32-E35</f>
-        <v>-141568.615041458</v>
+        <v>-141486.848241458</v>
       </c>
       <c r="F36" s="7" t="n">
         <f aca="false">F12-F32-F35</f>
-        <v>-138041.420656787</v>
+        <v>-137925.148393187</v>
       </c>
       <c r="G36" s="7" t="n">
         <f aca="false">G12-G32-G35</f>
-        <v>-134891.453088418</v>
+        <v>-134744.237859272</v>
       </c>
       <c r="H36" s="7" t="n">
         <f aca="false">H12-H32-H35</f>
-        <v>-131352.348698133</v>
+        <v>-131170.117460434</v>
       </c>
       <c r="I36" s="7" t="n">
         <f aca="false">I12-I32-I35</f>
-        <v>-128165.058495877</v>
+        <v>-127951.303377215</v>
       </c>
       <c r="J36" s="7" t="n">
         <f aca="false">J12-J32-J35</f>
-        <v>-125301.951817466</v>
+        <v>-125059.74222432</v>
       </c>
       <c r="K36" s="7" t="n">
         <f aca="false">K12-K32-K35</f>
-        <v>-122017.341257574</v>
+        <v>-121742.176490531</v>
       </c>
       <c r="L36" s="7" t="n">
         <f aca="false">L12-L32-L35</f>
-        <v>-119032.006847677</v>
+        <v>-118726.987861311</v>
       </c>
       <c r="M36" s="7" t="n">
         <f aca="false">M12-M32-M35</f>
-        <v>-116334.40639464</v>
+        <v>-116002.263888661</v>
       </c>
       <c r="N36" s="7" t="n">
         <f aca="false">N12-N32-N35</f>
-        <v>-163197.321498241</v>
+        <v>-162833.261100355</v>
       </c>
       <c r="O36" s="7" t="n">
         <f aca="false">O12-O32-O35</f>
-        <v>-160319.475403836</v>
+        <v>-159926.323263309</v>
       </c>
       <c r="P36" s="7" t="n">
         <f aca="false">P12-P32-P35</f>
-        <v>-157019.94454267</v>
+        <v>-156592.993685131</v>
       </c>
       <c r="Q36" s="7" t="n">
         <f aca="false">Q12-Q32-Q35</f>
-        <v>-153299.930602772</v>
+        <v>-152834.87376527</v>
       </c>
       <c r="R36" s="7" t="n">
         <f aca="false">R12-R32-R35</f>
-        <v>-149871.468634415</v>
+        <v>-149371.547215422</v>
       </c>
       <c r="S36" s="7" t="n">
         <f aca="false">S12-S32-S35</f>
-        <v>-146073.197615099</v>
+        <v>-145534.077110083</v>
       </c>
       <c r="T36" s="7" t="n">
         <f aca="false">T12-T32-T35</f>
-        <v>-141889.708314741</v>
+        <v>-141307.395576944</v>
       </c>
       <c r="U36" s="7" t="n">
         <f aca="false">U12-U32-U35</f>
-        <v>-137352.839443515</v>
+        <v>-136723.639160025</v>
       </c>
       <c r="V36" s="7" t="n">
         <f aca="false">V12-V32-V35</f>
-        <v>-132490.39443659</v>
+        <v>-131810.870845753</v>
       </c>
       <c r="W36" s="7" t="n">
         <f aca="false">W12-W32-W35</f>
-        <v>-127326.62938124</v>
+        <v>-126593.572556272</v>
       </c>
       <c r="X36" s="7" t="n">
         <f aca="false">X12-X32-X35</f>
-        <v>-121882.678028419</v>
+        <v>-121093.07414156</v>
       </c>
       <c r="Y36" s="7" t="n">
         <f aca="false">Y12-Y32-Y35</f>
-        <v>-116176.922241796</v>
+        <v>-115327.927300545</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6943,91 +6943,91 @@
       </c>
       <c r="D40" s="14" t="n">
         <f aca="false">D12-D32</f>
-        <v>-95526.23</v>
+        <v>-95483.03</v>
       </c>
       <c r="E40" s="14" t="n">
         <f aca="false">E12-E32</f>
-        <v>-141568.615041458</v>
+        <v>-141486.848241458</v>
       </c>
       <c r="F40" s="14" t="n">
         <f aca="false">F12-F32</f>
-        <v>-138041.420656787</v>
+        <v>-137925.148393187</v>
       </c>
       <c r="G40" s="14" t="n">
         <f aca="false">G12-G32</f>
-        <v>-134891.453088418</v>
+        <v>-134744.237859272</v>
       </c>
       <c r="H40" s="14" t="n">
         <f aca="false">H12-H32</f>
-        <v>-131352.348698133</v>
+        <v>-131170.117460434</v>
       </c>
       <c r="I40" s="14" t="n">
         <f aca="false">I12-I32</f>
-        <v>-128165.058495877</v>
+        <v>-127951.303377215</v>
       </c>
       <c r="J40" s="14" t="n">
         <f aca="false">J12-J32</f>
-        <v>-125301.951817466</v>
+        <v>-125059.74222432</v>
       </c>
       <c r="K40" s="14" t="n">
         <f aca="false">K12-K32</f>
-        <v>-122017.341257574</v>
+        <v>-121742.176490531</v>
       </c>
       <c r="L40" s="14" t="n">
         <f aca="false">L12-L32</f>
-        <v>-119032.006847677</v>
+        <v>-118726.987861311</v>
       </c>
       <c r="M40" s="14" t="n">
         <f aca="false">M12-M32</f>
-        <v>-116334.40639464</v>
+        <v>-116002.263888661</v>
       </c>
       <c r="N40" s="14" t="n">
         <f aca="false">N12-N32</f>
-        <v>-163197.321498241</v>
+        <v>-162833.261100355</v>
       </c>
       <c r="O40" s="14" t="n">
         <f aca="false">O12-O32</f>
-        <v>-160319.475403836</v>
+        <v>-159926.323263309</v>
       </c>
       <c r="P40" s="14" t="n">
         <f aca="false">P12-P32</f>
-        <v>-157019.94454267</v>
+        <v>-156592.993685131</v>
       </c>
       <c r="Q40" s="14" t="n">
         <f aca="false">Q12-Q32</f>
-        <v>-153299.930602772</v>
+        <v>-152834.87376527</v>
       </c>
       <c r="R40" s="14" t="n">
         <f aca="false">R12-R32</f>
-        <v>-149871.468634415</v>
+        <v>-149371.547215422</v>
       </c>
       <c r="S40" s="14" t="n">
         <f aca="false">S12-S32</f>
-        <v>-146073.197615099</v>
+        <v>-145534.077110083</v>
       </c>
       <c r="T40" s="14" t="n">
         <f aca="false">T12-T32</f>
-        <v>-141889.708314741</v>
+        <v>-141307.395576944</v>
       </c>
       <c r="U40" s="14" t="n">
         <f aca="false">U12-U32</f>
-        <v>-137352.839443515</v>
+        <v>-136723.639160025</v>
       </c>
       <c r="V40" s="14" t="n">
         <f aca="false">V12-V32</f>
-        <v>-132490.39443659</v>
+        <v>-131810.870845753</v>
       </c>
       <c r="W40" s="14" t="n">
         <f aca="false">W12-W32</f>
-        <v>-127326.62938124</v>
+        <v>-126593.572556272</v>
       </c>
       <c r="X40" s="14" t="n">
         <f aca="false">X12-X32</f>
-        <v>-121882.678028419</v>
+        <v>-121093.07414156</v>
       </c>
       <c r="Y40" s="14" t="n">
         <f aca="false">Y12-Y32</f>
-        <v>-116176.922241796</v>
+        <v>-115327.927300545</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7044,91 +7044,91 @@
       </c>
       <c r="D41" s="14" t="n">
         <f aca="false">D40-D38</f>
-        <v>-95668.035</v>
+        <v>-95624.835</v>
       </c>
       <c r="E41" s="14" t="n">
         <f aca="false">E40-E38</f>
-        <v>-141836.642637083</v>
+        <v>-141754.875837083</v>
       </c>
       <c r="F41" s="14" t="n">
         <f aca="false">F40-F38</f>
-        <v>-138422.023915946</v>
+        <v>-138305.751652346</v>
       </c>
       <c r="G41" s="14" t="n">
         <f aca="false">G40-G38</f>
-        <v>-135372.671388087</v>
+        <v>-135225.456158941</v>
       </c>
       <c r="H41" s="14" t="n">
         <f aca="false">H40-H38</f>
-        <v>-131947.194484806</v>
+        <v>-131764.963247106</v>
       </c>
       <c r="I41" s="14" t="n">
         <f aca="false">I40-I38</f>
-        <v>-128861.828436203</v>
+        <v>-128648.073317542</v>
       </c>
       <c r="J41" s="14" t="n">
         <f aca="false">J40-J38</f>
-        <v>-126090.366469969</v>
+        <v>-125848.156876823</v>
       </c>
       <c r="K41" s="14" t="n">
         <f aca="false">K40-K38</f>
-        <v>-122911.770065447</v>
+        <v>-122636.605298404</v>
       </c>
       <c r="L41" s="14" t="n">
         <f aca="false">L40-L38</f>
-        <v>-120022.082944047</v>
+        <v>-119717.063957681</v>
       </c>
       <c r="M41" s="14" t="n">
         <f aca="false">M40-M38</f>
-        <v>-117411.005578804</v>
+        <v>-117078.863072825</v>
       </c>
       <c r="N41" s="14" t="n">
         <f aca="false">N40-N38</f>
-        <v>-164375.714216678</v>
+        <v>-164011.653818791</v>
       </c>
       <c r="O41" s="14" t="n">
         <f aca="false">O40-O38</f>
-        <v>-161590.235039534</v>
+        <v>-161197.082899007</v>
       </c>
       <c r="P41" s="14" t="n">
         <f aca="false">P40-P38</f>
-        <v>-158397.99761723</v>
+        <v>-157971.046759691</v>
       </c>
       <c r="Q41" s="14" t="n">
         <f aca="false">Q40-Q38</f>
-        <v>-154798.850774335</v>
+        <v>-154333.793936834</v>
       </c>
       <c r="R41" s="14" t="n">
         <f aca="false">R40-R38</f>
-        <v>-151480.474979247</v>
+        <v>-150980.553560254</v>
       </c>
       <c r="S41" s="14" t="n">
         <f aca="false">S40-S38</f>
-        <v>-147805.902215046</v>
+        <v>-147266.78171003</v>
       </c>
       <c r="T41" s="14" t="n">
         <f aca="false">T40-T38</f>
-        <v>-143758.568257609</v>
+        <v>-143176.255519812</v>
       </c>
       <c r="U41" s="14" t="n">
         <f aca="false">U40-U38</f>
-        <v>-139369.302551117</v>
+        <v>-138740.102267627</v>
       </c>
       <c r="V41" s="14" t="n">
         <f aca="false">V40-V38</f>
-        <v>-134665.027224393</v>
+        <v>-133985.503633557</v>
       </c>
       <c r="W41" s="14" t="n">
         <f aca="false">W40-W38</f>
-        <v>-129669.22955089</v>
+        <v>-128936.172725922</v>
       </c>
       <c r="X41" s="14" t="n">
         <f aca="false">X40-X38</f>
-        <v>-124402.373487281</v>
+        <v>-123612.769600422</v>
       </c>
       <c r="Y41" s="14" t="n">
         <f aca="false">Y40-Y38</f>
-        <v>-118882.258378957</v>
+        <v>-118033.263437706</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7145,91 +7145,91 @@
       </c>
       <c r="D42" s="14" t="n">
         <f aca="false">D14-D32-D38</f>
-        <v>-94943.8683333333</v>
+        <v>-94900.6683333333</v>
       </c>
       <c r="E42" s="14" t="n">
         <f aca="false">E14-E32-E38</f>
-        <v>-140750.392637083</v>
+        <v>-140668.625837083</v>
       </c>
       <c r="F42" s="14" t="n">
         <f aca="false">F14-F32-F38</f>
-        <v>-136973.690582613</v>
+        <v>-136857.418319013</v>
       </c>
       <c r="G42" s="14" t="n">
         <f aca="false">G14-G32-G38</f>
-        <v>-133562.25472142</v>
+        <v>-133415.039492275</v>
       </c>
       <c r="H42" s="14" t="n">
         <f aca="false">H14-H32-H38</f>
-        <v>-129412.611151472</v>
+        <v>-129230.379913772</v>
       </c>
       <c r="I42" s="14" t="n">
         <f aca="false">I14-I32-I38</f>
-        <v>-125904.814547314</v>
+        <v>-125691.059428653</v>
       </c>
       <c r="J42" s="14" t="n">
         <f aca="false">J14-J32-J38</f>
-        <v>-122710.922025524</v>
+        <v>-122468.712432379</v>
       </c>
       <c r="K42" s="14" t="n">
         <f aca="false">K14-K32-K38</f>
-        <v>-118566.770065447</v>
+        <v>-118291.605298404</v>
       </c>
       <c r="L42" s="14" t="n">
         <f aca="false">L14-L32-L38</f>
-        <v>-115194.30516627</v>
+        <v>-114889.286179903</v>
       </c>
       <c r="M42" s="14" t="n">
         <f aca="false">M14-M32-M38</f>
-        <v>-112100.450023248</v>
+        <v>-111768.30751727</v>
       </c>
       <c r="N42" s="14" t="n">
         <f aca="false">N14-N32-N38</f>
-        <v>-157858.214216678</v>
+        <v>-157494.153818791</v>
       </c>
       <c r="O42" s="14" t="n">
         <f aca="false">O14-O32-O38</f>
-        <v>-154529.610039534</v>
+        <v>-154136.457899007</v>
       </c>
       <c r="P42" s="14" t="n">
         <f aca="false">P14-P32-P38</f>
-        <v>-149949.386506119</v>
+        <v>-149522.435648579</v>
       </c>
       <c r="Q42" s="14" t="n">
         <f aca="false">Q14-Q32-Q38</f>
-        <v>-144841.559107669</v>
+        <v>-144376.502270168</v>
       </c>
       <c r="R42" s="14" t="n">
         <f aca="false">R14-R32-R38</f>
-        <v>-140859.363868136</v>
+        <v>-140359.442449143</v>
       </c>
       <c r="S42" s="14" t="n">
         <f aca="false">S14-S32-S38</f>
-        <v>-135495.068881713</v>
+        <v>-134955.948376697</v>
       </c>
       <c r="T42" s="14" t="n">
         <f aca="false">T14-T32-T38</f>
-        <v>-129637.318257609</v>
+        <v>-129055.005519812</v>
       </c>
       <c r="U42" s="14" t="n">
         <f aca="false">U14-U32-U38</f>
-        <v>-123316.941440005</v>
+        <v>-122687.741156516</v>
       </c>
       <c r="V42" s="14" t="n">
         <f aca="false">V14-V32-V38</f>
-        <v>-116560.860557726</v>
+        <v>-115881.33696689</v>
       </c>
       <c r="W42" s="14" t="n">
         <f aca="false">W14-W32-W38</f>
-        <v>-109392.562884223</v>
+        <v>-108659.506059255</v>
       </c>
       <c r="X42" s="14" t="n">
         <f aca="false">X14-X32-X38</f>
-        <v>-101832.512376169</v>
+        <v>-101042.908489311</v>
       </c>
       <c r="Y42" s="14" t="n">
         <f aca="false">Y14-Y32-Y38</f>
-        <v>-93898.5083789573</v>
+        <v>-93049.5134377056</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7246,91 +7246,91 @@
       </c>
       <c r="D43" s="14" t="n">
         <f aca="false">C43+D42</f>
-        <v>205146.965</v>
+        <v>205190.165</v>
       </c>
       <c r="E43" s="14" t="n">
         <f aca="false">D43+E42</f>
-        <v>64396.5723629167</v>
+        <v>64521.5391629167</v>
       </c>
       <c r="F43" s="14" t="n">
         <f aca="false">E43+F42</f>
-        <v>-72577.1182196961</v>
+        <v>-72335.8791560961</v>
       </c>
       <c r="G43" s="14" t="n">
         <f aca="false">F43+G42</f>
-        <v>-206139.372941116</v>
+        <v>-205750.918648371</v>
       </c>
       <c r="H43" s="14" t="n">
         <f aca="false">G43+H42</f>
-        <v>-335551.984092589</v>
+        <v>-334981.298562143</v>
       </c>
       <c r="I43" s="14" t="n">
         <f aca="false">H43+I42</f>
-        <v>-461456.798639903</v>
+        <v>-460672.357990796</v>
       </c>
       <c r="J43" s="14" t="n">
         <f aca="false">I43+J42</f>
-        <v>-584167.720665427</v>
+        <v>-583141.070423175</v>
       </c>
       <c r="K43" s="14" t="n">
         <f aca="false">J43+K42</f>
-        <v>-702734.490730874</v>
+        <v>-701432.675721579</v>
       </c>
       <c r="L43" s="14" t="n">
         <f aca="false">K43+L42</f>
-        <v>-817928.795897143</v>
+        <v>-816321.961901482</v>
       </c>
       <c r="M43" s="14" t="n">
         <f aca="false">L43+M42</f>
-        <v>-930029.245920391</v>
+        <v>-928090.269418752</v>
       </c>
       <c r="N43" s="14" t="n">
         <f aca="false">M43+N42</f>
-        <v>-1087887.46013707</v>
+        <v>-1085584.42323754</v>
       </c>
       <c r="O43" s="14" t="n">
         <f aca="false">N43+O42</f>
-        <v>-1242417.0701766</v>
+        <v>-1239720.88113655</v>
       </c>
       <c r="P43" s="14" t="n">
         <f aca="false">O43+P42</f>
-        <v>-1392366.45668272</v>
+        <v>-1389243.31678513</v>
       </c>
       <c r="Q43" s="14" t="n">
         <f aca="false">P43+Q42</f>
-        <v>-1537208.01579039</v>
+        <v>-1533619.8190553</v>
       </c>
       <c r="R43" s="14" t="n">
         <f aca="false">Q43+R42</f>
-        <v>-1678067.37965853</v>
+        <v>-1673979.26150444</v>
       </c>
       <c r="S43" s="14" t="n">
         <f aca="false">R43+S42</f>
-        <v>-1813562.44854024</v>
+        <v>-1808935.20988114</v>
       </c>
       <c r="T43" s="14" t="n">
         <f aca="false">S43+T42</f>
-        <v>-1943199.76679785</v>
+        <v>-1937990.21540095</v>
       </c>
       <c r="U43" s="14" t="n">
         <f aca="false">T43+U42</f>
-        <v>-2066516.70823785</v>
+        <v>-2060677.95655746</v>
       </c>
       <c r="V43" s="14" t="n">
         <f aca="false">U43+V42</f>
-        <v>-2183077.56879558</v>
+        <v>-2176559.29352435</v>
       </c>
       <c r="W43" s="14" t="n">
         <f aca="false">V43+W42</f>
-        <v>-2292470.1316798</v>
+        <v>-2285218.79958361</v>
       </c>
       <c r="X43" s="14" t="n">
         <f aca="false">W43+X42</f>
-        <v>-2394302.64405597</v>
+        <v>-2386261.70807292</v>
       </c>
       <c r="Y43" s="14" t="n">
         <f aca="false">X43+Y42</f>
-        <v>-2488201.15243493</v>
+        <v>-2479311.22151063</v>
       </c>
       <c r="Z43" s="8" t="s">
         <v>272</v>
@@ -8579,91 +8579,91 @@
       </c>
       <c r="D17" s="7" t="n">
         <f aca="false">Допущения!$C$24+D10*Допущения!$C$28*Допущения!$C$29</f>
-        <v>7076.8</v>
+        <v>7048</v>
       </c>
       <c r="E17" s="7" t="n">
         <f aca="false">Допущения!$C$24+E10*Допущения!$C$28*Допущения!$C$29</f>
-        <v>7165.3312</v>
+        <v>7103.332</v>
       </c>
       <c r="F17" s="7" t="n">
         <f aca="false">Допущения!$C$24+F10*Допущения!$C$28*Допущения!$C$29</f>
-        <v>7245.4042944</v>
+        <v>7153.377684</v>
       </c>
       <c r="G17" s="7" t="n">
         <f aca="false">Допущения!$C$24+G10*Допущения!$C$28*Допущения!$C$29</f>
-        <v>7317.98863464267</v>
+        <v>7198.74289665167</v>
       </c>
       <c r="H17" s="7" t="n">
         <f aca="false">Допущения!$C$24+H10*Допущения!$C$28*Допущения!$C$29</f>
-        <v>7383.93870866894</v>
+        <v>7239.96169291808</v>
       </c>
       <c r="I17" s="7" t="n">
         <f aca="false">Допущения!$C$24+I10*Допущения!$C$28*Допущения!$C$29</f>
-        <v>7444.008444516</v>
+        <v>7277.5052778225</v>
       </c>
       <c r="J17" s="7" t="n">
         <f aca="false">Допущения!$C$24+J10*Допущения!$C$28*Допущения!$C$29</f>
-        <v>7518.06366199085</v>
+        <v>7323.78978874428</v>
       </c>
       <c r="K17" s="7" t="n">
         <f aca="false">Допущения!$C$24+K10*Допущения!$C$28*Допущения!$C$29</f>
-        <v>7585.73132100319</v>
+        <v>7366.08207562699</v>
       </c>
       <c r="L17" s="7" t="n">
         <f aca="false">Допущения!$C$24+L10*Допущения!$C$28*Допущения!$C$29</f>
-        <v>7647.72739267873</v>
+        <v>7404.82962042421</v>
       </c>
       <c r="M17" s="7" t="n">
         <f aca="false">Допущения!$C$24+M10*Допущения!$C$28*Допущения!$C$29</f>
-        <v>7723.88590462037</v>
+        <v>7452.42869038773</v>
       </c>
       <c r="N17" s="7" t="n">
         <f aca="false">Допущения!$C$24+N10*Допущения!$C$28*Допущения!$C$29</f>
-        <v>7793.86005910916</v>
+        <v>7496.16253694322</v>
       </c>
       <c r="O17" s="7" t="n">
         <f aca="false">Допущения!$C$24+O10*Допущения!$C$28*Допущения!$C$29</f>
-        <v>7858.33421890263</v>
+        <v>7536.45888681414</v>
       </c>
       <c r="P17" s="7" t="n">
         <f aca="false">Допущения!$C$24+P10*Допущения!$C$28*Допущения!$C$29</f>
-        <v>7937.11608615495</v>
+        <v>7585.69755384684</v>
       </c>
       <c r="Q17" s="7" t="n">
         <f aca="false">Допущения!$C$24+Q10*Допущения!$C$28*Допущения!$C$29</f>
-        <v>8009.88982372408</v>
+        <v>7631.18113982755</v>
       </c>
       <c r="R17" s="7" t="n">
         <f aca="false">Допущения!$C$24+R10*Допущения!$C$28*Допущения!$C$29</f>
-        <v>8096.5125587663</v>
+        <v>7685.32034922893</v>
       </c>
       <c r="S17" s="7" t="n">
         <f aca="false">Допущения!$C$24+S10*Допущения!$C$28*Допущения!$C$29</f>
-        <v>8176.74862359711</v>
+        <v>7735.46788974819</v>
       </c>
       <c r="T17" s="7" t="n">
         <f aca="false">Допущения!$C$24+T10*Допущения!$C$28*Допущения!$C$29</f>
-        <v>8270.49011352675</v>
+        <v>7794.05632095422</v>
       </c>
       <c r="U17" s="7" t="n">
         <f aca="false">Допущения!$C$24+U10*Допущения!$C$28*Допущения!$C$29</f>
-        <v>8376.76880498466</v>
+        <v>7860.48050311542</v>
       </c>
       <c r="V17" s="7" t="n">
         <f aca="false">Допущения!$C$24+V10*Допущения!$C$28*Допущения!$C$29</f>
-        <v>8475.53268591092</v>
+        <v>7922.20792869432</v>
       </c>
       <c r="W17" s="7" t="n">
         <f aca="false">Допущения!$C$24+W10*Допущения!$C$28*Допущения!$C$29</f>
-        <v>8586.78342152361</v>
+        <v>7991.73963845226</v>
       </c>
       <c r="X17" s="7" t="n">
         <f aca="false">Допущения!$C$24+X10*Допущения!$C$28*Допущения!$C$29</f>
-        <v>8709.70521170531</v>
+        <v>8068.56575731582</v>
       </c>
       <c r="Y17" s="7" t="n">
         <f aca="false">Допущения!$C$24+Y10*Допущения!$C$28*Допущения!$C$29</f>
-        <v>8843.5809754149</v>
+        <v>8152.23810963431</v>
       </c>
       <c r="Z17" s="8" t="s">
         <v>243</v>
@@ -10109,91 +10109,91 @@
       </c>
       <c r="D32" s="14" t="n">
         <f aca="false">SUM(D16:D31)</f>
-        <v>100187.935333333</v>
+        <v>100159.135333333</v>
       </c>
       <c r="E32" s="14" t="n">
         <f aca="false">SUM(E16:E31)</f>
-        <v>150445.954685958</v>
+        <v>150383.955485958</v>
       </c>
       <c r="F32" s="14" t="n">
         <f aca="false">SUM(F16:F31)</f>
-        <v>150672.565058163</v>
+        <v>150580.538447763</v>
       </c>
       <c r="G32" s="14" t="n">
         <f aca="false">SUM(G16:G31)</f>
-        <v>150879.812529299</v>
+        <v>150760.566791308</v>
       </c>
       <c r="H32" s="14" t="n">
         <f aca="false">SUM(H16:H31)</f>
-        <v>151069.914351066</v>
+        <v>150925.937335316</v>
       </c>
       <c r="I32" s="14" t="n">
         <f aca="false">SUM(I16:I31)</f>
-        <v>151244.825247638</v>
+        <v>151078.322080944</v>
       </c>
       <c r="J32" s="14" t="n">
         <f aca="false">SUM(J16:J31)</f>
-        <v>151492.922081357</v>
+        <v>151298.64820811</v>
       </c>
       <c r="K32" s="14" t="n">
         <f aca="false">SUM(K16:K31)</f>
-        <v>151691.185810877</v>
+        <v>151471.536565501</v>
       </c>
       <c r="L32" s="14" t="n">
         <f aca="false">SUM(L16:L31)</f>
-        <v>151874.81891654</v>
+        <v>151631.921144285</v>
       </c>
       <c r="M32" s="14" t="n">
         <f aca="false">SUM(M16:M31)</f>
-        <v>152146.268915823</v>
+        <v>151874.81170159</v>
       </c>
       <c r="N32" s="14" t="n">
         <f aca="false">SUM(N16:N31)</f>
-        <v>202354.139796263</v>
+        <v>202056.442274097</v>
       </c>
       <c r="O32" s="14" t="n">
         <f aca="false">SUM(O16:O31)</f>
-        <v>202547.841114946</v>
+        <v>202225.965782858</v>
       </c>
       <c r="P32" s="14" t="n">
         <f aca="false">SUM(P16:P31)</f>
-        <v>202843.905501002</v>
+        <v>202492.486968694</v>
       </c>
       <c r="Q32" s="14" t="n">
         <f aca="false">SUM(Q16:Q31)</f>
-        <v>203062.571672856</v>
+        <v>202683.86298896</v>
       </c>
       <c r="R32" s="14" t="n">
         <f aca="false">SUM(R16:R31)</f>
-        <v>203391.871875313</v>
+        <v>202980.679665776</v>
       </c>
       <c r="S32" s="14" t="n">
         <f aca="false">SUM(S16:S31)</f>
-        <v>203633.287563769</v>
+        <v>203192.00682992</v>
       </c>
       <c r="T32" s="14" t="n">
         <f aca="false">SUM(T16:T31)</f>
-        <v>203993.904882877</v>
+        <v>203517.471090304</v>
       </c>
       <c r="U32" s="14" t="n">
         <f aca="false">SUM(U16:U31)</f>
-        <v>204394.975612383</v>
+        <v>203878.687310514</v>
       </c>
       <c r="V32" s="14" t="n">
         <f aca="false">SUM(V16:V31)</f>
-        <v>204691.001168155</v>
+        <v>204137.676410939</v>
       </c>
       <c r="W32" s="14" t="n">
         <f aca="false">SUM(W16:W31)</f>
-        <v>205117.79453436</v>
+        <v>204522.750751289</v>
       </c>
       <c r="X32" s="14" t="n">
         <f aca="false">SUM(X16:X31)</f>
-        <v>205582.708730459</v>
+        <v>204941.569276069</v>
       </c>
       <c r="Y32" s="14" t="n">
         <f aca="false">SUM(Y16:Y31)</f>
-        <v>206083.873671996</v>
+        <v>205392.530806215</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10447,91 +10447,91 @@
       </c>
       <c r="D36" s="7" t="n">
         <f aca="false">D12-D32-D35</f>
-        <v>-96240.0353333333</v>
+        <v>-96211.2353333333</v>
       </c>
       <c r="E36" s="7" t="n">
         <f aca="false">E12-E32-E35</f>
-        <v>-141960.137098458</v>
+        <v>-141898.137898458</v>
       </c>
       <c r="F36" s="7" t="n">
         <f aca="false">F12-F32-F35</f>
-        <v>-138096.234043846</v>
+        <v>-138004.207433446</v>
       </c>
       <c r="G36" s="7" t="n">
         <f aca="false">G12-G32-G35</f>
-        <v>-134608.772985197</v>
+        <v>-134489.527247206</v>
       </c>
       <c r="H36" s="7" t="n">
         <f aca="false">H12-H32-H35</f>
-        <v>-131454.545715594</v>
+        <v>-131310.568699843</v>
       </c>
       <c r="I36" s="7" t="n">
         <f aca="false">I12-I32-I35</f>
-        <v>-128595.48042136</v>
+        <v>-128428.977254667</v>
       </c>
       <c r="J36" s="7" t="n">
         <f aca="false">J12-J32-J35</f>
-        <v>-125106.752546937</v>
+        <v>-124912.478673691</v>
       </c>
       <c r="K36" s="7" t="n">
         <f aca="false">K12-K32-K35</f>
-        <v>-121904.68892619</v>
+        <v>-121685.039680813</v>
       </c>
       <c r="L36" s="7" t="n">
         <f aca="false">L12-L32-L35</f>
-        <v>-118986.629232285</v>
+        <v>-118743.731460031</v>
       </c>
       <c r="M36" s="7" t="n">
         <f aca="false">M12-M32-M35</f>
-        <v>-115448.175486862</v>
+        <v>-115176.718272629</v>
       </c>
       <c r="N36" s="7" t="n">
         <f aca="false">N12-N32-N35</f>
-        <v>-162171.176335574</v>
+        <v>-161873.478813408</v>
       </c>
       <c r="O36" s="7" t="n">
         <f aca="false">O12-O32-O35</f>
-        <v>-159168.993191278</v>
+        <v>-158847.117859189</v>
       </c>
       <c r="P36" s="7" t="n">
         <f aca="false">P12-P32-P35</f>
-        <v>-155557.36945053</v>
+        <v>-155205.950918222</v>
       </c>
       <c r="Q36" s="7" t="n">
         <f aca="false">Q12-Q32-Q35</f>
-        <v>-152183.454479569</v>
+        <v>-151804.745795673</v>
       </c>
       <c r="R36" s="7" t="n">
         <f aca="false">R12-R32-R35</f>
-        <v>-148235.005768204</v>
+        <v>-147823.813558667</v>
       </c>
       <c r="S36" s="7" t="n">
         <f aca="false">S12-S32-S35</f>
-        <v>-144533.079835806</v>
+        <v>-144091.799101957</v>
       </c>
       <c r="T36" s="7" t="n">
         <f aca="false">T12-T32-T35</f>
-        <v>-140285.773682319</v>
+        <v>-139809.339889746</v>
       </c>
       <c r="U36" s="7" t="n">
         <f aca="false">U12-U32-U35</f>
-        <v>-135466.005643551</v>
+        <v>-134949.717341682</v>
       </c>
       <c r="V36" s="7" t="n">
         <f aca="false">V12-V32-V35</f>
-        <v>-130933.579537791</v>
+        <v>-130380.254780574</v>
       </c>
       <c r="W36" s="7" t="n">
         <f aca="false">W12-W32-W35</f>
-        <v>-125924.285217578</v>
+        <v>-125329.241434506</v>
       </c>
       <c r="X36" s="7" t="n">
         <f aca="false">X12-X32-X35</f>
-        <v>-120389.077549794</v>
+        <v>-119747.938095404</v>
       </c>
       <c r="Y36" s="7" t="n">
         <f aca="false">Y12-Y32-Y35</f>
-        <v>-114364.519897074</v>
+        <v>-113673.177031293</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10782,91 +10782,91 @@
       </c>
       <c r="D40" s="14" t="n">
         <f aca="false">D12-D32</f>
-        <v>-96240.0353333333</v>
+        <v>-96211.2353333333</v>
       </c>
       <c r="E40" s="14" t="n">
         <f aca="false">E12-E32</f>
-        <v>-141960.137098458</v>
+        <v>-141898.137898458</v>
       </c>
       <c r="F40" s="14" t="n">
         <f aca="false">F12-F32</f>
-        <v>-138096.234043846</v>
+        <v>-138004.207433446</v>
       </c>
       <c r="G40" s="14" t="n">
         <f aca="false">G12-G32</f>
-        <v>-134608.772985197</v>
+        <v>-134489.527247206</v>
       </c>
       <c r="H40" s="14" t="n">
         <f aca="false">H12-H32</f>
-        <v>-131454.545715594</v>
+        <v>-131310.568699843</v>
       </c>
       <c r="I40" s="14" t="n">
         <f aca="false">I12-I32</f>
-        <v>-128595.48042136</v>
+        <v>-128428.977254667</v>
       </c>
       <c r="J40" s="14" t="n">
         <f aca="false">J12-J32</f>
-        <v>-125106.752546937</v>
+        <v>-124912.478673691</v>
       </c>
       <c r="K40" s="14" t="n">
         <f aca="false">K12-K32</f>
-        <v>-121904.68892619</v>
+        <v>-121685.039680813</v>
       </c>
       <c r="L40" s="14" t="n">
         <f aca="false">L12-L32</f>
-        <v>-118986.629232285</v>
+        <v>-118743.731460031</v>
       </c>
       <c r="M40" s="14" t="n">
         <f aca="false">M12-M32</f>
-        <v>-115448.175486862</v>
+        <v>-115176.718272629</v>
       </c>
       <c r="N40" s="14" t="n">
         <f aca="false">N12-N32</f>
-        <v>-162171.176335574</v>
+        <v>-161873.478813408</v>
       </c>
       <c r="O40" s="14" t="n">
         <f aca="false">O12-O32</f>
-        <v>-159168.993191278</v>
+        <v>-158847.117859189</v>
       </c>
       <c r="P40" s="14" t="n">
         <f aca="false">P12-P32</f>
-        <v>-155557.36945053</v>
+        <v>-155205.950918222</v>
       </c>
       <c r="Q40" s="14" t="n">
         <f aca="false">Q12-Q32</f>
-        <v>-152183.454479569</v>
+        <v>-151804.745795673</v>
       </c>
       <c r="R40" s="14" t="n">
         <f aca="false">R12-R32</f>
-        <v>-148235.005768204</v>
+        <v>-147823.813558667</v>
       </c>
       <c r="S40" s="14" t="n">
         <f aca="false">S12-S32</f>
-        <v>-144533.079835806</v>
+        <v>-144091.799101957</v>
       </c>
       <c r="T40" s="14" t="n">
         <f aca="false">T12-T32</f>
-        <v>-140285.773682319</v>
+        <v>-139809.339889746</v>
       </c>
       <c r="U40" s="14" t="n">
         <f aca="false">U12-U32</f>
-        <v>-135466.005643551</v>
+        <v>-134949.717341682</v>
       </c>
       <c r="V40" s="14" t="n">
         <f aca="false">V12-V32</f>
-        <v>-130933.579537791</v>
+        <v>-130380.254780574</v>
       </c>
       <c r="W40" s="14" t="n">
         <f aca="false">W12-W32</f>
-        <v>-125924.285217578</v>
+        <v>-125329.241434506</v>
       </c>
       <c r="X40" s="14" t="n">
         <f aca="false">X12-X32</f>
-        <v>-120389.077549794</v>
+        <v>-119747.938095404</v>
       </c>
       <c r="Y40" s="14" t="n">
         <f aca="false">Y12-Y32</f>
-        <v>-114364.519897074</v>
+        <v>-113673.177031293</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10883,91 +10883,91 @@
       </c>
       <c r="D41" s="14" t="n">
         <f aca="false">D40-D38</f>
-        <v>-96358.4723333333</v>
+        <v>-96329.6723333333</v>
       </c>
       <c r="E41" s="14" t="n">
         <f aca="false">E40-E38</f>
-        <v>-142214.711626083</v>
+        <v>-142152.712426083</v>
       </c>
       <c r="F41" s="14" t="n">
         <f aca="false">F40-F38</f>
-        <v>-138473.523974276</v>
+        <v>-138381.497363876</v>
       </c>
       <c r="G41" s="14" t="n">
         <f aca="false">G40-G38</f>
-        <v>-135096.90417152</v>
+        <v>-134977.658433529</v>
       </c>
       <c r="H41" s="14" t="n">
         <f aca="false">H40-H38</f>
-        <v>-132043.006774658</v>
+        <v>-131899.029758907</v>
       </c>
       <c r="I41" s="14" t="n">
         <f aca="false">I40-I38</f>
-        <v>-129274.960766149</v>
+        <v>-129108.457599455</v>
       </c>
       <c r="J41" s="14" t="n">
         <f aca="false">J40-J38</f>
-        <v>-125898.33763297</v>
+        <v>-125704.063759723</v>
       </c>
       <c r="K41" s="14" t="n">
         <f aca="false">K40-K38</f>
-        <v>-122798.28383273</v>
+        <v>-122578.634587354</v>
       </c>
       <c r="L41" s="14" t="n">
         <f aca="false">L40-L38</f>
-        <v>-119973.274922813</v>
+        <v>-119730.377150559</v>
       </c>
       <c r="M41" s="14" t="n">
         <f aca="false">M40-M38</f>
-        <v>-116549.118289731</v>
+        <v>-116277.661075498</v>
       </c>
       <c r="N41" s="14" t="n">
         <f aca="false">N40-N38</f>
-        <v>-163376.665239395</v>
+        <v>-163078.967717229</v>
       </c>
       <c r="O41" s="14" t="n">
         <f aca="false">O40-O38</f>
-        <v>-160470.358628988</v>
+        <v>-160148.4832969</v>
       </c>
       <c r="P41" s="14" t="n">
         <f aca="false">P40-P38</f>
-        <v>-156975.965532044</v>
+        <v>-156624.546999736</v>
       </c>
       <c r="Q41" s="14" t="n">
         <f aca="false">Q40-Q38</f>
-        <v>-153709.827995368</v>
+        <v>-153331.119311472</v>
       </c>
       <c r="R41" s="14" t="n">
         <f aca="false">R40-R38</f>
-        <v>-149889.711751417</v>
+        <v>-149478.51954188</v>
       </c>
       <c r="S41" s="14" t="n">
         <f aca="false">S40-S38</f>
-        <v>-146306.086067645</v>
+        <v>-145864.805333796</v>
       </c>
       <c r="T41" s="14" t="n">
         <f aca="false">T40-T38</f>
-        <v>-142197.017618336</v>
+        <v>-141720.583825763</v>
       </c>
       <c r="U41" s="14" t="n">
         <f aca="false">U40-U38</f>
-        <v>-137533.874742616</v>
+        <v>-137017.586440747</v>
       </c>
       <c r="V41" s="14" t="n">
         <f aca="false">V40-V38</f>
-        <v>-133146.302186701</v>
+        <v>-132592.977429485</v>
       </c>
       <c r="W41" s="14" t="n">
         <f aca="false">W40-W38</f>
-        <v>-128300.090497081</v>
+        <v>-127705.04671401</v>
       </c>
       <c r="X41" s="14" t="n">
         <f aca="false">X40-X38</f>
-        <v>-122944.886485214</v>
+        <v>-122303.747030824</v>
       </c>
       <c r="Y41" s="14" t="n">
         <f aca="false">Y40-Y38</f>
-        <v>-117116.100510322</v>
+        <v>-116424.757644541</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10984,91 +10984,91 @@
       </c>
       <c r="D42" s="14" t="n">
         <f aca="false">D14-D32-D38</f>
-        <v>-95692.9723333333</v>
+        <v>-95664.1723333333</v>
       </c>
       <c r="E42" s="14" t="n">
         <f aca="false">E14-E32-E38</f>
-        <v>-140966.899126083</v>
+        <v>-140904.899926083</v>
       </c>
       <c r="F42" s="14" t="n">
         <f aca="false">F14-F32-F38</f>
-        <v>-136809.773974276</v>
+        <v>-136717.747363876</v>
       </c>
       <c r="G42" s="14" t="n">
         <f aca="false">G14-G32-G38</f>
-        <v>-133017.21667152</v>
+        <v>-132897.970933529</v>
       </c>
       <c r="H42" s="14" t="n">
         <f aca="false">H14-H32-H38</f>
-        <v>-129547.381774658</v>
+        <v>-129403.404758907</v>
       </c>
       <c r="I42" s="14" t="n">
         <f aca="false">I14-I32-I38</f>
-        <v>-126363.398266149</v>
+        <v>-126196.895099455</v>
       </c>
       <c r="J42" s="14" t="n">
         <f aca="false">J14-J32-J38</f>
-        <v>-121905.33763297</v>
+        <v>-121711.063759723</v>
       </c>
       <c r="K42" s="14" t="n">
         <f aca="false">K14-K32-K38</f>
-        <v>-118306.15883273</v>
+        <v>-118086.509587354</v>
       </c>
       <c r="L42" s="14" t="n">
         <f aca="false">L14-L32-L38</f>
-        <v>-114982.024922813</v>
+        <v>-114739.127150559</v>
       </c>
       <c r="M42" s="14" t="n">
         <f aca="false">M14-M32-M38</f>
-        <v>-110143.680789731</v>
+        <v>-109872.223575498</v>
       </c>
       <c r="N42" s="14" t="n">
         <f aca="false">N14-N32-N38</f>
-        <v>-156388.915239395</v>
+        <v>-156091.217717229</v>
       </c>
       <c r="O42" s="14" t="n">
         <f aca="false">O14-O32-O38</f>
-        <v>-152900.296128988</v>
+        <v>-152578.4207969</v>
       </c>
       <c r="P42" s="14" t="n">
         <f aca="false">P14-P32-P38</f>
-        <v>-147658.965532044</v>
+        <v>-147307.546999736</v>
       </c>
       <c r="Q42" s="14" t="n">
         <f aca="false">Q14-Q32-Q38</f>
-        <v>-143727.327995368</v>
+        <v>-143348.619311472</v>
       </c>
       <c r="R42" s="14" t="n">
         <f aca="false">R14-R32-R38</f>
-        <v>-137910.711751417</v>
+        <v>-137499.51954188</v>
       </c>
       <c r="S42" s="14" t="n">
         <f aca="false">S14-S32-S38</f>
-        <v>-133578.398567645</v>
+        <v>-133137.117833796</v>
       </c>
       <c r="T42" s="14" t="n">
         <f aca="false">T14-T32-T38</f>
-        <v>-127223.267618336</v>
+        <v>-126746.833825763</v>
       </c>
       <c r="U42" s="14" t="n">
         <f aca="false">U14-U32-U38</f>
-        <v>-120147.687242616</v>
+        <v>-119631.398940747</v>
       </c>
       <c r="V42" s="14" t="n">
         <f aca="false">V14-V32-V38</f>
-        <v>-114845.052186701</v>
+        <v>-114291.727429485</v>
       </c>
       <c r="W42" s="14" t="n">
         <f aca="false">W14-W32-W38</f>
-        <v>-107336.840497081</v>
+        <v>-106741.79671401</v>
       </c>
       <c r="X42" s="14" t="n">
         <f aca="false">X14-X32-X38</f>
-        <v>-99153.2614852139</v>
+        <v>-98512.1220308244</v>
       </c>
       <c r="Y42" s="14" t="n">
         <f aca="false">Y14-Y32-Y38</f>
-        <v>-90329.7255103215</v>
+        <v>-89638.3826445409</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11085,91 +11085,91 @@
       </c>
       <c r="D43" s="14" t="n">
         <f aca="false">C43+D42</f>
-        <v>204397.861</v>
+        <v>204426.661</v>
       </c>
       <c r="E43" s="14" t="n">
         <f aca="false">D43+E42</f>
-        <v>63430.9618739167</v>
+        <v>63521.7610739167</v>
       </c>
       <c r="F43" s="14" t="n">
         <f aca="false">E43+F42</f>
-        <v>-73378.812100359</v>
+        <v>-73195.986289959</v>
       </c>
       <c r="G43" s="14" t="n">
         <f aca="false">F43+G42</f>
-        <v>-206396.028771879</v>
+        <v>-206093.957223488</v>
       </c>
       <c r="H43" s="14" t="n">
         <f aca="false">G43+H42</f>
-        <v>-335943.410546537</v>
+        <v>-335497.361982395</v>
       </c>
       <c r="I43" s="14" t="n">
         <f aca="false">H43+I42</f>
-        <v>-462306.808812686</v>
+        <v>-461694.257081851</v>
       </c>
       <c r="J43" s="14" t="n">
         <f aca="false">I43+J42</f>
-        <v>-584212.146445656</v>
+        <v>-583405.320841574</v>
       </c>
       <c r="K43" s="14" t="n">
         <f aca="false">J43+K42</f>
-        <v>-702518.305278386</v>
+        <v>-701491.830428928</v>
       </c>
       <c r="L43" s="14" t="n">
         <f aca="false">K43+L42</f>
-        <v>-817500.330201199</v>
+        <v>-816230.957579486</v>
       </c>
       <c r="M43" s="14" t="n">
         <f aca="false">L43+M42</f>
-        <v>-927644.01099093</v>
+        <v>-926103.181154984</v>
       </c>
       <c r="N43" s="14" t="n">
         <f aca="false">M43+N42</f>
-        <v>-1084032.92623032</v>
+        <v>-1082194.39887221</v>
       </c>
       <c r="O43" s="14" t="n">
         <f aca="false">N43+O42</f>
-        <v>-1236933.22235931</v>
+        <v>-1234772.81966911</v>
       </c>
       <c r="P43" s="14" t="n">
         <f aca="false">O43+P42</f>
-        <v>-1384592.18789136</v>
+        <v>-1382080.36666885</v>
       </c>
       <c r="Q43" s="14" t="n">
         <f aca="false">P43+Q42</f>
-        <v>-1528319.51588672</v>
+        <v>-1525428.98598032</v>
       </c>
       <c r="R43" s="14" t="n">
         <f aca="false">Q43+R42</f>
-        <v>-1666230.22763814</v>
+        <v>-1662928.5055222</v>
       </c>
       <c r="S43" s="14" t="n">
         <f aca="false">R43+S42</f>
-        <v>-1799808.62620579</v>
+        <v>-1796065.623356</v>
       </c>
       <c r="T43" s="14" t="n">
         <f aca="false">S43+T42</f>
-        <v>-1927031.89382412</v>
+        <v>-1922812.45718176</v>
       </c>
       <c r="U43" s="14" t="n">
         <f aca="false">T43+U42</f>
-        <v>-2047179.58106674</v>
+        <v>-2042443.85612251</v>
       </c>
       <c r="V43" s="14" t="n">
         <f aca="false">U43+V42</f>
-        <v>-2162024.63325344</v>
+        <v>-2156735.58355199</v>
       </c>
       <c r="W43" s="14" t="n">
         <f aca="false">V43+W42</f>
-        <v>-2269361.47375052</v>
+        <v>-2263477.380266</v>
       </c>
       <c r="X43" s="14" t="n">
         <f aca="false">W43+X42</f>
-        <v>-2368514.73523574</v>
+        <v>-2361989.50229683</v>
       </c>
       <c r="Y43" s="14" t="n">
         <f aca="false">X43+Y42</f>
-        <v>-2458844.46074606</v>
+        <v>-2451627.88494137</v>
       </c>
       <c r="Z43" s="8" t="s">
         <v>272</v>
@@ -12422,87 +12422,87 @@
       </c>
       <c r="E17" s="7" t="n">
         <f aca="false">Допущения!$D$24+E10*Допущения!$D$28*Допущения!$D$29</f>
-        <v>7085.5</v>
+        <v>7054</v>
       </c>
       <c r="F17" s="7" t="n">
         <f aca="false">Допущения!$D$24+F10*Допущения!$D$28*Допущения!$D$29</f>
-        <v>7164.07165</v>
+        <v>7103.6242</v>
       </c>
       <c r="G17" s="7" t="n">
         <f aca="false">Допущения!$D$24+G10*Допущения!$D$28*Допущения!$D$29</f>
-        <v>7236.43908168125</v>
+        <v>7149.329946325</v>
       </c>
       <c r="H17" s="7" t="n">
         <f aca="false">Допущения!$D$24+H10*Допущения!$D$28*Допущения!$D$29</f>
-        <v>7303.24857227435</v>
+        <v>7191.52541406801</v>
       </c>
       <c r="I17" s="7" t="n">
         <f aca="false">Допущения!$D$24+I10*Допущения!$D$28*Допущения!$D$29</f>
-        <v>7365.0774941369</v>
+        <v>7230.57525945488</v>
       </c>
       <c r="J17" s="7" t="n">
         <f aca="false">Допущения!$D$24+J10*Допущения!$D$28*Допущения!$D$29</f>
-        <v>7422.44218858875</v>
+        <v>7266.80559279289</v>
       </c>
       <c r="K17" s="7" t="n">
         <f aca="false">Допущения!$D$24+K10*Допущения!$D$28*Допущения!$D$29</f>
-        <v>7475.80489909186</v>
+        <v>7300.50835732117</v>
       </c>
       <c r="L17" s="7" t="n">
         <f aca="false">Допущения!$D$24+L10*Допущения!$D$28*Допущения!$D$29</f>
-        <v>7525.57988125171</v>
+        <v>7331.94518815898</v>
       </c>
       <c r="M17" s="7" t="n">
         <f aca="false">Допущения!$D$24+M10*Допущения!$D$28*Допущения!$D$29</f>
-        <v>7600.6387918833</v>
+        <v>7379.3508159263</v>
       </c>
       <c r="N17" s="7" t="n">
         <f aca="false">Допущения!$D$24+N10*Допущения!$D$28*Допущения!$D$29</f>
-        <v>7670.73209619663</v>
+        <v>7423.62027128209</v>
       </c>
       <c r="O17" s="7" t="n">
         <f aca="false">Допущения!$D$24+O10*Допущения!$D$28*Допущения!$D$29</f>
-        <v>7736.36672262672</v>
+        <v>7465.07371955372</v>
       </c>
       <c r="P17" s="7" t="n">
         <f aca="false">Допущения!$D$24+P10*Допущения!$D$28*Допущения!$D$29</f>
-        <v>7797.99877586925</v>
+        <v>7503.99922686479</v>
       </c>
       <c r="Q17" s="7" t="n">
         <f aca="false">Допущения!$D$24+Q10*Допущения!$D$28*Допущения!$D$29</f>
-        <v>7856.03911171142</v>
+        <v>7540.6562810809</v>
       </c>
       <c r="R17" s="7" t="n">
         <f aca="false">Допущения!$D$24+R10*Допущения!$D$28*Допущения!$D$29</f>
-        <v>7939.35827445511</v>
+        <v>7593.27891018217</v>
       </c>
       <c r="S17" s="7" t="n">
         <f aca="false">Допущения!$D$24+S10*Допущения!$D$28*Допущения!$D$29</f>
-        <v>8017.84883603661</v>
+        <v>7642.85189644418</v>
       </c>
       <c r="T17" s="7" t="n">
         <f aca="false">Допущения!$D$24+T10*Допущения!$D$28*Допущения!$D$29</f>
-        <v>8092.00028669675</v>
+        <v>7689.68439159795</v>
       </c>
       <c r="U17" s="7" t="n">
         <f aca="false">Допущения!$D$24+U10*Допущения!$D$28*Допущения!$D$29</f>
-        <v>8190.75536772937</v>
+        <v>7752.05602172381</v>
       </c>
       <c r="V17" s="7" t="n">
         <f aca="false">Допущения!$D$24+V10*Допущения!$D$28*Допущения!$D$29</f>
-        <v>8284.15780959901</v>
+        <v>7811.04703764148</v>
       </c>
       <c r="W17" s="7" t="n">
         <f aca="false">Допущения!$D$24+W10*Допущения!$D$28*Допущения!$D$29</f>
-        <v>8372.74698216799</v>
+        <v>7866.99809400084</v>
       </c>
       <c r="X17" s="7" t="n">
         <f aca="false">Допущения!$D$24+X10*Допущения!$D$28*Допущения!$D$29</f>
-        <v>8485.51225201134</v>
+        <v>7938.21826442822</v>
       </c>
       <c r="Y17" s="7" t="n">
         <f aca="false">Допущения!$D$24+Y10*Допущения!$D$28*Допущения!$D$29</f>
-        <v>8592.62576920501</v>
+        <v>8005.86890686632</v>
       </c>
       <c r="Z17" s="8" t="s">
         <v>243</v>
@@ -13952,87 +13952,87 @@
       </c>
       <c r="E32" s="14" t="n">
         <f aca="false">SUM(E16:E31)</f>
-        <v>150255.537333333</v>
+        <v>150224.037333333</v>
       </c>
       <c r="F32" s="14" t="n">
         <f aca="false">SUM(F16:F31)</f>
-        <v>150483.5019311</v>
+        <v>150423.0544811</v>
       </c>
       <c r="G32" s="14" t="n">
         <f aca="false">SUM(G16:G31)</f>
-        <v>150695.146848064</v>
+        <v>150608.037712708</v>
       </c>
       <c r="H32" s="14" t="n">
         <f aca="false">SUM(H16:H31)</f>
-        <v>150892.176933686</v>
+        <v>150780.453775479</v>
       </c>
       <c r="I32" s="14" t="n">
         <f aca="false">SUM(I16:I31)</f>
-        <v>151076.113647851</v>
+        <v>150941.611413169</v>
       </c>
       <c r="J32" s="14" t="n">
         <f aca="false">SUM(J16:J31)</f>
-        <v>151248.316142792</v>
+        <v>151092.679546996</v>
       </c>
       <c r="K32" s="14" t="n">
         <f aca="false">SUM(K16:K31)</f>
-        <v>151409.999810744</v>
+        <v>151234.703268974</v>
       </c>
       <c r="L32" s="14" t="n">
         <f aca="false">SUM(L16:L31)</f>
-        <v>151562.252615585</v>
+        <v>151368.617922492</v>
       </c>
       <c r="M32" s="14" t="n">
         <f aca="false">SUM(M16:M31)</f>
-        <v>151878.682151845</v>
+        <v>151657.394175888</v>
       </c>
       <c r="N32" s="14" t="n">
         <f aca="false">SUM(N16:N31)</f>
-        <v>202090.819328606</v>
+        <v>201843.707503691</v>
       </c>
       <c r="O32" s="14" t="n">
         <f aca="false">SUM(O16:O31)</f>
-        <v>202291.253984688</v>
+        <v>202019.960981615</v>
       </c>
       <c r="P32" s="14" t="n">
         <f aca="false">SUM(P16:P31)</f>
-        <v>202481.178908182</v>
+        <v>202187.179359178</v>
       </c>
       <c r="Q32" s="14" t="n">
         <f aca="false">SUM(Q16:Q31)</f>
-        <v>202661.667174926</v>
+        <v>202346.284344295</v>
       </c>
       <c r="R32" s="14" t="n">
         <f aca="false">SUM(R16:R31)</f>
-        <v>203051.514612273</v>
+        <v>202705.435248</v>
       </c>
       <c r="S32" s="14" t="n">
         <f aca="false">SUM(S16:S31)</f>
-        <v>203291.80855954</v>
+        <v>202916.811619948</v>
       </c>
       <c r="T32" s="14" t="n">
         <f aca="false">SUM(T16:T31)</f>
-        <v>203520.717290795</v>
+        <v>203118.401395696</v>
       </c>
       <c r="U32" s="14" t="n">
         <f aca="false">SUM(U16:U31)</f>
-        <v>203984.339330091</v>
+        <v>203545.639984086</v>
       </c>
       <c r="V32" s="14" t="n">
         <f aca="false">SUM(V16:V31)</f>
-        <v>204269.665169718</v>
+        <v>203796.55439776</v>
       </c>
       <c r="W32" s="14" t="n">
         <f aca="false">SUM(W16:W31)</f>
-        <v>204542.36706721</v>
+        <v>204036.618179043</v>
       </c>
       <c r="X32" s="14" t="n">
         <f aca="false">SUM(X16:X31)</f>
-        <v>205075.778459158</v>
+        <v>204528.484471575</v>
       </c>
       <c r="Y32" s="14" t="n">
         <f aca="false">SUM(Y16:Y31)</f>
-        <v>205402.731150854</v>
+        <v>204815.974288516</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14290,87 +14290,87 @@
       </c>
       <c r="E36" s="7" t="n">
         <f aca="false">E12-E32-E35</f>
-        <v>-145811.612333333</v>
+        <v>-145780.112333333</v>
       </c>
       <c r="F36" s="7" t="n">
         <f aca="false">F12-F32-F35</f>
-        <v>-141972.437005544</v>
+        <v>-141911.989555544</v>
       </c>
       <c r="G36" s="7" t="n">
         <f aca="false">G12-G32-G35</f>
-        <v>-138454.124079754</v>
+        <v>-138367.014944398</v>
       </c>
       <c r="H36" s="7" t="n">
         <f aca="false">H12-H32-H35</f>
-        <v>-135223.09266442</v>
+        <v>-135111.369506214</v>
       </c>
       <c r="I36" s="7" t="n">
         <f aca="false">I12-I32-I35</f>
-        <v>-132249.394635148</v>
+        <v>-132114.892400466</v>
       </c>
       <c r="J36" s="7" t="n">
         <f aca="false">J12-J32-J35</f>
-        <v>-129506.295447137</v>
+        <v>-129350.658851341</v>
       </c>
       <c r="K36" s="7" t="n">
         <f aca="false">K12-K32-K35</f>
-        <v>-126969.905533444</v>
+        <v>-126794.608991673</v>
       </c>
       <c r="L36" s="7" t="n">
         <f aca="false">L12-L32-L35</f>
-        <v>-124618.855915589</v>
+        <v>-124425.221222496</v>
       </c>
       <c r="M36" s="7" t="n">
         <f aca="false">M12-M32-M35</f>
-        <v>-121148.514597564</v>
+        <v>-120927.226621607</v>
       </c>
       <c r="N36" s="7" t="n">
         <f aca="false">N12-N32-N35</f>
-        <v>-167842.689359417</v>
+        <v>-167595.577534502</v>
       </c>
       <c r="O36" s="7" t="n">
         <f aca="false">O12-O32-O35</f>
-        <v>-164766.623027097</v>
+        <v>-164495.330024024</v>
       </c>
       <c r="P36" s="7" t="n">
         <f aca="false">P12-P32-P35</f>
-        <v>-161896.952275529</v>
+        <v>-161602.952726524</v>
       </c>
       <c r="Q36" s="7" t="n">
         <f aca="false">Q12-Q32-Q35</f>
-        <v>-159212.676178894</v>
+        <v>-158897.293348264</v>
       </c>
       <c r="R36" s="7" t="n">
         <f aca="false">R12-R32-R35</f>
-        <v>-155469.081129465</v>
+        <v>-155123.001765192</v>
       </c>
       <c r="S36" s="7" t="n">
         <f aca="false">S12-S32-S35</f>
-        <v>-151836.970553861</v>
+        <v>-151461.973614268</v>
       </c>
       <c r="T36" s="7" t="n">
         <f aca="false">T12-T32-T35</f>
-        <v>-148428.344931956</v>
+        <v>-148026.029036857</v>
       </c>
       <c r="U36" s="7" t="n">
         <f aca="false">U12-U32-U35</f>
-        <v>-144030.735029142</v>
+        <v>-143592.035683136</v>
       </c>
       <c r="V36" s="7" t="n">
         <f aca="false">V12-V32-V35</f>
-        <v>-139743.864276865</v>
+        <v>-139270.753504907</v>
       </c>
       <c r="W36" s="7" t="n">
         <f aca="false">W12-W32-W35</f>
-        <v>-135704.725343576</v>
+        <v>-135198.976455409</v>
       </c>
       <c r="X36" s="7" t="n">
         <f aca="false">X12-X32-X35</f>
-        <v>-130734.432665373</v>
+        <v>-130187.13867779</v>
       </c>
       <c r="Y36" s="7" t="n">
         <f aca="false">Y12-Y32-Y35</f>
-        <v>-125862.871206984</v>
+        <v>-125276.114344646</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14625,87 +14625,87 @@
       </c>
       <c r="E40" s="14" t="n">
         <f aca="false">E12-E32</f>
-        <v>-145811.612333333</v>
+        <v>-145780.112333333</v>
       </c>
       <c r="F40" s="14" t="n">
         <f aca="false">F12-F32</f>
-        <v>-141972.437005544</v>
+        <v>-141911.989555544</v>
       </c>
       <c r="G40" s="14" t="n">
         <f aca="false">G12-G32</f>
-        <v>-138454.124079754</v>
+        <v>-138367.014944398</v>
       </c>
       <c r="H40" s="14" t="n">
         <f aca="false">H12-H32</f>
-        <v>-135223.09266442</v>
+        <v>-135111.369506214</v>
       </c>
       <c r="I40" s="14" t="n">
         <f aca="false">I12-I32</f>
-        <v>-132249.394635148</v>
+        <v>-132114.892400466</v>
       </c>
       <c r="J40" s="14" t="n">
         <f aca="false">J12-J32</f>
-        <v>-129506.295447137</v>
+        <v>-129350.658851341</v>
       </c>
       <c r="K40" s="14" t="n">
         <f aca="false">K12-K32</f>
-        <v>-126969.905533444</v>
+        <v>-126794.608991673</v>
       </c>
       <c r="L40" s="14" t="n">
         <f aca="false">L12-L32</f>
-        <v>-124618.855915589</v>
+        <v>-124425.221222496</v>
       </c>
       <c r="M40" s="14" t="n">
         <f aca="false">M12-M32</f>
-        <v>-121148.514597564</v>
+        <v>-120927.226621607</v>
       </c>
       <c r="N40" s="14" t="n">
         <f aca="false">N12-N32</f>
-        <v>-167842.689359417</v>
+        <v>-167595.577534502</v>
       </c>
       <c r="O40" s="14" t="n">
         <f aca="false">O12-O32</f>
-        <v>-164766.623027097</v>
+        <v>-164495.330024024</v>
       </c>
       <c r="P40" s="14" t="n">
         <f aca="false">P12-P32</f>
-        <v>-161896.952275529</v>
+        <v>-161602.952726524</v>
       </c>
       <c r="Q40" s="14" t="n">
         <f aca="false">Q12-Q32</f>
-        <v>-159212.676178894</v>
+        <v>-158897.293348264</v>
       </c>
       <c r="R40" s="14" t="n">
         <f aca="false">R12-R32</f>
-        <v>-155469.081129465</v>
+        <v>-155123.001765192</v>
       </c>
       <c r="S40" s="14" t="n">
         <f aca="false">S12-S32</f>
-        <v>-151836.970553861</v>
+        <v>-151461.973614268</v>
       </c>
       <c r="T40" s="14" t="n">
         <f aca="false">T12-T32</f>
-        <v>-148428.344931956</v>
+        <v>-148026.029036857</v>
       </c>
       <c r="U40" s="14" t="n">
         <f aca="false">U12-U32</f>
-        <v>-144030.735029142</v>
+        <v>-143592.035683136</v>
       </c>
       <c r="V40" s="14" t="n">
         <f aca="false">V12-V32</f>
-        <v>-139743.864276865</v>
+        <v>-139270.753504907</v>
       </c>
       <c r="W40" s="14" t="n">
         <f aca="false">W12-W32</f>
-        <v>-135704.725343576</v>
+        <v>-135198.976455409</v>
       </c>
       <c r="X40" s="14" t="n">
         <f aca="false">X12-X32</f>
-        <v>-130734.432665373</v>
+        <v>-130187.13867779</v>
       </c>
       <c r="Y40" s="14" t="n">
         <f aca="false">Y12-Y32</f>
-        <v>-125862.871206984</v>
+        <v>-125276.114344646</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14726,87 +14726,87 @@
       </c>
       <c r="E41" s="14" t="n">
         <f aca="false">E40-E38</f>
-        <v>-145944.930083333</v>
+        <v>-145913.430083333</v>
       </c>
       <c r="F41" s="14" t="n">
         <f aca="false">F40-F38</f>
-        <v>-142227.768953311</v>
+        <v>-142167.321503311</v>
       </c>
       <c r="G41" s="14" t="n">
         <f aca="false">G40-G38</f>
-        <v>-138821.354762804</v>
+        <v>-138734.245627447</v>
       </c>
       <c r="H41" s="14" t="n">
         <f aca="false">H40-H38</f>
-        <v>-135693.165192498</v>
+        <v>-135581.442034292</v>
       </c>
       <c r="I41" s="14" t="n">
         <f aca="false">I40-I38</f>
-        <v>-132814.196205529</v>
+        <v>-132679.693970847</v>
       </c>
       <c r="J41" s="14" t="n">
         <f aca="false">J40-J38</f>
-        <v>-130158.556068006</v>
+        <v>-130002.919472211</v>
       </c>
       <c r="K41" s="14" t="n">
         <f aca="false">K40-K38</f>
-        <v>-127703.108361763</v>
+        <v>-127527.811819993</v>
       </c>
       <c r="L41" s="14" t="n">
         <f aca="false">L40-L38</f>
-        <v>-125427.157816588</v>
+        <v>-125233.523123496</v>
       </c>
       <c r="M41" s="14" t="n">
         <f aca="false">M40-M38</f>
-        <v>-122070.419624192</v>
+        <v>-121849.131648235</v>
       </c>
       <c r="N41" s="14" t="n">
         <f aca="false">N40-N38</f>
-        <v>-168870.133258492</v>
+        <v>-168623.021433578</v>
       </c>
       <c r="O41" s="14" t="n">
         <f aca="false">O40-O38</f>
-        <v>-165892.361955825</v>
+        <v>-165621.068952752</v>
       </c>
       <c r="P41" s="14" t="n">
         <f aca="false">P40-P38</f>
-        <v>-163114.479074508</v>
+        <v>-162820.479525504</v>
       </c>
       <c r="Q41" s="14" t="n">
         <f aca="false">Q40-Q38</f>
-        <v>-160516.145908775</v>
+        <v>-160200.763078145</v>
       </c>
       <c r="R41" s="14" t="n">
         <f aca="false">R40-R38</f>
-        <v>-156896.554133949</v>
+        <v>-156550.474769676</v>
       </c>
       <c r="S41" s="14" t="n">
         <f aca="false">S40-S38</f>
-        <v>-153380.615694031</v>
+        <v>-153005.618754439</v>
       </c>
       <c r="T41" s="14" t="n">
         <f aca="false">T40-T38</f>
-        <v>-150081.116102721</v>
+        <v>-149678.800207622</v>
       </c>
       <c r="U41" s="14" t="n">
         <f aca="false">U40-U38</f>
-        <v>-145829.34315817</v>
+        <v>-145390.643812165</v>
       </c>
       <c r="V41" s="14" t="n">
         <f aca="false">V40-V38</f>
-        <v>-141679.63830365</v>
+        <v>-141206.527531693</v>
       </c>
       <c r="W41" s="14" t="n">
         <f aca="false">W40-W38</f>
-        <v>-137769.854595285</v>
+        <v>-137264.105707118</v>
       </c>
       <c r="X41" s="14" t="n">
         <f aca="false">X40-X38</f>
-        <v>-132964.673039187</v>
+        <v>-132417.379051604</v>
       </c>
       <c r="Y41" s="14" t="n">
         <f aca="false">Y40-Y38</f>
-        <v>-128249.067005301</v>
+        <v>-127662.310142962</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14827,87 +14827,87 @@
       </c>
       <c r="E42" s="14" t="n">
         <f aca="false">E14-E32-E38</f>
-        <v>-144510.805083333</v>
+        <v>-144479.305083333</v>
       </c>
       <c r="F42" s="14" t="n">
         <f aca="false">F14-F32-F38</f>
-        <v>-140315.602286644</v>
+        <v>-140255.154836644</v>
       </c>
       <c r="G42" s="14" t="n">
         <f aca="false">G14-G32-G38</f>
-        <v>-136431.14642947</v>
+        <v>-136344.037294114</v>
       </c>
       <c r="H42" s="14" t="n">
         <f aca="false">H14-H32-H38</f>
-        <v>-132824.915192498</v>
+        <v>-132713.192034292</v>
       </c>
       <c r="I42" s="14" t="n">
         <f aca="false">I14-I32-I38</f>
-        <v>-129467.904538862</v>
+        <v>-129333.40230418</v>
       </c>
       <c r="J42" s="14" t="n">
         <f aca="false">J14-J32-J38</f>
-        <v>-126334.222734673</v>
+        <v>-126178.586138877</v>
       </c>
       <c r="K42" s="14" t="n">
         <f aca="false">K14-K32-K38</f>
-        <v>-123400.733361763</v>
+        <v>-123225.436819993</v>
       </c>
       <c r="L42" s="14" t="n">
         <f aca="false">L14-L32-L38</f>
-        <v>-120646.741149922</v>
+        <v>-120453.106456829</v>
       </c>
       <c r="M42" s="14" t="n">
         <f aca="false">M14-M32-M38</f>
-        <v>-115059.141846414</v>
+        <v>-114837.853870457</v>
       </c>
       <c r="N42" s="14" t="n">
         <f aca="false">N14-N32-N38</f>
-        <v>-161221.466591826</v>
+        <v>-160974.354766911</v>
       </c>
       <c r="O42" s="14" t="n">
         <f aca="false">O14-O32-O38</f>
-        <v>-157606.306400269</v>
+        <v>-157335.013397196</v>
       </c>
       <c r="P42" s="14" t="n">
         <f aca="false">P14-P32-P38</f>
-        <v>-154191.034630064</v>
+        <v>-153897.03508106</v>
       </c>
       <c r="Q42" s="14" t="n">
         <f aca="false">Q14-Q32-Q38</f>
-        <v>-150955.312575442</v>
+        <v>-150639.929744812</v>
       </c>
       <c r="R42" s="14" t="n">
         <f aca="false">R14-R32-R38</f>
-        <v>-144148.776356171</v>
+        <v>-143802.696991898</v>
       </c>
       <c r="S42" s="14" t="n">
         <f aca="false">S14-S32-S38</f>
-        <v>-139836.101805142</v>
+        <v>-139461.10486555</v>
       </c>
       <c r="T42" s="14" t="n">
         <f aca="false">T14-T32-T38</f>
-        <v>-135739.866102721</v>
+        <v>-135337.550207622</v>
       </c>
       <c r="U42" s="14" t="n">
         <f aca="false">U14-U32-U38</f>
-        <v>-127663.759824837</v>
+        <v>-127225.060478831</v>
       </c>
       <c r="V42" s="14" t="n">
         <f aca="false">V14-V32-V38</f>
-        <v>-122557.971636984</v>
+        <v>-122084.860865026</v>
       </c>
       <c r="W42" s="14" t="n">
         <f aca="false">W14-W32-W38</f>
-        <v>-117692.104595285</v>
+        <v>-117186.355707118</v>
       </c>
       <c r="X42" s="14" t="n">
         <f aca="false">X14-X32-X38</f>
-        <v>-108425.200816965</v>
+        <v>-107877.906829382</v>
       </c>
       <c r="Y42" s="14" t="n">
         <f aca="false">Y14-Y32-Y38</f>
-        <v>-102594.164227523</v>
+        <v>-102007.407365184</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14928,87 +14928,87 @@
       </c>
       <c r="E43" s="14" t="n">
         <f aca="false">D43+E42</f>
-        <v>55625.4449166667</v>
+        <v>55656.9449166667</v>
       </c>
       <c r="F43" s="14" t="n">
         <f aca="false">E43+F42</f>
-        <v>-84690.1573699777</v>
+        <v>-84598.2099199777</v>
       </c>
       <c r="G43" s="14" t="n">
         <f aca="false">F43+G42</f>
-        <v>-221121.303799448</v>
+        <v>-220942.247214092</v>
       </c>
       <c r="H43" s="14" t="n">
         <f aca="false">G43+H42</f>
-        <v>-353946.218991946</v>
+        <v>-353655.439248383</v>
       </c>
       <c r="I43" s="14" t="n">
         <f aca="false">H43+I42</f>
-        <v>-483414.123530808</v>
+        <v>-482988.841552564</v>
       </c>
       <c r="J43" s="14" t="n">
         <f aca="false">I43+J42</f>
-        <v>-609748.346265481</v>
+        <v>-609167.427691441</v>
       </c>
       <c r="K43" s="14" t="n">
         <f aca="false">J43+K42</f>
-        <v>-733149.079627244</v>
+        <v>-732392.864511433</v>
       </c>
       <c r="L43" s="14" t="n">
         <f aca="false">K43+L42</f>
-        <v>-853795.820777166</v>
+        <v>-852845.970968262</v>
       </c>
       <c r="M43" s="14" t="n">
         <f aca="false">L43+M42</f>
-        <v>-968854.962623581</v>
+        <v>-967683.82483872</v>
       </c>
       <c r="N43" s="14" t="n">
         <f aca="false">M43+N42</f>
-        <v>-1130076.42921541</v>
+        <v>-1128658.17960563</v>
       </c>
       <c r="O43" s="14" t="n">
         <f aca="false">N43+O42</f>
-        <v>-1287682.73561568</v>
+        <v>-1285993.19300283</v>
       </c>
       <c r="P43" s="14" t="n">
         <f aca="false">O43+P42</f>
-        <v>-1441873.77024574</v>
+        <v>-1439890.22808389</v>
       </c>
       <c r="Q43" s="14" t="n">
         <f aca="false">P43+Q42</f>
-        <v>-1592829.08282118</v>
+        <v>-1590530.1578287</v>
       </c>
       <c r="R43" s="14" t="n">
         <f aca="false">Q43+R42</f>
-        <v>-1736977.85917735</v>
+        <v>-1734332.8548206</v>
       </c>
       <c r="S43" s="14" t="n">
         <f aca="false">R43+S42</f>
-        <v>-1876813.9609825</v>
+        <v>-1873793.95968615</v>
       </c>
       <c r="T43" s="14" t="n">
         <f aca="false">S43+T42</f>
-        <v>-2012553.82708522</v>
+        <v>-2009131.50989377</v>
       </c>
       <c r="U43" s="14" t="n">
         <f aca="false">T43+U42</f>
-        <v>-2140217.58691005</v>
+        <v>-2136356.5703726</v>
       </c>
       <c r="V43" s="14" t="n">
         <f aca="false">U43+V42</f>
-        <v>-2262775.55854704</v>
+        <v>-2258441.43123763</v>
       </c>
       <c r="W43" s="14" t="n">
         <f aca="false">V43+W42</f>
-        <v>-2380467.66314232</v>
+        <v>-2375627.78694474</v>
       </c>
       <c r="X43" s="14" t="n">
         <f aca="false">W43+X42</f>
-        <v>-2488892.86395929</v>
+        <v>-2483505.69377413</v>
       </c>
       <c r="Y43" s="14" t="n">
         <f aca="false">X43+Y42</f>
-        <v>-2591487.02818681</v>
+        <v>-2585513.10113931</v>
       </c>
       <c r="Z43" s="8" t="s">
         <v>272</v>

--- a/finance/Компас_финмодель_24м.xlsx
+++ b/finance/Компас_финмодель_24м.xlsx
@@ -31,7 +31,7 @@
     <t xml:space="preserve">«Компас» — финансовая модель на 24 месяца</t>
   </si>
   <si>
-    <t xml:space="preserve">Октябрь 2026 — сентябрь 2028. Два тарифа: One — 990 ₽ в месяц, Pro — 45 000 ₽ в год. Три колонки — темп продаж Pro.</t>
+    <t xml:space="preserve">Октябрь 2026 — сентябрь 2028. Два тарифа: One — 990 ₽ в месяц, Pro — 49 900 ₽ в год. Три колонки — темп продаж Pro.</t>
   </si>
   <si>
     <t xml:space="preserve">Один подписчик</t>
@@ -199,13 +199,13 @@
     <t xml:space="preserve">•</t>
   </si>
   <si>
-    <t xml:space="preserve">Два тарифа: One — 990 ₽ в месяц для человека, Pro — 45 000 ₽ в год для команды. Обе цены заданы, поэтому три колонки различаются только ТЕМПОМ продаж Pro: 0,5, 1 и 2 клиента в месяц.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Главное число Pro — «один Pro = столько подписчиков One». При цене 45 тыс это 3,7: Pro не рычаг, а второй ручеёк примерно той же ширины. Для сравнения, тариф за 200 тыс давал бы 17.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Строки «порог: только One» и «порог: только Pro» — две границы одного и того же: 111 подписчиков ИЛИ 30 договоров. Любая настоящая смесь лежит между ними.</t>
+    <t xml:space="preserve">Два тарифа: One — 990 ₽ в месяц для человека, Pro — 49 900 ₽ в год для команды. Обе цены заданы, поэтому три колонки различаются только ТЕМПОМ продаж Pro: 0,5, 1 и 2 клиента в месяц.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Главное число Pro — «один Pro = столько подписчиков One». При цене 49,9 тыс это 4,1: Pro не рычаг, а второй ручеёк примерно той же ширины. Для сравнения, тариф за 200 тыс давал бы 17.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Строки «порог: только One» и «порог: только Pro» — две границы одного и того же: 111 подписчиков ИЛИ 27 договоров. Любая настоящая смесь лежит между ними.</t>
   </si>
   <si>
     <t xml:space="preserve">Темп продаж Pro — самое неизвестное число модели: продаж ещё не было ни одной. Проверяется он первыми тремя разговорами, а не расчётом.</t>
@@ -313,7 +313,7 @@
     <t xml:space="preserve">Сколько это подписчиков One</t>
   </si>
   <si>
-    <t xml:space="preserve">Честный способ смотреть на Pro. При цене 45 тыс один договор стоит меньше четырёх подписок One — против семнадцати, если бы Pro стоил 200 тыс. Поэтому Pro здесь не рычаг, а второй ручеёк той же ширины.</t>
+    <t xml:space="preserve">Честный способ смотреть на Pro. При цене 49 900 один договор стоит около четырёх подписок One — против семнадцати, если бы Pro стоил 200 тыс. Поэтому Pro здесь не рычаг, а второй ручеёк той же ширины.</t>
   </si>
   <si>
     <t xml:space="preserve">Когда бизнес перестаёт быть убыточным</t>
@@ -355,10 +355,10 @@
     <t xml:space="preserve">Первый месяц с положительной чистой прибылью — из помесячного расчёта: там уже сложены обе выручки, людей и компаний.</t>
   </si>
   <si>
-    <t xml:space="preserve">Сколько подписчиков — это 20 млн ₽ в год (порог НДС)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Порог НДС в B2C далеко: при таком чеке до него нужны тысячи человек. Это редкий случай, когда низкая цена упрощает жизнь не только покупателю.</t>
+    <t xml:space="preserve">Сколько подписчиков — это 60 млн ₽ в год (предел АУСН)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Предел режима в B2C далеко: при таком чеке до него нужны тысячи человек. Это редкий случай, когда низкая цена упрощает жизнь не только покупателю.</t>
   </si>
   <si>
     <t xml:space="preserve">Что из этого следует</t>
@@ -379,22 +379,22 @@
     <t xml:space="preserve">Допущения модели — подписка для людей и тариф для компаний</t>
   </si>
   <si>
-    <t xml:space="preserve">Подписка одна: 990 ₽ в месяц. Три колонки — три цены КОРПОРАТИВНОГО тарифа.</t>
+    <t xml:space="preserve">Обе цены заданы: One 990 ₽ в месяц, Pro 49 900 ₽ в год. Три колонки — три ТЕМПА продаж Pro.</t>
   </si>
   <si>
     <t xml:space="preserve">Жёлтые клетки можно менять. Всё остальное считается формулами.</t>
   </si>
   <si>
-    <t xml:space="preserve">Составлено 22 сентября 2026. Ставки налогов проверены по источникам в этот день.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">120 тыс</t>
-  </si>
-  <si>
-    <t xml:space="preserve">200 тыс</t>
-  </si>
-  <si>
-    <t xml:space="preserve">250 тыс</t>
+    <t xml:space="preserve">Составлено 23 сентября 2026. Ставки налогов проверены по источникам в этот день.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pro 0,5 в месяц</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pro 1 в месяц</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pro 2 в месяц</t>
   </si>
   <si>
     <t xml:space="preserve">Откуда число</t>
@@ -481,7 +481,7 @@
     <t xml:space="preserve">Человек смотрит, возвращается, ждёт повода. Чем дороже, тем дольше думает.</t>
   </si>
   <si>
-    <t xml:space="preserve">Тариф Pro — для команды, 45 000 ₽ в год</t>
+    <t xml:space="preserve">Тариф Pro — для команды, 49 900 ₽ в год</t>
   </si>
   <si>
     <t xml:space="preserve">Pro, ₽ в год</t>
@@ -511,7 +511,7 @@
     <t xml:space="preserve">Обслуживание одного Pro, ₽ в месяц</t>
   </si>
   <si>
-    <t xml:space="preserve">ПЕРЕСЧИТАНО ПОД ЦЕНУ 45 ТЫС. Раньше здесь стояло 1 500 ₽ — величина для корпоративного тарифа за 200 тыс, и при 45 тыс она съедала бы 40% чека. Считаем от измеренного: команда из трёх человек по 20 вопросов ассистенту в месяц — это 60 вопросов по 1 ₽. Остальное — запас на выгрузки и ответы на уточнения.</t>
+    <t xml:space="preserve">ПЕРЕСЧИТАНО ПОД ЦЕНУ 49 900. Раньше здесь стояло 1 500 ₽ — величина для корпоративного тарифа за 200 тыс, и при 49 900 она съедала бы 36% чека. Считаем от измеренного: команда из трёх человек по 20 вопросов ассистенту в месяц — это 60 вопросов по 1 ₽. Остальное — запас на выгрузки и ответы на уточнения.</t>
   </si>
   <si>
     <t xml:space="preserve">Расходы, ₽ в месяц — по вашим счетам</t>
@@ -1826,15 +1826,15 @@
       </c>
       <c r="B10" s="7" t="n">
         <f aca="false">'Единица экономики'!$B$23</f>
-        <v>3350</v>
+        <v>3758.33333333333</v>
       </c>
       <c r="C10" s="7" t="n">
         <f aca="false">'Единица экономики'!$C$23</f>
-        <v>3350</v>
+        <v>3758.33333333333</v>
       </c>
       <c r="D10" s="7" t="n">
         <f aca="false">'Единица экономики'!$D$23</f>
-        <v>3350</v>
+        <v>3758.33333333333</v>
       </c>
       <c r="E10" s="8" t="s">
         <v>17</v>
@@ -1846,15 +1846,15 @@
       </c>
       <c r="B11" s="10" t="n">
         <f aca="false">'Единица экономики'!$B$24</f>
-        <v>3.7</v>
+        <v>4.1</v>
       </c>
       <c r="C11" s="10" t="n">
         <f aca="false">'Единица экономики'!$C$24</f>
-        <v>3.7</v>
+        <v>4.1</v>
       </c>
       <c r="D11" s="10" t="n">
         <f aca="false">'Единица экономики'!$D$24</f>
-        <v>3.7</v>
+        <v>4.1</v>
       </c>
       <c r="E11" s="8" t="s">
         <v>19</v>
@@ -1886,15 +1886,15 @@
       </c>
       <c r="B13" s="10" t="n">
         <f aca="false">'Единица экономики'!$B$31</f>
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="C13" s="10" t="n">
         <f aca="false">'Единица экономики'!$C$31</f>
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="D13" s="10" t="n">
         <f aca="false">'Единица экономики'!$D$31</f>
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="E13" s="8" t="s">
         <v>23</v>
@@ -2046,15 +2046,15 @@
       </c>
       <c r="B23" s="7" t="n">
         <f aca="false">SUM('Расчёт 0,5 в месяц'!B15:Y15)</f>
-        <v>388591.698086101</v>
+        <v>430905.016322143</v>
       </c>
       <c r="C23" s="7" t="n">
         <f aca="false">SUM('Расчёт 1 в месяц'!B15:Y15)</f>
-        <v>777183.396172202</v>
+        <v>861810.032644286</v>
       </c>
       <c r="D23" s="7" t="n">
         <f aca="false">SUM('Расчёт 2 в месяц'!B15:Y15)</f>
-        <v>1554366.7923444</v>
+        <v>1723620.06528857</v>
       </c>
       <c r="E23" s="8" t="s">
         <v>35</v>
@@ -2086,15 +2086,15 @@
       </c>
       <c r="B25" s="7" t="n">
         <f aca="false">SUM('Расчёт 0,5 в месяц'!B17:M17)</f>
-        <v>290036.968734385</v>
+        <v>298827.810205775</v>
       </c>
       <c r="C25" s="7" t="n">
         <f aca="false">SUM('Расчёт 1 в месяц'!B17:M17)</f>
-        <v>370769.186328779</v>
+        <v>388350.869271559</v>
       </c>
       <c r="D25" s="7" t="n">
         <f aca="false">SUM('Расчёт 2 в месяц'!B17:M17)</f>
-        <v>532233.621517568</v>
+        <v>567396.987403126</v>
       </c>
       <c r="E25" s="8"/>
     </row>
@@ -2104,15 +2104,15 @@
       </c>
       <c r="B26" s="15" t="n">
         <f aca="false">SUM('Расчёт 0,5 в месяц'!B17:Y17)</f>
-        <v>1356382.0047614</v>
+        <v>1398695.32299745</v>
       </c>
       <c r="C26" s="15" t="n">
         <f aca="false">SUM('Расчёт 1 в месяц'!B17:Y17)</f>
-        <v>1744973.70284751</v>
+        <v>1829600.33931959</v>
       </c>
       <c r="D26" s="15" t="n">
         <f aca="false">SUM('Расчёт 2 в месяц'!B17:Y17)</f>
-        <v>2522157.09901971</v>
+        <v>2691410.37196388</v>
       </c>
       <c r="E26" s="8"/>
     </row>
@@ -2122,15 +2122,15 @@
       </c>
       <c r="B27" s="7" t="n">
         <f aca="false">SUM('Расчёт 0,5 в месяц'!B38:Y38)</f>
-        <v>4157721.45104559</v>
+        <v>4159264.95104559</v>
       </c>
       <c r="C27" s="7" t="n">
         <f aca="false">SUM('Расчёт 1 в месяц'!B38:Y38)</f>
-        <v>4213346.23217478</v>
+        <v>4216433.23217478</v>
       </c>
       <c r="D27" s="7" t="n">
         <f aca="false">SUM('Расчёт 2 в месяц'!B38:Y38)</f>
-        <v>4324595.79443315</v>
+        <v>4330769.79443315</v>
       </c>
       <c r="E27" s="8"/>
     </row>
@@ -2140,15 +2140,15 @@
       </c>
       <c r="B28" s="7" t="n">
         <f aca="false">SUM('Расчёт 0,5 в месяц'!B44:Y44)</f>
-        <v>40691.4601428421</v>
+        <v>41960.8596899234</v>
       </c>
       <c r="C28" s="7" t="n">
         <f aca="false">SUM('Расчёт 1 в месяц'!B44:Y44)</f>
-        <v>52349.2110854252</v>
+        <v>54888.0101795877</v>
       </c>
       <c r="D28" s="7" t="n">
         <f aca="false">SUM('Расчёт 2 в месяц'!B44:Y44)</f>
-        <v>75664.7129705912</v>
+        <v>80742.3111589163</v>
       </c>
       <c r="E28" s="8" t="s">
         <v>42</v>
@@ -2180,15 +2180,15 @@
       </c>
       <c r="B30" s="15" t="n">
         <f aca="false">SUM('Расчёт 0,5 в месяц'!B47:Y47)</f>
-        <v>-2842030.90642703</v>
+        <v>-2802530.48773807</v>
       </c>
       <c r="C30" s="15" t="n">
         <f aca="false">SUM('Расчёт 1 в месяц'!B47:Y47)</f>
-        <v>-2520721.7404127</v>
+        <v>-2441720.90303478</v>
       </c>
       <c r="D30" s="15" t="n">
         <f aca="false">SUM('Расчёт 2 в месяц'!B47:Y47)</f>
-        <v>-1878103.40838403</v>
+        <v>-1720101.73362819</v>
       </c>
       <c r="E30" s="8"/>
     </row>
@@ -2198,15 +2198,15 @@
       </c>
       <c r="B31" s="15" t="n">
         <f aca="false">'Расчёт 0,5 в месяц'!Y49</f>
-        <v>-2046410.41701313</v>
+        <v>-1997773.31656021</v>
       </c>
       <c r="C31" s="15" t="n">
         <f aca="false">'Расчёт 1 в месяц'!Y49</f>
-        <v>-1641192.9490849</v>
+        <v>-1543918.74817906</v>
       </c>
       <c r="D31" s="15" t="n">
         <f aca="false">'Расчёт 2 в месяц'!Y49</f>
-        <v>-830758.013228435</v>
+        <v>-636209.61141676</v>
       </c>
       <c r="E31" s="8" t="s">
         <v>47</v>
@@ -2250,9 +2250,9 @@
         <f aca="false">IFERROR(MATCH(TRUE(),INDEX('Расчёт 1 в месяц'!B47:Y47&gt;0,0),0),"за 24 месяца не выходим")</f>
         <v>за 24 месяца не выходим</v>
       </c>
-      <c r="D35" s="13" t="str">
+      <c r="D35" s="13" t="n">
         <f aca="false">IFERROR(MATCH(TRUE(),INDEX('Расчёт 2 в месяц'!B47:Y47&gt;0,0),0),"за 24 месяца не выходим")</f>
-        <v>за 24 месяца не выходим</v>
+        <v>24</v>
       </c>
       <c r="E35" s="8" t="s">
         <v>50</v>
@@ -2272,7 +2272,7 @@
       </c>
       <c r="D36" s="12" t="n">
         <f aca="false">IFERROR(MATCH(TRUE(),INDEX('Расчёт 2 в месяц'!B49:Y49&lt;0,0),0),"не уходят")</f>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E36" s="8" t="s">
         <v>52</v>
@@ -2284,15 +2284,15 @@
       </c>
       <c r="B37" s="16" t="n">
         <f aca="false">MAX(0,-MIN('Расчёт 0,5 в месяц'!B49:Y49))</f>
-        <v>2046410.41701313</v>
+        <v>1997773.31656021</v>
       </c>
       <c r="C37" s="16" t="n">
         <f aca="false">MAX(0,-MIN('Расчёт 1 в месяц'!B49:Y49))</f>
-        <v>1641192.9490849</v>
+        <v>1543918.74817906</v>
       </c>
       <c r="D37" s="16" t="n">
         <f aca="false">MAX(0,-MIN('Расчёт 2 в месяц'!B49:Y49))</f>
-        <v>830758.013228435</v>
+        <v>636209.61141676</v>
       </c>
       <c r="E37" s="8" t="s">
         <v>54</v>
@@ -2681,15 +2681,15 @@
       </c>
       <c r="B21" s="7" t="n">
         <f aca="false">Допущения!$B$23/12</f>
-        <v>3750</v>
+        <v>4158.33333333333</v>
       </c>
       <c r="C21" s="7" t="n">
         <f aca="false">Допущения!$C$23/12</f>
-        <v>3750</v>
+        <v>4158.33333333333</v>
       </c>
       <c r="D21" s="7" t="n">
         <f aca="false">Допущения!$D$23/12</f>
-        <v>3750</v>
+        <v>4158.33333333333</v>
       </c>
       <c r="E21" s="8" t="s">
         <v>90</v>
@@ -2721,15 +2721,15 @@
       </c>
       <c r="B23" s="15" t="n">
         <f aca="false">$B$21+$B$22</f>
-        <v>3350</v>
+        <v>3758.33333333333</v>
       </c>
       <c r="C23" s="15" t="n">
         <f aca="false">$C$21+$C$22</f>
-        <v>3350</v>
+        <v>3758.33333333333</v>
       </c>
       <c r="D23" s="15" t="n">
         <f aca="false">$D$21+$D$22</f>
-        <v>3350</v>
+        <v>3758.33333333333</v>
       </c>
       <c r="E23" s="8"/>
     </row>
@@ -2739,15 +2739,15 @@
       </c>
       <c r="B24" s="25" t="n">
         <f aca="false">ROUND($B$23/$B$10,1)</f>
-        <v>3.7</v>
+        <v>4.1</v>
       </c>
       <c r="C24" s="25" t="n">
         <f aca="false">ROUND($C$23/$C$10,1)</f>
-        <v>3.7</v>
+        <v>4.1</v>
       </c>
       <c r="D24" s="25" t="n">
         <f aca="false">ROUND($D$23/$D$10,1)</f>
-        <v>3.7</v>
+        <v>4.1</v>
       </c>
       <c r="E24" s="8" t="s">
         <v>95</v>
@@ -2848,15 +2848,15 @@
       </c>
       <c r="B31" s="10" t="n">
         <f aca="false">ROUNDUP($B$27/$B$23,0)</f>
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="C31" s="10" t="n">
         <f aca="false">ROUNDUP($C$27/$C$23,0)</f>
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="D31" s="10" t="n">
         <f aca="false">ROUNDUP($D$27/$D$23,0)</f>
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="E31" s="8" t="s">
         <v>106</v>
@@ -2892,9 +2892,9 @@
         <f aca="false">IFERROR(MATCH(TRUE(),INDEX('Расчёт 1 в месяц'!$B$47:$Y$47&gt;0,0),0),"за 24 месяца не выходим")</f>
         <v>за 24 месяца не выходим</v>
       </c>
-      <c r="D33" s="13" t="str">
+      <c r="D33" s="13" t="n">
         <f aca="false">IFERROR(MATCH(TRUE(),INDEX('Расчёт 2 в месяц'!$B$47:$Y$47&gt;0,0),0),"за 24 месяца не выходим")</f>
-        <v>за 24 месяца не выходим</v>
+        <v>24</v>
       </c>
       <c r="E33" s="8" t="s">
         <v>108</v>
@@ -3281,13 +3281,13 @@
         <v>152</v>
       </c>
       <c r="B23" s="26" t="n">
-        <v>45000</v>
+        <v>49900</v>
       </c>
       <c r="C23" s="26" t="n">
-        <v>45000</v>
+        <v>49900</v>
       </c>
       <c r="D23" s="26" t="n">
-        <v>45000</v>
+        <v>49900</v>
       </c>
       <c r="E23" s="8" t="s">
         <v>153</v>
@@ -5005,87 +5005,87 @@
       </c>
       <c r="E15" s="7" t="n">
         <f aca="false">E13*Допущения!$B$23/12</f>
-        <v>1875</v>
+        <v>2079.16666666667</v>
       </c>
       <c r="F15" s="7" t="n">
         <f aca="false">F13*Допущения!$B$23/12</f>
-        <v>3718.75</v>
+        <v>4123.68055555556</v>
       </c>
       <c r="G15" s="7" t="n">
         <f aca="false">G13*Допущения!$B$23/12</f>
-        <v>5531.77083333333</v>
+        <v>6134.11921296296</v>
       </c>
       <c r="H15" s="7" t="n">
         <f aca="false">H13*Допущения!$B$23/12</f>
-        <v>7314.57465277778</v>
+        <v>8111.05055941358</v>
       </c>
       <c r="I15" s="7" t="n">
         <f aca="false">I13*Допущения!$B$23/12</f>
-        <v>9067.66507523148</v>
+        <v>10055.03305009</v>
       </c>
       <c r="J15" s="7" t="n">
         <f aca="false">J13*Допущения!$B$23/12</f>
-        <v>10791.5373239776</v>
+        <v>11966.6158325885</v>
       </c>
       <c r="K15" s="7" t="n">
         <f aca="false">K13*Допущения!$B$23/12</f>
-        <v>12486.678368578</v>
+        <v>13846.3389020454</v>
       </c>
       <c r="L15" s="7" t="n">
         <f aca="false">L13*Допущения!$B$23/12</f>
-        <v>14153.567062435</v>
+        <v>15694.733253678</v>
       </c>
       <c r="M15" s="7" t="n">
         <f aca="false">M13*Допущения!$B$23/12</f>
-        <v>15792.6742780611</v>
+        <v>17512.3210327833</v>
       </c>
       <c r="N15" s="7" t="n">
         <f aca="false">N13*Допущения!$B$23/12</f>
-        <v>17404.4630400934</v>
+        <v>19299.6156822369</v>
       </c>
       <c r="O15" s="7" t="n">
         <f aca="false">O13*Допущения!$B$23/12</f>
-        <v>18989.3886560919</v>
+        <v>21057.122087533</v>
       </c>
       <c r="P15" s="7" t="n">
         <f aca="false">P13*Допущения!$B$23/12</f>
-        <v>20547.898845157</v>
+        <v>22785.3367194074</v>
       </c>
       <c r="Q15" s="7" t="n">
         <f aca="false">Q13*Допущения!$B$23/12</f>
-        <v>22080.4338644044</v>
+        <v>24484.747774084</v>
       </c>
       <c r="R15" s="7" t="n">
         <f aca="false">R13*Допущения!$B$23/12</f>
-        <v>23587.426633331</v>
+        <v>26155.8353111826</v>
       </c>
       <c r="S15" s="7" t="n">
         <f aca="false">S13*Допущения!$B$23/12</f>
-        <v>25069.3028561088</v>
+        <v>27799.0713893295</v>
       </c>
       <c r="T15" s="7" t="n">
         <f aca="false">T13*Допущения!$B$23/12</f>
-        <v>26526.4811418403</v>
+        <v>29414.9201995074</v>
       </c>
       <c r="U15" s="7" t="n">
         <f aca="false">U13*Допущения!$B$23/12</f>
-        <v>27959.3731228096</v>
+        <v>31003.8381961822</v>
       </c>
       <c r="V15" s="7" t="n">
         <f aca="false">V13*Допущения!$B$23/12</f>
-        <v>29368.3835707628</v>
+        <v>32566.2742262459</v>
       </c>
       <c r="W15" s="7" t="n">
         <f aca="false">W13*Допущения!$B$23/12</f>
-        <v>30753.9105112501</v>
+        <v>34102.6696558084</v>
       </c>
       <c r="X15" s="7" t="n">
         <f aca="false">X13*Допущения!$B$23/12</f>
-        <v>32116.3453360626</v>
+        <v>35613.4584948783</v>
       </c>
       <c r="Y15" s="7" t="n">
         <f aca="false">Y13*Допущения!$B$23/12</f>
-        <v>33456.0729137949</v>
+        <v>37099.0675199637</v>
       </c>
       <c r="Z15" s="8" t="s">
         <v>275</v>
@@ -5213,87 +5213,87 @@
       </c>
       <c r="E17" s="15" t="n">
         <f aca="false">E16+E15</f>
-        <v>10360.8175875</v>
+        <v>10564.9842541667</v>
       </c>
       <c r="F17" s="15" t="n">
         <f aca="false">F16+F15</f>
-        <v>16295.0810143167</v>
+        <v>16700.0115698722</v>
       </c>
       <c r="G17" s="15" t="n">
         <f aca="false">G16+G15</f>
-        <v>21802.8103774351</v>
+        <v>22405.1587570648</v>
       </c>
       <c r="H17" s="15" t="n">
         <f aca="false">H16+H15</f>
-        <v>26929.9432882504</v>
+        <v>27726.4191948862</v>
       </c>
       <c r="I17" s="15" t="n">
         <f aca="false">I16+I15</f>
-        <v>31717.0099015089</v>
+        <v>32704.3778763675</v>
       </c>
       <c r="J17" s="15" t="n">
         <f aca="false">J16+J15</f>
-        <v>37177.7068583971</v>
+        <v>38352.785367008</v>
       </c>
       <c r="K17" s="15" t="n">
         <f aca="false">K16+K15</f>
-        <v>42273.1752532656</v>
+        <v>43632.835786733</v>
       </c>
       <c r="L17" s="15" t="n">
         <f aca="false">L16+L15</f>
-        <v>47041.7567466892</v>
+        <v>48582.9229379322</v>
       </c>
       <c r="M17" s="15" t="n">
         <f aca="false">M16+M15</f>
-        <v>52490.7677070218</v>
+        <v>54210.414461744</v>
       </c>
       <c r="N17" s="15" t="n">
         <f aca="false">N16+N15</f>
-        <v>57587.4265007828</v>
+        <v>59482.5791429263</v>
       </c>
       <c r="O17" s="15" t="n">
         <f aca="false">O16+O15</f>
-        <v>62368.23657976</v>
+        <v>64435.9700112011</v>
       </c>
       <c r="P17" s="15" t="n">
         <f aca="false">P16+P15</f>
-        <v>67834.4348956292</v>
+        <v>70071.8727698797</v>
       </c>
       <c r="Q17" s="15" t="n">
         <f aca="false">Q16+Q15</f>
-        <v>72959.551057691</v>
+        <v>75363.8649673706</v>
       </c>
       <c r="R17" s="15" t="n">
         <f aca="false">R16+R15</f>
-        <v>78744.2927404397</v>
+        <v>81312.7014182913</v>
       </c>
       <c r="S17" s="15" t="n">
         <f aca="false">S16+S15</f>
-        <v>84169.5105840721</v>
+        <v>86899.2791172928</v>
       </c>
       <c r="T17" s="15" t="n">
         <f aca="false">T16+T15</f>
-        <v>90234.6123423984</v>
+        <v>93123.0514000654</v>
       </c>
       <c r="U17" s="15" t="n">
         <f aca="false">U16+U15</f>
-        <v>96888.3430916414</v>
+        <v>99932.808165014</v>
       </c>
       <c r="V17" s="15" t="n">
         <f aca="false">V16+V15</f>
-        <v>103125.805201128</v>
+        <v>106323.695856611</v>
       </c>
       <c r="W17" s="15" t="n">
         <f aca="false">W16+W15</f>
-        <v>109947.419828033</v>
+        <v>113296.178972591</v>
       </c>
       <c r="X17" s="15" t="n">
         <f aca="false">X16+X15</f>
-        <v>117309.976516727</v>
+        <v>120807.089675543</v>
       </c>
       <c r="Y17" s="15" t="n">
         <f aca="false">Y16+Y15</f>
-        <v>125175.426688717</v>
+        <v>128818.421294886</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5418,87 +5418,87 @@
       </c>
       <c r="E19" s="7" t="n">
         <f aca="false">E16+E18-E9*Допущения!$B$10*3/24*Допущения!$B$9/12+E12*Допущения!$B$23</f>
-        <v>32233.6300875</v>
+        <v>34683.6300875</v>
       </c>
       <c r="F19" s="7" t="n">
         <f aca="false">F16+F18-F9*Допущения!$B$10*4/24*Допущения!$B$9/12+F12*Допущения!$B$23</f>
-        <v>36740.0810143167</v>
+        <v>39190.0810143167</v>
       </c>
       <c r="G19" s="7" t="n">
         <f aca="false">G16+G18-G9*Допущения!$B$10*5/24*Допущения!$B$9/12+G12*Допущения!$B$23</f>
-        <v>40850.7270441018</v>
+        <v>43300.7270441018</v>
       </c>
       <c r="H19" s="7" t="n">
         <f aca="false">H16+H18-H9*Допущения!$B$10*6/24*Допущения!$B$9/12+H12*Допущения!$B$23</f>
-        <v>44610.9936354726</v>
+        <v>47060.9936354726</v>
       </c>
       <c r="I19" s="7" t="n">
         <f aca="false">I16+I18-I9*Допущения!$B$10*7/24*Допущения!$B$9/12+I12*Допущения!$B$23</f>
-        <v>48060.9073262775</v>
+        <v>50510.9073262775</v>
       </c>
       <c r="J19" s="7" t="n">
         <f aca="false">J16+J18-J9*Допущения!$B$10*8/24*Допущения!$B$9/12+J12*Допущения!$B$23</f>
-        <v>52879.1695344194</v>
+        <v>55329.1695344194</v>
       </c>
       <c r="K19" s="7" t="n">
         <f aca="false">K16+K18-K9*Допущения!$B$10*9/24*Допущения!$B$9/12+K12*Допущения!$B$23</f>
-        <v>56778.6218846876</v>
+        <v>59228.6218846876</v>
       </c>
       <c r="L19" s="7" t="n">
         <f aca="false">L16+L18-L9*Допущения!$B$10*10/24*Допущения!$B$9/12+L12*Допущения!$B$23</f>
-        <v>60379.4396842542</v>
+        <v>62829.4396842542</v>
       </c>
       <c r="M19" s="7" t="n">
         <f aca="false">M16+M18-M9*Допущения!$B$10*11/24*Допущения!$B$9/12+M12*Допущения!$B$23</f>
-        <v>65603.5309289607</v>
+        <v>68053.5309289607</v>
       </c>
       <c r="N19" s="7" t="n">
         <f aca="false">N16+N18-N9*Допущения!$B$10*12/24*Допущения!$B$9/12+N12*Допущения!$B$23</f>
-        <v>69670.7134606893</v>
+        <v>72120.7134606893</v>
       </c>
       <c r="O19" s="7" t="n">
         <f aca="false">O16+O18-O9*Допущения!$B$10*13/24*Допущения!$B$9/12+O12*Допущения!$B$23</f>
-        <v>73448.9104236681</v>
+        <v>75898.9104236681</v>
       </c>
       <c r="P19" s="7" t="n">
         <f aca="false">P16+P18-P9*Допущения!$B$10*14/24*Допущения!$B$9/12+P12*Допущения!$B$23</f>
-        <v>79103.5360504722</v>
+        <v>81553.5360504722</v>
       </c>
       <c r="Q19" s="7" t="n">
         <f aca="false">Q16+Q18-Q9*Допущения!$B$10*15/24*Допущения!$B$9/12+Q12*Допущения!$B$23</f>
-        <v>83361.6171932866</v>
+        <v>85811.6171932866</v>
       </c>
       <c r="R19" s="7" t="n">
         <f aca="false">R16+R18-R9*Допущения!$B$10*16/24*Допущения!$B$9/12+R12*Допущения!$B$23</f>
-        <v>89635.8661071087</v>
+        <v>92085.8661071087</v>
       </c>
       <c r="S19" s="7" t="n">
         <f aca="false">S16+S18-S9*Допущения!$B$10*17/24*Допущения!$B$9/12+S12*Допущения!$B$23</f>
-        <v>94327.8952279633</v>
+        <v>96777.8952279633</v>
       </c>
       <c r="T19" s="7" t="n">
         <f aca="false">T16+T18-T9*Допущения!$B$10*18/24*Допущения!$B$9/12+T12*Допущения!$B$23</f>
-        <v>101181.881200558</v>
+        <v>103631.881200558</v>
       </c>
       <c r="U19" s="7" t="n">
         <f aca="false">U16+U18-U9*Допущения!$B$10*19/24*Допущения!$B$9/12+U12*Допущения!$B$23</f>
-        <v>108815.157468832</v>
+        <v>111265.157468832</v>
       </c>
       <c r="V19" s="7" t="n">
         <f aca="false">V16+V18-V9*Допущения!$B$10*20/24*Допущения!$B$9/12+V12*Допущения!$B$23</f>
-        <v>114558.671630365</v>
+        <v>117008.671630365</v>
       </c>
       <c r="W19" s="7" t="n">
         <f aca="false">W16+W18-W9*Допущения!$B$10*21/24*Допущения!$B$9/12+W12*Допущения!$B$23</f>
-        <v>122656.759316783</v>
+        <v>125106.759316783</v>
       </c>
       <c r="X19" s="7" t="n">
         <f aca="false">X16+X18-X9*Допущения!$B$10*22/24*Допущения!$B$9/12+X12*Допущения!$B$23</f>
-        <v>131485.256180665</v>
+        <v>133935.256180665</v>
       </c>
       <c r="Y19" s="7" t="n">
         <f aca="false">Y16+Y18-Y9*Допущения!$B$10*23/24*Допущения!$B$9/12+Y12*Допущения!$B$23</f>
-        <v>141005.728774922</v>
+        <v>143455.728774922</v>
       </c>
       <c r="Z19" s="8" t="s">
         <v>282</v>
@@ -6671,87 +6671,87 @@
       </c>
       <c r="E32" s="7" t="n">
         <f aca="false">E19*Допущения!$B$58</f>
-        <v>967.008902625</v>
+        <v>1040.508902625</v>
       </c>
       <c r="F32" s="7" t="n">
         <f aca="false">F19*Допущения!$B$58</f>
-        <v>1102.2024304295</v>
+        <v>1175.7024304295</v>
       </c>
       <c r="G32" s="7" t="n">
         <f aca="false">G19*Допущения!$B$58</f>
-        <v>1225.52181132305</v>
+        <v>1299.02181132305</v>
       </c>
       <c r="H32" s="7" t="n">
         <f aca="false">H19*Допущения!$B$58</f>
-        <v>1338.32980906418</v>
+        <v>1411.82980906418</v>
       </c>
       <c r="I32" s="7" t="n">
         <f aca="false">I19*Допущения!$B$58</f>
-        <v>1441.82721978832</v>
+        <v>1515.32721978832</v>
       </c>
       <c r="J32" s="7" t="n">
         <f aca="false">J19*Допущения!$B$58</f>
-        <v>1586.37508603258</v>
+        <v>1659.87508603258</v>
       </c>
       <c r="K32" s="7" t="n">
         <f aca="false">K19*Допущения!$B$58</f>
-        <v>1703.35865654063</v>
+        <v>1776.85865654063</v>
       </c>
       <c r="L32" s="7" t="n">
         <f aca="false">L19*Допущения!$B$58</f>
-        <v>1811.38319052763</v>
+        <v>1884.88319052763</v>
       </c>
       <c r="M32" s="7" t="n">
         <f aca="false">M19*Допущения!$B$58</f>
-        <v>1968.10592786882</v>
+        <v>2041.60592786882</v>
       </c>
       <c r="N32" s="7" t="n">
         <f aca="false">N19*Допущения!$B$58</f>
-        <v>2090.12140382068</v>
+        <v>2163.62140382068</v>
       </c>
       <c r="O32" s="7" t="n">
         <f aca="false">O19*Допущения!$B$58</f>
-        <v>2203.46731271004</v>
+        <v>2276.96731271004</v>
       </c>
       <c r="P32" s="7" t="n">
         <f aca="false">P19*Допущения!$B$58</f>
-        <v>2373.10608151417</v>
+        <v>2446.60608151417</v>
       </c>
       <c r="Q32" s="7" t="n">
         <f aca="false">Q19*Допущения!$B$58</f>
-        <v>2500.8485157986</v>
+        <v>2574.3485157986</v>
       </c>
       <c r="R32" s="7" t="n">
         <f aca="false">R19*Допущения!$B$58</f>
-        <v>2689.07598321326</v>
+        <v>2762.57598321326</v>
       </c>
       <c r="S32" s="7" t="n">
         <f aca="false">S19*Допущения!$B$58</f>
-        <v>2829.8368568389</v>
+        <v>2903.3368568389</v>
       </c>
       <c r="T32" s="7" t="n">
         <f aca="false">T19*Допущения!$B$58</f>
-        <v>3035.45643601674</v>
+        <v>3108.95643601674</v>
       </c>
       <c r="U32" s="7" t="n">
         <f aca="false">U19*Допущения!$B$58</f>
-        <v>3264.45472406495</v>
+        <v>3337.95472406495</v>
       </c>
       <c r="V32" s="7" t="n">
         <f aca="false">V19*Допущения!$B$58</f>
-        <v>3436.76014891094</v>
+        <v>3510.26014891094</v>
       </c>
       <c r="W32" s="7" t="n">
         <f aca="false">W19*Допущения!$B$58</f>
-        <v>3679.70277950348</v>
+        <v>3753.20277950348</v>
       </c>
       <c r="X32" s="7" t="n">
         <f aca="false">X19*Допущения!$B$58</f>
-        <v>3944.55768541994</v>
+        <v>4018.05768541994</v>
       </c>
       <c r="Y32" s="7" t="n">
         <f aca="false">Y19*Допущения!$B$58</f>
-        <v>4230.17186324766</v>
+        <v>4303.67186324766</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7286,87 +7286,87 @@
       </c>
       <c r="E38" s="15" t="n">
         <f aca="false">SUM(E21:E37)</f>
-        <v>151258.955485958</v>
+        <v>151332.455485958</v>
       </c>
       <c r="F38" s="15" t="n">
         <f aca="false">SUM(F21:F37)</f>
-        <v>151652.20511443</v>
+        <v>151725.70511443</v>
       </c>
       <c r="G38" s="15" t="n">
         <f aca="false">SUM(G21:G37)</f>
-        <v>152025.622346864</v>
+        <v>152099.122346864</v>
       </c>
       <c r="H38" s="15" t="n">
         <f aca="false">SUM(H21:H37)</f>
-        <v>152381.158631612</v>
+        <v>152454.658631612</v>
       </c>
       <c r="I38" s="15" t="n">
         <f aca="false">SUM(I21:I37)</f>
-        <v>152720.539688969</v>
+        <v>152794.039688969</v>
       </c>
       <c r="J38" s="15" t="n">
         <f aca="false">SUM(J21:J37)</f>
-        <v>153124.745522668</v>
+        <v>153198.245522668</v>
       </c>
       <c r="K38" s="15" t="n">
         <f aca="false">SUM(K21:K37)</f>
-        <v>153478.448924816</v>
+        <v>153551.948924816</v>
       </c>
       <c r="L38" s="15" t="n">
         <f aca="false">SUM(L21:L37)</f>
-        <v>153816.634964278</v>
+        <v>153890.134964278</v>
       </c>
       <c r="M38" s="15" t="n">
         <f aca="false">SUM(M21:M37)</f>
-        <v>154234.363624583</v>
+        <v>154307.863624583</v>
       </c>
       <c r="N38" s="15" t="n">
         <f aca="false">SUM(N21:N37)</f>
-        <v>204587.918331707</v>
+        <v>204661.418331707</v>
       </c>
       <c r="O38" s="15" t="n">
         <f aca="false">SUM(O21:O37)</f>
-        <v>204926.500572841</v>
+        <v>205000.000572841</v>
       </c>
       <c r="P38" s="15" t="n">
         <f aca="false">SUM(P21:P37)</f>
-        <v>205359.262845511</v>
+        <v>205432.762845511</v>
       </c>
       <c r="Q38" s="15" t="n">
         <f aca="false">SUM(Q21:Q37)</f>
-        <v>205714.109267829</v>
+        <v>205787.609267829</v>
       </c>
       <c r="R38" s="15" t="n">
         <f aca="false">SUM(R21:R37)</f>
-        <v>206171.671839998</v>
+        <v>206245.171839998</v>
       </c>
       <c r="S38" s="15" t="n">
         <f aca="false">SUM(S21:S37)</f>
-        <v>206541.065801239</v>
+        <v>206614.565801239</v>
       </c>
       <c r="T38" s="15" t="n">
         <f aca="false">SUM(T21:T37)</f>
-        <v>207021.962412101</v>
+        <v>207095.462412101</v>
       </c>
       <c r="U38" s="15" t="n">
         <f aca="false">SUM(U21:U37)</f>
-        <v>207536.020443613</v>
+        <v>207609.520443613</v>
       </c>
       <c r="V38" s="15" t="n">
         <f aca="false">SUM(V21:V37)</f>
-        <v>207945.30399182</v>
+        <v>208018.80399182</v>
       </c>
       <c r="W38" s="15" t="n">
         <f aca="false">SUM(W21:W37)</f>
-        <v>208478.167872489</v>
+        <v>208551.667872489</v>
       </c>
       <c r="X38" s="15" t="n">
         <f aca="false">SUM(X21:X37)</f>
-        <v>209042.312778582</v>
+        <v>209115.812778582</v>
       </c>
       <c r="Y38" s="15" t="n">
         <f aca="false">SUM(Y21:Y37)</f>
-        <v>209636.178583687</v>
+        <v>209709.678583687</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7416,87 +7416,87 @@
       </c>
       <c r="E40" s="7" t="n">
         <f aca="false">SUM($E$17:E17)</f>
-        <v>10360.8175875</v>
+        <v>10564.9842541667</v>
       </c>
       <c r="F40" s="7" t="n">
         <f aca="false">SUM($E$17:F17)</f>
-        <v>26655.8986018167</v>
+        <v>27264.9958240389</v>
       </c>
       <c r="G40" s="7" t="n">
         <f aca="false">SUM($E$17:G17)</f>
-        <v>48458.7089792518</v>
+        <v>49670.1545811037</v>
       </c>
       <c r="H40" s="7" t="n">
         <f aca="false">SUM($E$17:H17)</f>
-        <v>75388.6522675022</v>
+        <v>77396.5737759899</v>
       </c>
       <c r="I40" s="7" t="n">
         <f aca="false">SUM($E$17:I17)</f>
-        <v>107105.662169011</v>
+        <v>110100.951652357</v>
       </c>
       <c r="J40" s="7" t="n">
         <f aca="false">SUM($E$17:J17)</f>
-        <v>144283.369027408</v>
+        <v>148453.737019365</v>
       </c>
       <c r="K40" s="7" t="n">
         <f aca="false">SUM($E$17:K17)</f>
-        <v>186556.544280674</v>
+        <v>192086.572806098</v>
       </c>
       <c r="L40" s="7" t="n">
         <f aca="false">SUM($E$17:L17)</f>
-        <v>233598.301027363</v>
+        <v>240669.49574403</v>
       </c>
       <c r="M40" s="7" t="n">
         <f aca="false">SUM($E$17:M17)</f>
-        <v>286089.068734385</v>
+        <v>294879.910205775</v>
       </c>
       <c r="N40" s="7" t="n">
         <f aca="false">SUM($E$17:N17)</f>
-        <v>343676.495235168</v>
+        <v>354362.489348701</v>
       </c>
       <c r="O40" s="7" t="n">
         <f aca="false">SUM($E$17:O17)</f>
-        <v>406044.731814928</v>
+        <v>418798.459359902</v>
       </c>
       <c r="P40" s="7" t="n">
         <f aca="false">SUM($E$17:P17)</f>
-        <v>473879.166710557</v>
+        <v>488870.332129782</v>
       </c>
       <c r="Q40" s="7" t="n">
         <f aca="false">SUM($E$17:Q17)</f>
-        <v>546838.717768248</v>
+        <v>564234.197097152</v>
       </c>
       <c r="R40" s="7" t="n">
         <f aca="false">SUM($E$17:R17)</f>
-        <v>625583.010508688</v>
+        <v>645546.898515443</v>
       </c>
       <c r="S40" s="7" t="n">
         <f aca="false">SUM($E$17:S17)</f>
-        <v>709752.52109276</v>
+        <v>732446.177632736</v>
       </c>
       <c r="T40" s="7" t="n">
         <f aca="false">SUM($E$17:T17)</f>
-        <v>799987.133435158</v>
+        <v>825569.229032802</v>
       </c>
       <c r="U40" s="7" t="n">
         <f aca="false">SUM($E$17:U17)</f>
-        <v>896875.476526799</v>
+        <v>925502.037197816</v>
       </c>
       <c r="V40" s="7" t="n">
         <f aca="false">SUM($E$17:V17)</f>
-        <v>1000001.28172793</v>
+        <v>1031825.73305443</v>
       </c>
       <c r="W40" s="7" t="n">
         <f aca="false">SUM($E$17:W17)</f>
-        <v>1109948.70155596</v>
+        <v>1145121.91202702</v>
       </c>
       <c r="X40" s="7" t="n">
         <f aca="false">SUM($E$17:X17)</f>
-        <v>1227258.67807269</v>
+        <v>1265929.00170256</v>
       </c>
       <c r="Y40" s="7" t="n">
         <f aca="false">SUM($E$17:Y17)</f>
-        <v>1352434.1047614</v>
+        <v>1394747.42299745</v>
       </c>
       <c r="Z40" s="8" t="s">
         <v>303</v>
@@ -7624,87 +7624,87 @@
       </c>
       <c r="E42" s="7" t="n">
         <f aca="false">E17-E38-E41</f>
-        <v>-140898.137898458</v>
+        <v>-140767.471231792</v>
       </c>
       <c r="F42" s="7" t="n">
         <f aca="false">F17-F38-F41</f>
-        <v>-135357.124100113</v>
+        <v>-135025.693544557</v>
       </c>
       <c r="G42" s="7" t="n">
         <f aca="false">G17-G38-G41</f>
-        <v>-130222.811969428</v>
+        <v>-129693.963589799</v>
       </c>
       <c r="H42" s="7" t="n">
         <f aca="false">H17-H38-H41</f>
-        <v>-125451.215343361</v>
+        <v>-124728.239436726</v>
       </c>
       <c r="I42" s="7" t="n">
         <f aca="false">I17-I38-I41</f>
-        <v>-121003.52978746</v>
+        <v>-120089.661812601</v>
       </c>
       <c r="J42" s="7" t="n">
         <f aca="false">J17-J38-J41</f>
-        <v>-115947.038664271</v>
+        <v>-114845.46015566</v>
       </c>
       <c r="K42" s="7" t="n">
         <f aca="false">K17-K38-K41</f>
-        <v>-111205.27367155</v>
+        <v>-109919.113138083</v>
       </c>
       <c r="L42" s="7" t="n">
         <f aca="false">L17-L38-L41</f>
-        <v>-106774.878217589</v>
+        <v>-105307.212026346</v>
       </c>
       <c r="M42" s="7" t="n">
         <f aca="false">M17-M38-M41</f>
-        <v>-101743.595917561</v>
+        <v>-100097.449162839</v>
       </c>
       <c r="N42" s="7" t="n">
         <f aca="false">N17-N38-N41</f>
-        <v>-147000.491830924</v>
+        <v>-145178.839188781</v>
       </c>
       <c r="O42" s="7" t="n">
         <f aca="false">O17-O38-O41</f>
-        <v>-142558.263993081</v>
+        <v>-140564.03056164</v>
       </c>
       <c r="P42" s="7" t="n">
         <f aca="false">P17-P38-P41</f>
-        <v>-137524.827949882</v>
+        <v>-135360.890075631</v>
       </c>
       <c r="Q42" s="7" t="n">
         <f aca="false">Q17-Q38-Q41</f>
-        <v>-132754.558210138</v>
+        <v>-130423.744300459</v>
       </c>
       <c r="R42" s="7" t="n">
         <f aca="false">R17-R38-R41</f>
-        <v>-127427.379099558</v>
+        <v>-124932.470421706</v>
       </c>
       <c r="S42" s="7" t="n">
         <f aca="false">S17-S38-S41</f>
-        <v>-122371.555217167</v>
+        <v>-119715.286683946</v>
       </c>
       <c r="T42" s="7" t="n">
         <f aca="false">T17-T38-T41</f>
-        <v>-116787.350069702</v>
+        <v>-113972.411012035</v>
       </c>
       <c r="U42" s="7" t="n">
         <f aca="false">U17-U38-U41</f>
-        <v>-110647.677351972</v>
+        <v>-107676.712278599</v>
       </c>
       <c r="V42" s="7" t="n">
         <f aca="false">V17-V38-V41</f>
-        <v>-104819.498790692</v>
+        <v>-101695.108135209</v>
       </c>
       <c r="W42" s="7" t="n">
         <f aca="false">W17-W38-W41</f>
-        <v>-98530.7480444562</v>
+        <v>-95255.4888998978</v>
       </c>
       <c r="X42" s="7" t="n">
         <f aca="false">X17-X38-X41</f>
-        <v>-91732.3362618552</v>
+        <v>-88308.7231030395</v>
       </c>
       <c r="Y42" s="7" t="n">
         <f aca="false">Y17-Y38-Y41</f>
-        <v>-84460.7518949698</v>
+        <v>-80891.2572888011</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7725,87 +7725,87 @@
       </c>
       <c r="E43" s="7" t="n">
         <f aca="false">MAX(E42*Допущения!$B$51,E17*Допущения!$B$52)</f>
-        <v>310.824527625</v>
+        <v>316.949527625</v>
       </c>
       <c r="F43" s="7" t="n">
         <f aca="false">MAX(F42*Допущения!$B$51,F17*Допущения!$B$52)</f>
-        <v>488.8524304295</v>
+        <v>501.000347096167</v>
       </c>
       <c r="G43" s="7" t="n">
         <f aca="false">MAX(G42*Допущения!$B$51,G17*Допущения!$B$52)</f>
-        <v>654.084311323054</v>
+        <v>672.154762711943</v>
       </c>
       <c r="H43" s="7" t="n">
         <f aca="false">MAX(H42*Допущения!$B$51,H17*Допущения!$B$52)</f>
-        <v>807.898298647513</v>
+        <v>831.792575846587</v>
       </c>
       <c r="I43" s="7" t="n">
         <f aca="false">MAX(I42*Допущения!$B$51,I17*Допущения!$B$52)</f>
-        <v>951.510297045268</v>
+        <v>981.131336291024</v>
       </c>
       <c r="J43" s="7" t="n">
         <f aca="false">MAX(J42*Допущения!$B$51,J17*Допущения!$B$52)</f>
-        <v>1115.33120575191</v>
+        <v>1150.58356101024</v>
       </c>
       <c r="K43" s="7" t="n">
         <f aca="false">MAX(K42*Допущения!$B$51,K17*Допущения!$B$52)</f>
-        <v>1268.19525759797</v>
+        <v>1308.98507360199</v>
       </c>
       <c r="L43" s="7" t="n">
         <f aca="false">MAX(L42*Допущения!$B$51,L17*Допущения!$B$52)</f>
-        <v>1411.25270240068</v>
+        <v>1457.48768813796</v>
       </c>
       <c r="M43" s="7" t="n">
         <f aca="false">MAX(M42*Допущения!$B$51,M17*Допущения!$B$52)</f>
-        <v>1574.72303121065</v>
+        <v>1626.31243385232</v>
       </c>
       <c r="N43" s="7" t="n">
         <f aca="false">MAX(N42*Допущения!$B$51,N17*Допущения!$B$52)</f>
-        <v>1727.62279502348</v>
+        <v>1784.47737428779</v>
       </c>
       <c r="O43" s="7" t="n">
         <f aca="false">MAX(O42*Допущения!$B$51,O17*Допущения!$B$52)</f>
-        <v>1871.0470973928</v>
+        <v>1933.07910033603</v>
       </c>
       <c r="P43" s="7" t="n">
         <f aca="false">MAX(P42*Допущения!$B$51,P17*Допущения!$B$52)</f>
-        <v>2035.03304686888</v>
+        <v>2102.15618309639</v>
       </c>
       <c r="Q43" s="7" t="n">
         <f aca="false">MAX(Q42*Допущения!$B$51,Q17*Допущения!$B$52)</f>
-        <v>2188.78653173073</v>
+        <v>2260.91594902112</v>
       </c>
       <c r="R43" s="7" t="n">
         <f aca="false">MAX(R42*Допущения!$B$51,R17*Допущения!$B$52)</f>
-        <v>2362.32878221319</v>
+        <v>2439.38104254874</v>
       </c>
       <c r="S43" s="7" t="n">
         <f aca="false">MAX(S42*Допущения!$B$51,S17*Допущения!$B$52)</f>
-        <v>2525.08531752216</v>
+        <v>2606.97837351878</v>
       </c>
       <c r="T43" s="7" t="n">
         <f aca="false">MAX(T42*Допущения!$B$51,T17*Допущения!$B$52)</f>
-        <v>2707.03837027195</v>
+        <v>2793.69154200196</v>
       </c>
       <c r="U43" s="7" t="n">
         <f aca="false">MAX(U42*Допущения!$B$51,U17*Допущения!$B$52)</f>
-        <v>2906.65029274924</v>
+        <v>2997.98424495042</v>
       </c>
       <c r="V43" s="7" t="n">
         <f aca="false">MAX(V42*Допущения!$B$51,V17*Допущения!$B$52)</f>
-        <v>3093.77415603383</v>
+        <v>3189.71087569832</v>
       </c>
       <c r="W43" s="7" t="n">
         <f aca="false">MAX(W42*Допущения!$B$51,W17*Допущения!$B$52)</f>
-        <v>3298.42259484099</v>
+        <v>3398.88536917774</v>
       </c>
       <c r="X43" s="7" t="n">
         <f aca="false">MAX(X42*Допущения!$B$51,X17*Допущения!$B$52)</f>
-        <v>3519.29929550182</v>
+        <v>3624.21269026629</v>
       </c>
       <c r="Y43" s="7" t="n">
         <f aca="false">MAX(Y42*Допущения!$B$51,Y17*Допущения!$B$52)</f>
-        <v>3755.26280066151</v>
+        <v>3864.55263884657</v>
       </c>
       <c r="Z43" s="8" t="s">
         <v>308</v>
@@ -7829,87 +7829,87 @@
       </c>
       <c r="E44" s="15" t="n">
         <f aca="false">E41+E43</f>
-        <v>310.824527625</v>
+        <v>316.949527625</v>
       </c>
       <c r="F44" s="15" t="n">
         <f aca="false">F41+F43</f>
-        <v>488.8524304295</v>
+        <v>501.000347096167</v>
       </c>
       <c r="G44" s="15" t="n">
         <f aca="false">G41+G43</f>
-        <v>654.084311323054</v>
+        <v>672.154762711943</v>
       </c>
       <c r="H44" s="15" t="n">
         <f aca="false">H41+H43</f>
-        <v>807.898298647513</v>
+        <v>831.792575846587</v>
       </c>
       <c r="I44" s="15" t="n">
         <f aca="false">I41+I43</f>
-        <v>951.510297045268</v>
+        <v>981.131336291024</v>
       </c>
       <c r="J44" s="15" t="n">
         <f aca="false">J41+J43</f>
-        <v>1115.33120575191</v>
+        <v>1150.58356101024</v>
       </c>
       <c r="K44" s="15" t="n">
         <f aca="false">K41+K43</f>
-        <v>1268.19525759797</v>
+        <v>1308.98507360199</v>
       </c>
       <c r="L44" s="15" t="n">
         <f aca="false">L41+L43</f>
-        <v>1411.25270240068</v>
+        <v>1457.48768813796</v>
       </c>
       <c r="M44" s="15" t="n">
         <f aca="false">M41+M43</f>
-        <v>1574.72303121065</v>
+        <v>1626.31243385232</v>
       </c>
       <c r="N44" s="15" t="n">
         <f aca="false">N41+N43</f>
-        <v>1727.62279502348</v>
+        <v>1784.47737428779</v>
       </c>
       <c r="O44" s="15" t="n">
         <f aca="false">O41+O43</f>
-        <v>1871.0470973928</v>
+        <v>1933.07910033603</v>
       </c>
       <c r="P44" s="15" t="n">
         <f aca="false">P41+P43</f>
-        <v>2035.03304686888</v>
+        <v>2102.15618309639</v>
       </c>
       <c r="Q44" s="15" t="n">
         <f aca="false">Q41+Q43</f>
-        <v>2188.78653173073</v>
+        <v>2260.91594902112</v>
       </c>
       <c r="R44" s="15" t="n">
         <f aca="false">R41+R43</f>
-        <v>2362.32878221319</v>
+        <v>2439.38104254874</v>
       </c>
       <c r="S44" s="15" t="n">
         <f aca="false">S41+S43</f>
-        <v>2525.08531752216</v>
+        <v>2606.97837351878</v>
       </c>
       <c r="T44" s="15" t="n">
         <f aca="false">T41+T43</f>
-        <v>2707.03837027195</v>
+        <v>2793.69154200196</v>
       </c>
       <c r="U44" s="15" t="n">
         <f aca="false">U41+U43</f>
-        <v>2906.65029274924</v>
+        <v>2997.98424495042</v>
       </c>
       <c r="V44" s="15" t="n">
         <f aca="false">V41+V43</f>
-        <v>3093.77415603383</v>
+        <v>3189.71087569832</v>
       </c>
       <c r="W44" s="15" t="n">
         <f aca="false">W41+W43</f>
-        <v>3298.42259484099</v>
+        <v>3398.88536917774</v>
       </c>
       <c r="X44" s="15" t="n">
         <f aca="false">X41+X43</f>
-        <v>3519.29929550182</v>
+        <v>3624.21269026629</v>
       </c>
       <c r="Y44" s="15" t="n">
         <f aca="false">Y41+Y43</f>
-        <v>3755.26280066151</v>
+        <v>3864.55263884657</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7959,87 +7959,87 @@
       </c>
       <c r="E46" s="15" t="n">
         <f aca="false">E17-E38</f>
-        <v>-140898.137898458</v>
+        <v>-140767.471231792</v>
       </c>
       <c r="F46" s="15" t="n">
         <f aca="false">F17-F38</f>
-        <v>-135357.124100113</v>
+        <v>-135025.693544557</v>
       </c>
       <c r="G46" s="15" t="n">
         <f aca="false">G17-G38</f>
-        <v>-130222.811969428</v>
+        <v>-129693.963589799</v>
       </c>
       <c r="H46" s="15" t="n">
         <f aca="false">H17-H38</f>
-        <v>-125451.215343361</v>
+        <v>-124728.239436726</v>
       </c>
       <c r="I46" s="15" t="n">
         <f aca="false">I17-I38</f>
-        <v>-121003.52978746</v>
+        <v>-120089.661812601</v>
       </c>
       <c r="J46" s="15" t="n">
         <f aca="false">J17-J38</f>
-        <v>-115947.038664271</v>
+        <v>-114845.46015566</v>
       </c>
       <c r="K46" s="15" t="n">
         <f aca="false">K17-K38</f>
-        <v>-111205.27367155</v>
+        <v>-109919.113138083</v>
       </c>
       <c r="L46" s="15" t="n">
         <f aca="false">L17-L38</f>
-        <v>-106774.878217589</v>
+        <v>-105307.212026346</v>
       </c>
       <c r="M46" s="15" t="n">
         <f aca="false">M17-M38</f>
-        <v>-101743.595917561</v>
+        <v>-100097.449162839</v>
       </c>
       <c r="N46" s="15" t="n">
         <f aca="false">N17-N38</f>
-        <v>-147000.491830924</v>
+        <v>-145178.839188781</v>
       </c>
       <c r="O46" s="15" t="n">
         <f aca="false">O17-O38</f>
-        <v>-142558.263993081</v>
+        <v>-140564.03056164</v>
       </c>
       <c r="P46" s="15" t="n">
         <f aca="false">P17-P38</f>
-        <v>-137524.827949882</v>
+        <v>-135360.890075631</v>
       </c>
       <c r="Q46" s="15" t="n">
         <f aca="false">Q17-Q38</f>
-        <v>-132754.558210138</v>
+        <v>-130423.744300459</v>
       </c>
       <c r="R46" s="15" t="n">
         <f aca="false">R17-R38</f>
-        <v>-127427.379099558</v>
+        <v>-124932.470421706</v>
       </c>
       <c r="S46" s="15" t="n">
         <f aca="false">S17-S38</f>
-        <v>-122371.555217167</v>
+        <v>-119715.286683946</v>
       </c>
       <c r="T46" s="15" t="n">
         <f aca="false">T17-T38</f>
-        <v>-116787.350069702</v>
+        <v>-113972.411012035</v>
       </c>
       <c r="U46" s="15" t="n">
         <f aca="false">U17-U38</f>
-        <v>-110647.677351972</v>
+        <v>-107676.712278599</v>
       </c>
       <c r="V46" s="15" t="n">
         <f aca="false">V17-V38</f>
-        <v>-104819.498790692</v>
+        <v>-101695.108135209</v>
       </c>
       <c r="W46" s="15" t="n">
         <f aca="false">W17-W38</f>
-        <v>-98530.7480444562</v>
+        <v>-95255.4888998978</v>
       </c>
       <c r="X46" s="15" t="n">
         <f aca="false">X17-X38</f>
-        <v>-91732.3362618552</v>
+        <v>-88308.7231030395</v>
       </c>
       <c r="Y46" s="15" t="n">
         <f aca="false">Y17-Y38</f>
-        <v>-84460.7518949698</v>
+        <v>-80891.2572888011</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8060,87 +8060,87 @@
       </c>
       <c r="E47" s="15" t="n">
         <f aca="false">E46-E44</f>
-        <v>-141208.962426083</v>
+        <v>-141084.420759417</v>
       </c>
       <c r="F47" s="15" t="n">
         <f aca="false">F46-F44</f>
-        <v>-135845.976530542</v>
+        <v>-135526.693891653</v>
       </c>
       <c r="G47" s="15" t="n">
         <f aca="false">G46-G44</f>
-        <v>-130876.896280752</v>
+        <v>-130366.118352511</v>
       </c>
       <c r="H47" s="15" t="n">
         <f aca="false">H46-H44</f>
-        <v>-126259.113642009</v>
+        <v>-125560.032012572</v>
       </c>
       <c r="I47" s="15" t="n">
         <f aca="false">I46-I44</f>
-        <v>-121955.040084505</v>
+        <v>-121070.793148892</v>
       </c>
       <c r="J47" s="15" t="n">
         <f aca="false">J46-J44</f>
-        <v>-117062.369870023</v>
+        <v>-115996.04371667</v>
       </c>
       <c r="K47" s="15" t="n">
         <f aca="false">K46-K44</f>
-        <v>-112473.468929148</v>
+        <v>-111228.098211685</v>
       </c>
       <c r="L47" s="15" t="n">
         <f aca="false">L46-L44</f>
-        <v>-108186.13091999</v>
+        <v>-106764.699714484</v>
       </c>
       <c r="M47" s="15" t="n">
         <f aca="false">M46-M44</f>
-        <v>-103318.318948772</v>
+        <v>-101723.761596691</v>
       </c>
       <c r="N47" s="15" t="n">
         <f aca="false">N46-N44</f>
-        <v>-148728.114625948</v>
+        <v>-146963.316563069</v>
       </c>
       <c r="O47" s="15" t="n">
         <f aca="false">O46-O44</f>
-        <v>-144429.311090474</v>
+        <v>-142497.109661976</v>
       </c>
       <c r="P47" s="15" t="n">
         <f aca="false">P46-P44</f>
-        <v>-139559.860996751</v>
+        <v>-137463.046258728</v>
       </c>
       <c r="Q47" s="15" t="n">
         <f aca="false">Q46-Q44</f>
-        <v>-134943.344741869</v>
+        <v>-132684.66024948</v>
       </c>
       <c r="R47" s="15" t="n">
         <f aca="false">R46-R44</f>
-        <v>-129789.707881771</v>
+        <v>-127371.851464255</v>
       </c>
       <c r="S47" s="15" t="n">
         <f aca="false">S46-S44</f>
-        <v>-124896.640534689</v>
+        <v>-122322.265057465</v>
       </c>
       <c r="T47" s="15" t="n">
         <f aca="false">T46-T44</f>
-        <v>-119494.388439974</v>
+        <v>-116766.102554037</v>
       </c>
       <c r="U47" s="15" t="n">
         <f aca="false">U46-U44</f>
-        <v>-113554.327644721</v>
+        <v>-110674.69652355</v>
       </c>
       <c r="V47" s="15" t="n">
         <f aca="false">V46-V44</f>
-        <v>-107913.272946726</v>
+        <v>-104884.819010908</v>
       </c>
       <c r="W47" s="15" t="n">
         <f aca="false">W46-W44</f>
-        <v>-101829.170639297</v>
+        <v>-98654.3742690756</v>
       </c>
       <c r="X47" s="15" t="n">
         <f aca="false">X46-X44</f>
-        <v>-95251.635557357</v>
+        <v>-91932.9357933058</v>
       </c>
       <c r="Y47" s="15" t="n">
         <f aca="false">Y46-Y44</f>
-        <v>-88216.0146956314</v>
+        <v>-84755.8099276476</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8161,87 +8161,87 @@
       </c>
       <c r="E48" s="15" t="n">
         <f aca="false">E19-E38-E44</f>
-        <v>-119336.149926083</v>
+        <v>-116965.774926083</v>
       </c>
       <c r="F48" s="15" t="n">
         <f aca="false">F19-F38-F44</f>
-        <v>-115400.976530542</v>
+        <v>-113036.624447209</v>
       </c>
       <c r="G48" s="15" t="n">
         <f aca="false">G19-G38-G44</f>
-        <v>-111828.979614085</v>
+        <v>-109470.550065474</v>
       </c>
       <c r="H48" s="15" t="n">
         <f aca="false">H19-H38-H44</f>
-        <v>-108578.063294787</v>
+        <v>-106225.457571986</v>
       </c>
       <c r="I48" s="15" t="n">
         <f aca="false">I19-I38-I44</f>
-        <v>-105611.142659737</v>
+        <v>-103264.263698982</v>
       </c>
       <c r="J48" s="15" t="n">
         <f aca="false">J19-J38-J44</f>
-        <v>-101360.907194</v>
+        <v>-99019.6595492586</v>
       </c>
       <c r="K48" s="15" t="n">
         <f aca="false">K19-K38-K44</f>
-        <v>-97968.0222977263</v>
+        <v>-95632.3121137303</v>
       </c>
       <c r="L48" s="15" t="n">
         <f aca="false">L19-L38-L44</f>
-        <v>-94848.4479824247</v>
+        <v>-92518.182968162</v>
       </c>
       <c r="M48" s="15" t="n">
         <f aca="false">M19-M38-M44</f>
-        <v>-90205.555726833</v>
+        <v>-87880.6451294747</v>
       </c>
       <c r="N48" s="15" t="n">
         <f aca="false">N19-N38-N44</f>
-        <v>-136644.827666041</v>
+        <v>-134325.182245306</v>
       </c>
       <c r="O48" s="15" t="n">
         <f aca="false">O19-O38-O44</f>
-        <v>-133348.637246565</v>
+        <v>-131034.169249509</v>
       </c>
       <c r="P48" s="15" t="n">
         <f aca="false">P19-P38-P44</f>
-        <v>-128290.759841908</v>
+        <v>-125981.382978135</v>
       </c>
       <c r="Q48" s="15" t="n">
         <f aca="false">Q19-Q38-Q44</f>
-        <v>-124541.278606273</v>
+        <v>-122236.908023564</v>
       </c>
       <c r="R48" s="15" t="n">
         <f aca="false">R19-R38-R44</f>
-        <v>-118898.134515102</v>
+        <v>-116598.686775438</v>
       </c>
       <c r="S48" s="15" t="n">
         <f aca="false">S19-S38-S44</f>
-        <v>-114738.255890798</v>
+        <v>-112443.648946794</v>
       </c>
       <c r="T48" s="15" t="n">
         <f aca="false">T19-T38-T44</f>
-        <v>-108547.119581814</v>
+        <v>-106257.272753544</v>
       </c>
       <c r="U48" s="15" t="n">
         <f aca="false">U19-U38-U44</f>
-        <v>-101627.513267531</v>
+        <v>-99342.347219732</v>
       </c>
       <c r="V48" s="15" t="n">
         <f aca="false">V19-V38-V44</f>
-        <v>-96480.4065174891</v>
+        <v>-94199.8432371536</v>
       </c>
       <c r="W48" s="15" t="n">
         <f aca="false">W19-W38-W44</f>
-        <v>-89119.8311505472</v>
+        <v>-86843.793924884</v>
       </c>
       <c r="X48" s="15" t="n">
         <f aca="false">X19-X38-X44</f>
-        <v>-81076.3558934196</v>
+        <v>-78804.7692881841</v>
       </c>
       <c r="Y48" s="15" t="n">
         <f aca="false">Y19-Y38-Y44</f>
-        <v>-72385.7126094263</v>
+        <v>-70118.5024476113</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8262,87 +8262,87 @@
       </c>
       <c r="E49" s="15" t="n">
         <f aca="false">D49+E48</f>
-        <v>85090.5110739167</v>
+        <v>87460.8860739167</v>
       </c>
       <c r="F49" s="15" t="n">
         <f aca="false">E49+F48</f>
-        <v>-30310.4654566256</v>
+        <v>-25575.7383732923</v>
       </c>
       <c r="G49" s="15" t="n">
         <f aca="false">F49+G48</f>
-        <v>-142139.445070711</v>
+        <v>-135046.288438766</v>
       </c>
       <c r="H49" s="15" t="n">
         <f aca="false">G49+H48</f>
-        <v>-250717.508365497</v>
+        <v>-241271.746010752</v>
       </c>
       <c r="I49" s="15" t="n">
         <f aca="false">H49+I48</f>
-        <v>-356328.651025234</v>
+        <v>-344536.009709734</v>
       </c>
       <c r="J49" s="15" t="n">
         <f aca="false">I49+J48</f>
-        <v>-457689.558219234</v>
+        <v>-443555.669258993</v>
       </c>
       <c r="K49" s="15" t="n">
         <f aca="false">J49+K48</f>
-        <v>-555657.580516961</v>
+        <v>-539187.981372723</v>
       </c>
       <c r="L49" s="15" t="n">
         <f aca="false">K49+L48</f>
-        <v>-650506.028499385</v>
+        <v>-631706.164340885</v>
       </c>
       <c r="M49" s="15" t="n">
         <f aca="false">L49+M48</f>
-        <v>-740711.584226218</v>
+        <v>-719586.80947036</v>
       </c>
       <c r="N49" s="15" t="n">
         <f aca="false">M49+N48</f>
-        <v>-877356.41189226</v>
+        <v>-853911.991715666</v>
       </c>
       <c r="O49" s="15" t="n">
         <f aca="false">N49+O48</f>
-        <v>-1010705.04913883</v>
+        <v>-984946.160965174</v>
       </c>
       <c r="P49" s="15" t="n">
         <f aca="false">O49+P48</f>
-        <v>-1138995.80898073</v>
+        <v>-1110927.54394331</v>
       </c>
       <c r="Q49" s="15" t="n">
         <f aca="false">P49+Q48</f>
-        <v>-1263537.08758701</v>
+        <v>-1233164.45196687</v>
       </c>
       <c r="R49" s="15" t="n">
         <f aca="false">Q49+R48</f>
-        <v>-1382435.22210211</v>
+        <v>-1349763.13874231</v>
       </c>
       <c r="S49" s="15" t="n">
         <f aca="false">R49+S48</f>
-        <v>-1497173.47799291</v>
+        <v>-1462206.78768911</v>
       </c>
       <c r="T49" s="15" t="n">
         <f aca="false">S49+T48</f>
-        <v>-1605720.59757472</v>
+        <v>-1568464.06044265</v>
       </c>
       <c r="U49" s="15" t="n">
         <f aca="false">T49+U48</f>
-        <v>-1707348.11084225</v>
+        <v>-1667806.40766238</v>
       </c>
       <c r="V49" s="15" t="n">
         <f aca="false">U49+V48</f>
-        <v>-1803828.51735974</v>
+        <v>-1762006.25089954</v>
       </c>
       <c r="W49" s="15" t="n">
         <f aca="false">V49+W48</f>
-        <v>-1892948.34851029</v>
+        <v>-1848850.04482442</v>
       </c>
       <c r="X49" s="15" t="n">
         <f aca="false">W49+X48</f>
-        <v>-1974024.70440371</v>
+        <v>-1927654.8141126</v>
       </c>
       <c r="Y49" s="15" t="n">
         <f aca="false">X49+Y48</f>
-        <v>-2046410.41701313</v>
+        <v>-1997773.31656021</v>
       </c>
       <c r="Z49" s="8" t="s">
         <v>315</v>
@@ -9390,87 +9390,87 @@
       </c>
       <c r="E15" s="7" t="n">
         <f aca="false">E13*Допущения!$C$23/12</f>
-        <v>3750</v>
+        <v>4158.33333333333</v>
       </c>
       <c r="F15" s="7" t="n">
         <f aca="false">F13*Допущения!$C$23/12</f>
-        <v>7437.5</v>
+        <v>8247.36111111111</v>
       </c>
       <c r="G15" s="7" t="n">
         <f aca="false">G13*Допущения!$C$23/12</f>
-        <v>11063.5416666667</v>
+        <v>12268.2384259259</v>
       </c>
       <c r="H15" s="7" t="n">
         <f aca="false">H13*Допущения!$C$23/12</f>
-        <v>14629.1493055556</v>
+        <v>16222.1011188272</v>
       </c>
       <c r="I15" s="7" t="n">
         <f aca="false">I13*Допущения!$C$23/12</f>
-        <v>18135.330150463</v>
+        <v>20110.06610018</v>
       </c>
       <c r="J15" s="7" t="n">
         <f aca="false">J13*Допущения!$C$23/12</f>
-        <v>21583.0746479552</v>
+        <v>23933.231665177</v>
       </c>
       <c r="K15" s="7" t="n">
         <f aca="false">K13*Допущения!$C$23/12</f>
-        <v>24973.356737156</v>
+        <v>27692.6778040908</v>
       </c>
       <c r="L15" s="7" t="n">
         <f aca="false">L13*Допущения!$C$23/12</f>
-        <v>28307.1341248701</v>
+        <v>31389.4665073559</v>
       </c>
       <c r="M15" s="7" t="n">
         <f aca="false">M13*Допущения!$C$23/12</f>
-        <v>31585.3485561222</v>
+        <v>35024.6420655666</v>
       </c>
       <c r="N15" s="7" t="n">
         <f aca="false">N13*Допущения!$C$23/12</f>
-        <v>34808.9260801868</v>
+        <v>38599.2313644739</v>
       </c>
       <c r="O15" s="7" t="n">
         <f aca="false">O13*Допущения!$C$23/12</f>
-        <v>37978.7773121837</v>
+        <v>42114.244175066</v>
       </c>
       <c r="P15" s="7" t="n">
         <f aca="false">P13*Допущения!$C$23/12</f>
-        <v>41095.797690314</v>
+        <v>45570.6734388149</v>
       </c>
       <c r="Q15" s="7" t="n">
         <f aca="false">Q13*Допущения!$C$23/12</f>
-        <v>44160.8677288088</v>
+        <v>48969.4955481679</v>
       </c>
       <c r="R15" s="7" t="n">
         <f aca="false">R13*Допущения!$C$23/12</f>
-        <v>47174.853266662</v>
+        <v>52311.6706223651</v>
       </c>
       <c r="S15" s="7" t="n">
         <f aca="false">S13*Допущения!$C$23/12</f>
-        <v>50138.6057122176</v>
+        <v>55598.142778659</v>
       </c>
       <c r="T15" s="7" t="n">
         <f aca="false">T13*Допущения!$C$23/12</f>
-        <v>53052.9622836806</v>
+        <v>58829.8403990147</v>
       </c>
       <c r="U15" s="7" t="n">
         <f aca="false">U13*Допущения!$C$23/12</f>
-        <v>55918.7462456193</v>
+        <v>62007.6763923645</v>
       </c>
       <c r="V15" s="7" t="n">
         <f aca="false">V13*Допущения!$C$23/12</f>
-        <v>58736.7671415256</v>
+        <v>65132.5484524917</v>
       </c>
       <c r="W15" s="7" t="n">
         <f aca="false">W13*Допущения!$C$23/12</f>
-        <v>61507.8210225002</v>
+        <v>68205.3393116169</v>
       </c>
       <c r="X15" s="7" t="n">
         <f aca="false">X13*Допущения!$C$23/12</f>
-        <v>64232.6906721252</v>
+        <v>71226.9169897566</v>
       </c>
       <c r="Y15" s="7" t="n">
         <f aca="false">Y13*Допущения!$C$23/12</f>
-        <v>66912.1458275898</v>
+        <v>74198.1350399273</v>
       </c>
       <c r="Z15" s="8" t="s">
         <v>275</v>
@@ -9598,87 +9598,87 @@
       </c>
       <c r="E17" s="15" t="n">
         <f aca="false">E16+E15</f>
-        <v>12235.8175875</v>
+        <v>12644.1509208333</v>
       </c>
       <c r="F17" s="15" t="n">
         <f aca="false">F16+F15</f>
-        <v>20013.8310143167</v>
+        <v>20823.6921254278</v>
       </c>
       <c r="G17" s="15" t="n">
         <f aca="false">G16+G15</f>
-        <v>27334.5812107685</v>
+        <v>28539.2779700277</v>
       </c>
       <c r="H17" s="15" t="n">
         <f aca="false">H16+H15</f>
-        <v>34244.5179410282</v>
+        <v>35837.4697542998</v>
       </c>
       <c r="I17" s="15" t="n">
         <f aca="false">I16+I15</f>
-        <v>40784.6749767404</v>
+        <v>42759.4109264575</v>
       </c>
       <c r="J17" s="15" t="n">
         <f aca="false">J16+J15</f>
-        <v>47969.2441823747</v>
+        <v>50319.4011995965</v>
       </c>
       <c r="K17" s="15" t="n">
         <f aca="false">K16+K15</f>
-        <v>54759.8536218436</v>
+        <v>57479.1746887784</v>
       </c>
       <c r="L17" s="15" t="n">
         <f aca="false">L16+L15</f>
-        <v>61195.3238091243</v>
+        <v>64277.6561916101</v>
       </c>
       <c r="M17" s="15" t="n">
         <f aca="false">M16+M15</f>
-        <v>68283.4419850829</v>
+        <v>71722.7354945274</v>
       </c>
       <c r="N17" s="15" t="n">
         <f aca="false">N16+N15</f>
-        <v>74991.8895408762</v>
+        <v>78782.1948251632</v>
       </c>
       <c r="O17" s="15" t="n">
         <f aca="false">O16+O15</f>
-        <v>81357.6252358518</v>
+        <v>85493.092098734</v>
       </c>
       <c r="P17" s="15" t="n">
         <f aca="false">P16+P15</f>
-        <v>88382.3337407862</v>
+        <v>92857.2094892871</v>
       </c>
       <c r="Q17" s="15" t="n">
         <f aca="false">Q16+Q15</f>
-        <v>95039.9849220953</v>
+        <v>99848.6127414545</v>
       </c>
       <c r="R17" s="15" t="n">
         <f aca="false">R16+R15</f>
-        <v>102331.719373771</v>
+        <v>107468.536729474</v>
       </c>
       <c r="S17" s="15" t="n">
         <f aca="false">S16+S15</f>
-        <v>109238.813440181</v>
+        <v>114698.350506622</v>
       </c>
       <c r="T17" s="15" t="n">
         <f aca="false">T16+T15</f>
-        <v>116761.093484239</v>
+        <v>122537.971599573</v>
       </c>
       <c r="U17" s="15" t="n">
         <f aca="false">U16+U15</f>
-        <v>124847.716214451</v>
+        <v>130936.646361196</v>
       </c>
       <c r="V17" s="15" t="n">
         <f aca="false">V16+V15</f>
-        <v>132494.18877189</v>
+        <v>138889.970082856</v>
       </c>
       <c r="W17" s="15" t="n">
         <f aca="false">W16+W15</f>
-        <v>140701.330339283</v>
+        <v>147398.8486284</v>
       </c>
       <c r="X17" s="15" t="n">
         <f aca="false">X16+X15</f>
-        <v>149426.32185279</v>
+        <v>156420.548170421</v>
       </c>
       <c r="Y17" s="15" t="n">
         <f aca="false">Y16+Y15</f>
-        <v>158631.499602512</v>
+        <v>165917.488814849</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9803,87 +9803,87 @@
       </c>
       <c r="E19" s="7" t="n">
         <f aca="false">E16+E18-E9*Допущения!$C$10*3/24*Допущения!$C$9/12+E12*Допущения!$C$23</f>
-        <v>54733.6300875</v>
+        <v>59633.6300875</v>
       </c>
       <c r="F19" s="7" t="n">
         <f aca="false">F16+F18-F9*Допущения!$C$10*4/24*Допущения!$C$9/12+F12*Допущения!$C$23</f>
-        <v>59240.0810143167</v>
+        <v>64140.0810143167</v>
       </c>
       <c r="G19" s="7" t="n">
         <f aca="false">G16+G18-G9*Допущения!$C$10*5/24*Допущения!$C$9/12+G12*Допущения!$C$23</f>
-        <v>63350.7270441018</v>
+        <v>68250.7270441018</v>
       </c>
       <c r="H19" s="7" t="n">
         <f aca="false">H16+H18-H9*Допущения!$C$10*6/24*Допущения!$C$9/12+H12*Допущения!$C$23</f>
-        <v>67110.9936354726</v>
+        <v>72010.9936354726</v>
       </c>
       <c r="I19" s="7" t="n">
         <f aca="false">I16+I18-I9*Допущения!$C$10*7/24*Допущения!$C$9/12+I12*Допущения!$C$23</f>
-        <v>70560.9073262775</v>
+        <v>75460.9073262775</v>
       </c>
       <c r="J19" s="7" t="n">
         <f aca="false">J16+J18-J9*Допущения!$C$10*8/24*Допущения!$C$9/12+J12*Допущения!$C$23</f>
-        <v>75379.1695344194</v>
+        <v>80279.1695344194</v>
       </c>
       <c r="K19" s="7" t="n">
         <f aca="false">K16+K18-K9*Допущения!$C$10*9/24*Допущения!$C$9/12+K12*Допущения!$C$23</f>
-        <v>79278.6218846876</v>
+        <v>84178.6218846876</v>
       </c>
       <c r="L19" s="7" t="n">
         <f aca="false">L16+L18-L9*Допущения!$C$10*10/24*Допущения!$C$9/12+L12*Допущения!$C$23</f>
-        <v>82879.4396842542</v>
+        <v>87779.4396842542</v>
       </c>
       <c r="M19" s="7" t="n">
         <f aca="false">M16+M18-M9*Допущения!$C$10*11/24*Допущения!$C$9/12+M12*Допущения!$C$23</f>
-        <v>88103.5309289607</v>
+        <v>93003.5309289607</v>
       </c>
       <c r="N19" s="7" t="n">
         <f aca="false">N16+N18-N9*Допущения!$C$10*12/24*Допущения!$C$9/12+N12*Допущения!$C$23</f>
-        <v>92170.7134606893</v>
+        <v>97070.7134606893</v>
       </c>
       <c r="O19" s="7" t="n">
         <f aca="false">O16+O18-O9*Допущения!$C$10*13/24*Допущения!$C$9/12+O12*Допущения!$C$23</f>
-        <v>95948.9104236681</v>
+        <v>100848.910423668</v>
       </c>
       <c r="P19" s="7" t="n">
         <f aca="false">P16+P18-P9*Допущения!$C$10*14/24*Допущения!$C$9/12+P12*Допущения!$C$23</f>
-        <v>101603.536050472</v>
+        <v>106503.536050472</v>
       </c>
       <c r="Q19" s="7" t="n">
         <f aca="false">Q16+Q18-Q9*Допущения!$C$10*15/24*Допущения!$C$9/12+Q12*Допущения!$C$23</f>
-        <v>105861.617193287</v>
+        <v>110761.617193287</v>
       </c>
       <c r="R19" s="7" t="n">
         <f aca="false">R16+R18-R9*Допущения!$C$10*16/24*Допущения!$C$9/12+R12*Допущения!$C$23</f>
-        <v>112135.866107109</v>
+        <v>117035.866107109</v>
       </c>
       <c r="S19" s="7" t="n">
         <f aca="false">S16+S18-S9*Допущения!$C$10*17/24*Допущения!$C$9/12+S12*Допущения!$C$23</f>
-        <v>116827.895227963</v>
+        <v>121727.895227963</v>
       </c>
       <c r="T19" s="7" t="n">
         <f aca="false">T16+T18-T9*Допущения!$C$10*18/24*Допущения!$C$9/12+T12*Допущения!$C$23</f>
-        <v>123681.881200558</v>
+        <v>128581.881200558</v>
       </c>
       <c r="U19" s="7" t="n">
         <f aca="false">U16+U18-U9*Допущения!$C$10*19/24*Допущения!$C$9/12+U12*Допущения!$C$23</f>
-        <v>131315.157468832</v>
+        <v>136215.157468832</v>
       </c>
       <c r="V19" s="7" t="n">
         <f aca="false">V16+V18-V9*Допущения!$C$10*20/24*Допущения!$C$9/12+V12*Допущения!$C$23</f>
-        <v>137058.671630365</v>
+        <v>141958.671630365</v>
       </c>
       <c r="W19" s="7" t="n">
         <f aca="false">W16+W18-W9*Допущения!$C$10*21/24*Допущения!$C$9/12+W12*Допущения!$C$23</f>
-        <v>145156.759316783</v>
+        <v>150056.759316783</v>
       </c>
       <c r="X19" s="7" t="n">
         <f aca="false">X16+X18-X9*Допущения!$C$10*22/24*Допущения!$C$9/12+X12*Допущения!$C$23</f>
-        <v>153985.256180665</v>
+        <v>158885.256180665</v>
       </c>
       <c r="Y19" s="7" t="n">
         <f aca="false">Y16+Y18-Y9*Допущения!$C$10*23/24*Допущения!$C$9/12+Y12*Допущения!$C$23</f>
-        <v>163505.728774922</v>
+        <v>168405.728774922</v>
       </c>
       <c r="Z19" s="8" t="s">
         <v>282</v>
@@ -11056,87 +11056,87 @@
       </c>
       <c r="E32" s="7" t="n">
         <f aca="false">E19*Допущения!$C$58</f>
-        <v>1642.008902625</v>
+        <v>1789.008902625</v>
       </c>
       <c r="F32" s="7" t="n">
         <f aca="false">F19*Допущения!$C$58</f>
-        <v>1777.2024304295</v>
+        <v>1924.2024304295</v>
       </c>
       <c r="G32" s="7" t="n">
         <f aca="false">G19*Допущения!$C$58</f>
-        <v>1900.52181132305</v>
+        <v>2047.52181132305</v>
       </c>
       <c r="H32" s="7" t="n">
         <f aca="false">H19*Допущения!$C$58</f>
-        <v>2013.32980906418</v>
+        <v>2160.32980906418</v>
       </c>
       <c r="I32" s="7" t="n">
         <f aca="false">I19*Допущения!$C$58</f>
-        <v>2116.82721978832</v>
+        <v>2263.82721978832</v>
       </c>
       <c r="J32" s="7" t="n">
         <f aca="false">J19*Допущения!$C$58</f>
-        <v>2261.37508603258</v>
+        <v>2408.37508603258</v>
       </c>
       <c r="K32" s="7" t="n">
         <f aca="false">K19*Допущения!$C$58</f>
-        <v>2378.35865654063</v>
+        <v>2525.35865654063</v>
       </c>
       <c r="L32" s="7" t="n">
         <f aca="false">L19*Допущения!$C$58</f>
-        <v>2486.38319052763</v>
+        <v>2633.38319052763</v>
       </c>
       <c r="M32" s="7" t="n">
         <f aca="false">M19*Допущения!$C$58</f>
-        <v>2643.10592786882</v>
+        <v>2790.10592786882</v>
       </c>
       <c r="N32" s="7" t="n">
         <f aca="false">N19*Допущения!$C$58</f>
-        <v>2765.12140382068</v>
+        <v>2912.12140382068</v>
       </c>
       <c r="O32" s="7" t="n">
         <f aca="false">O19*Допущения!$C$58</f>
-        <v>2878.46731271004</v>
+        <v>3025.46731271004</v>
       </c>
       <c r="P32" s="7" t="n">
         <f aca="false">P19*Допущения!$C$58</f>
-        <v>3048.10608151417</v>
+        <v>3195.10608151417</v>
       </c>
       <c r="Q32" s="7" t="n">
         <f aca="false">Q19*Допущения!$C$58</f>
-        <v>3175.8485157986</v>
+        <v>3322.8485157986</v>
       </c>
       <c r="R32" s="7" t="n">
         <f aca="false">R19*Допущения!$C$58</f>
-        <v>3364.07598321326</v>
+        <v>3511.07598321326</v>
       </c>
       <c r="S32" s="7" t="n">
         <f aca="false">S19*Допущения!$C$58</f>
-        <v>3504.8368568389</v>
+        <v>3651.8368568389</v>
       </c>
       <c r="T32" s="7" t="n">
         <f aca="false">T19*Допущения!$C$58</f>
-        <v>3710.45643601674</v>
+        <v>3857.45643601674</v>
       </c>
       <c r="U32" s="7" t="n">
         <f aca="false">U19*Допущения!$C$58</f>
-        <v>3939.45472406495</v>
+        <v>4086.45472406495</v>
       </c>
       <c r="V32" s="7" t="n">
         <f aca="false">V19*Допущения!$C$58</f>
-        <v>4111.76014891094</v>
+        <v>4258.76014891094</v>
       </c>
       <c r="W32" s="7" t="n">
         <f aca="false">W19*Допущения!$C$58</f>
-        <v>4354.70277950349</v>
+        <v>4501.70277950349</v>
       </c>
       <c r="X32" s="7" t="n">
         <f aca="false">X19*Допущения!$C$58</f>
-        <v>4619.55768541994</v>
+        <v>4766.55768541994</v>
       </c>
       <c r="Y32" s="7" t="n">
         <f aca="false">Y19*Допущения!$C$58</f>
-        <v>4905.17186324766</v>
+        <v>5052.17186324766</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11671,87 +11671,87 @@
       </c>
       <c r="E38" s="15" t="n">
         <f aca="false">SUM(E21:E37)</f>
-        <v>152133.955485958</v>
+        <v>152280.955485958</v>
       </c>
       <c r="F38" s="15" t="n">
         <f aca="false">SUM(F21:F37)</f>
-        <v>152723.871781096</v>
+        <v>152870.871781096</v>
       </c>
       <c r="G38" s="15" t="n">
         <f aca="false">SUM(G21:G37)</f>
-        <v>153290.677902419</v>
+        <v>153437.677902419</v>
       </c>
       <c r="H38" s="15" t="n">
         <f aca="false">SUM(H21:H37)</f>
-        <v>153836.379927908</v>
+        <v>153983.379927908</v>
       </c>
       <c r="I38" s="15" t="n">
         <f aca="false">SUM(I21:I37)</f>
-        <v>154362.757296994</v>
+        <v>154509.757296994</v>
       </c>
       <c r="J38" s="15" t="n">
         <f aca="false">SUM(J21:J37)</f>
-        <v>154950.842837225</v>
+        <v>155097.842837225</v>
       </c>
       <c r="K38" s="15" t="n">
         <f aca="false">SUM(K21:K37)</f>
-        <v>155485.361284131</v>
+        <v>155632.361284131</v>
       </c>
       <c r="L38" s="15" t="n">
         <f aca="false">SUM(L21:L37)</f>
-        <v>156001.348784271</v>
+        <v>156148.348784271</v>
       </c>
       <c r="M38" s="15" t="n">
         <f aca="false">SUM(M21:M37)</f>
-        <v>156593.915547576</v>
+        <v>156740.915547576</v>
       </c>
       <c r="N38" s="15" t="n">
         <f aca="false">SUM(N21:N37)</f>
-        <v>207119.394389317</v>
+        <v>207266.394389317</v>
       </c>
       <c r="O38" s="15" t="n">
         <f aca="false">SUM(O21:O37)</f>
-        <v>207627.035362824</v>
+        <v>207774.035362824</v>
       </c>
       <c r="P38" s="15" t="n">
         <f aca="false">SUM(P21:P37)</f>
-        <v>208226.038722328</v>
+        <v>208373.038722328</v>
       </c>
       <c r="Q38" s="15" t="n">
         <f aca="false">SUM(Q21:Q37)</f>
-        <v>208744.355546699</v>
+        <v>208891.355546699</v>
       </c>
       <c r="R38" s="15" t="n">
         <f aca="false">SUM(R21:R37)</f>
-        <v>209362.664014219</v>
+        <v>209509.664014219</v>
       </c>
       <c r="S38" s="15" t="n">
         <f aca="false">SUM(S21:S37)</f>
-        <v>209890.124772557</v>
+        <v>210037.124772557</v>
       </c>
       <c r="T38" s="15" t="n">
         <f aca="false">SUM(T21:T37)</f>
-        <v>210526.453733897</v>
+        <v>210673.453733897</v>
       </c>
       <c r="U38" s="15" t="n">
         <f aca="false">SUM(U21:U37)</f>
-        <v>211193.353576713</v>
+        <v>211340.353576713</v>
       </c>
       <c r="V38" s="15" t="n">
         <f aca="false">SUM(V21:V37)</f>
-        <v>211752.931572701</v>
+        <v>211899.931572701</v>
       </c>
       <c r="W38" s="15" t="n">
         <f aca="false">SUM(W21:W37)</f>
-        <v>212433.584993689</v>
+        <v>212580.584993689</v>
       </c>
       <c r="X38" s="15" t="n">
         <f aca="false">SUM(X21:X37)</f>
-        <v>213143.056281096</v>
+        <v>213290.056281096</v>
       </c>
       <c r="Y38" s="15" t="n">
         <f aca="false">SUM(Y21:Y37)</f>
-        <v>213879.826361158</v>
+        <v>214026.826361158</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11801,87 +11801,87 @@
       </c>
       <c r="E40" s="7" t="n">
         <f aca="false">SUM($E$17:E17)</f>
-        <v>12235.8175875</v>
+        <v>12644.1509208333</v>
       </c>
       <c r="F40" s="7" t="n">
         <f aca="false">SUM($E$17:F17)</f>
-        <v>32249.6486018167</v>
+        <v>33467.8430462611</v>
       </c>
       <c r="G40" s="7" t="n">
         <f aca="false">SUM($E$17:G17)</f>
-        <v>59584.2298125851</v>
+        <v>62007.1210162889</v>
       </c>
       <c r="H40" s="7" t="n">
         <f aca="false">SUM($E$17:H17)</f>
-        <v>93828.7477536133</v>
+        <v>97844.5907705887</v>
       </c>
       <c r="I40" s="7" t="n">
         <f aca="false">SUM($E$17:I17)</f>
-        <v>134613.422730354</v>
+        <v>140604.001697046</v>
       </c>
       <c r="J40" s="7" t="n">
         <f aca="false">SUM($E$17:J17)</f>
-        <v>182582.666912728</v>
+        <v>190923.402896643</v>
       </c>
       <c r="K40" s="7" t="n">
         <f aca="false">SUM($E$17:K17)</f>
-        <v>237342.520534572</v>
+        <v>248402.577585421</v>
       </c>
       <c r="L40" s="7" t="n">
         <f aca="false">SUM($E$17:L17)</f>
-        <v>298537.844343696</v>
+        <v>312680.233777031</v>
       </c>
       <c r="M40" s="7" t="n">
         <f aca="false">SUM($E$17:M17)</f>
-        <v>366821.286328779</v>
+        <v>384402.969271558</v>
       </c>
       <c r="N40" s="7" t="n">
         <f aca="false">SUM($E$17:N17)</f>
-        <v>441813.175869655</v>
+        <v>463185.164096722</v>
       </c>
       <c r="O40" s="7" t="n">
         <f aca="false">SUM($E$17:O17)</f>
-        <v>523170.801105507</v>
+        <v>548678.256195456</v>
       </c>
       <c r="P40" s="7" t="n">
         <f aca="false">SUM($E$17:P17)</f>
-        <v>611553.134846294</v>
+        <v>641535.465684743</v>
       </c>
       <c r="Q40" s="7" t="n">
         <f aca="false">SUM($E$17:Q17)</f>
-        <v>706593.119768389</v>
+        <v>741384.078426197</v>
       </c>
       <c r="R40" s="7" t="n">
         <f aca="false">SUM($E$17:R17)</f>
-        <v>808924.839142159</v>
+        <v>848852.615155671</v>
       </c>
       <c r="S40" s="7" t="n">
         <f aca="false">SUM($E$17:S17)</f>
-        <v>918163.65258234</v>
+        <v>963550.965662294</v>
       </c>
       <c r="T40" s="7" t="n">
         <f aca="false">SUM($E$17:T17)</f>
-        <v>1034924.74606658</v>
+        <v>1086088.93726187</v>
       </c>
       <c r="U40" s="7" t="n">
         <f aca="false">SUM($E$17:U17)</f>
-        <v>1159772.46228103</v>
+        <v>1217025.58362306</v>
       </c>
       <c r="V40" s="7" t="n">
         <f aca="false">SUM($E$17:V17)</f>
-        <v>1292266.65105292</v>
+        <v>1355915.55370592</v>
       </c>
       <c r="W40" s="7" t="n">
         <f aca="false">SUM($E$17:W17)</f>
-        <v>1432967.9813922</v>
+        <v>1503314.40233432</v>
       </c>
       <c r="X40" s="7" t="n">
         <f aca="false">SUM($E$17:X17)</f>
-        <v>1582394.30324499</v>
+        <v>1659734.95050474</v>
       </c>
       <c r="Y40" s="7" t="n">
         <f aca="false">SUM($E$17:Y17)</f>
-        <v>1741025.80284751</v>
+        <v>1825652.43931959</v>
       </c>
       <c r="Z40" s="8" t="s">
         <v>303</v>
@@ -12009,87 +12009,87 @@
       </c>
       <c r="E42" s="7" t="n">
         <f aca="false">E17-E38-E41</f>
-        <v>-139898.137898458</v>
+        <v>-139636.804565125</v>
       </c>
       <c r="F42" s="7" t="n">
         <f aca="false">F17-F38-F41</f>
-        <v>-132710.04076678</v>
+        <v>-132047.179655668</v>
       </c>
       <c r="G42" s="7" t="n">
         <f aca="false">G17-G38-G41</f>
-        <v>-125956.096691651</v>
+        <v>-124898.399932391</v>
       </c>
       <c r="H42" s="7" t="n">
         <f aca="false">H17-H38-H41</f>
-        <v>-119591.86198688</v>
+        <v>-118145.910173608</v>
       </c>
       <c r="I42" s="7" t="n">
         <f aca="false">I17-I38-I41</f>
-        <v>-113578.082320253</v>
+        <v>-111750.346370536</v>
       </c>
       <c r="J42" s="7" t="n">
         <f aca="false">J17-J38-J41</f>
-        <v>-106981.598654851</v>
+        <v>-104778.441637629</v>
       </c>
       <c r="K42" s="7" t="n">
         <f aca="false">K17-K38-K41</f>
-        <v>-100725.507662287</v>
+        <v>-98153.1865953526</v>
       </c>
       <c r="L42" s="7" t="n">
         <f aca="false">L17-L38-L41</f>
-        <v>-94806.0249751471</v>
+        <v>-91870.6925926612</v>
       </c>
       <c r="M42" s="7" t="n">
         <f aca="false">M17-M38-M41</f>
-        <v>-88310.4735624933</v>
+        <v>-85018.1800530489</v>
       </c>
       <c r="N42" s="7" t="n">
         <f aca="false">N17-N38-N41</f>
-        <v>-132127.504848441</v>
+        <v>-128484.199564154</v>
       </c>
       <c r="O42" s="7" t="n">
         <f aca="false">O17-O38-O41</f>
-        <v>-126269.410126972</v>
+        <v>-122280.94326409</v>
       </c>
       <c r="P42" s="7" t="n">
         <f aca="false">P17-P38-P41</f>
-        <v>-119843.704981542</v>
+        <v>-115515.829233041</v>
       </c>
       <c r="Q42" s="7" t="n">
         <f aca="false">Q17-Q38-Q41</f>
-        <v>-113704.370624604</v>
+        <v>-109042.742805245</v>
       </c>
       <c r="R42" s="7" t="n">
         <f aca="false">R17-R38-R41</f>
-        <v>-107030.944640449</v>
+        <v>-102041.127284746</v>
       </c>
       <c r="S42" s="7" t="n">
         <f aca="false">S17-S38-S41</f>
-        <v>-100651.311332376</v>
+        <v>-95338.7742659347</v>
       </c>
       <c r="T42" s="7" t="n">
         <f aca="false">T17-T38-T41</f>
-        <v>-93765.3602496582</v>
+        <v>-88135.4821343241</v>
       </c>
       <c r="U42" s="7" t="n">
         <f aca="false">U17-U38-U41</f>
-        <v>-86345.637362262</v>
+        <v>-80403.7072155168</v>
       </c>
       <c r="V42" s="7" t="n">
         <f aca="false">V17-V38-V41</f>
-        <v>-79258.742800811</v>
+        <v>-73009.9614898449</v>
       </c>
       <c r="W42" s="7" t="n">
         <f aca="false">W17-W38-W41</f>
-        <v>-71732.2546544061</v>
+        <v>-65181.7363652894</v>
       </c>
       <c r="X42" s="7" t="n">
         <f aca="false">X17-X38-X41</f>
-        <v>-63716.7344283059</v>
+        <v>-56869.5081106745</v>
       </c>
       <c r="Y42" s="7" t="n">
         <f aca="false">Y17-Y38-Y41</f>
-        <v>-55248.3267586464</v>
+        <v>-48109.3375463089</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12110,87 +12110,87 @@
       </c>
       <c r="E43" s="7" t="n">
         <f aca="false">MAX(E42*Допущения!$C$51,E17*Допущения!$C$52)</f>
-        <v>367.074527625</v>
+        <v>379.324527625</v>
       </c>
       <c r="F43" s="7" t="n">
         <f aca="false">MAX(F42*Допущения!$C$51,F17*Допущения!$C$52)</f>
-        <v>600.4149304295</v>
+        <v>624.710763762833</v>
       </c>
       <c r="G43" s="7" t="n">
         <f aca="false">MAX(G42*Допущения!$C$51,G17*Допущения!$C$52)</f>
-        <v>820.037436323054</v>
+        <v>856.178339100832</v>
       </c>
       <c r="H43" s="7" t="n">
         <f aca="false">MAX(H42*Допущения!$C$51,H17*Допущения!$C$52)</f>
-        <v>1027.33553823085</v>
+        <v>1075.12409262899</v>
       </c>
       <c r="I43" s="7" t="n">
         <f aca="false">MAX(I42*Допущения!$C$51,I17*Допущения!$C$52)</f>
-        <v>1223.54024930221</v>
+        <v>1282.78232779372</v>
       </c>
       <c r="J43" s="7" t="n">
         <f aca="false">MAX(J42*Допущения!$C$51,J17*Допущения!$C$52)</f>
-        <v>1439.07732547124</v>
+        <v>1509.58203598789</v>
       </c>
       <c r="K43" s="7" t="n">
         <f aca="false">MAX(K42*Допущения!$C$51,K17*Допущения!$C$52)</f>
-        <v>1642.79560865531</v>
+        <v>1724.37524066335</v>
       </c>
       <c r="L43" s="7" t="n">
         <f aca="false">MAX(L42*Допущения!$C$51,L17*Допущения!$C$52)</f>
-        <v>1835.85971427373</v>
+        <v>1928.3296857483</v>
       </c>
       <c r="M43" s="7" t="n">
         <f aca="false">MAX(M42*Допущения!$C$51,M17*Допущения!$C$52)</f>
-        <v>2048.50325955249</v>
+        <v>2151.68206483582</v>
       </c>
       <c r="N43" s="7" t="n">
         <f aca="false">MAX(N42*Допущения!$C$51,N17*Допущения!$C$52)</f>
-        <v>2249.75668622629</v>
+        <v>2363.4658447549</v>
       </c>
       <c r="O43" s="7" t="n">
         <f aca="false">MAX(O42*Допущения!$C$51,O17*Допущения!$C$52)</f>
-        <v>2440.72875707555</v>
+        <v>2564.79276296202</v>
       </c>
       <c r="P43" s="7" t="n">
         <f aca="false">MAX(P42*Допущения!$C$51,P17*Допущения!$C$52)</f>
-        <v>2651.47001222359</v>
+        <v>2785.71628467861</v>
       </c>
       <c r="Q43" s="7" t="n">
         <f aca="false">MAX(Q42*Допущения!$C$51,Q17*Допущения!$C$52)</f>
-        <v>2851.19954766286</v>
+        <v>2995.45838224364</v>
       </c>
       <c r="R43" s="7" t="n">
         <f aca="false">MAX(R42*Допущения!$C$51,R17*Допущения!$C$52)</f>
-        <v>3069.95158121312</v>
+        <v>3224.05610188422</v>
       </c>
       <c r="S43" s="7" t="n">
         <f aca="false">MAX(S42*Допущения!$C$51,S17*Допущения!$C$52)</f>
-        <v>3277.16440320543</v>
+        <v>3440.95051519867</v>
       </c>
       <c r="T43" s="7" t="n">
         <f aca="false">MAX(T42*Допущения!$C$51,T17*Допущения!$C$52)</f>
-        <v>3502.83280452716</v>
+        <v>3676.13914798718</v>
       </c>
       <c r="U43" s="7" t="n">
         <f aca="false">MAX(U42*Допущения!$C$51,U17*Допущения!$C$52)</f>
-        <v>3745.43148643353</v>
+        <v>3928.09939083589</v>
       </c>
       <c r="V43" s="7" t="n">
         <f aca="false">MAX(V42*Допущения!$C$51,V17*Допущения!$C$52)</f>
-        <v>3974.82566315671</v>
+        <v>4166.69910248569</v>
       </c>
       <c r="W43" s="7" t="n">
         <f aca="false">MAX(W42*Допущения!$C$51,W17*Допущения!$C$52)</f>
-        <v>4221.03991017849</v>
+        <v>4421.96545885199</v>
       </c>
       <c r="X43" s="7" t="n">
         <f aca="false">MAX(X42*Допущения!$C$51,X17*Допущения!$C$52)</f>
-        <v>4482.7896555837</v>
+        <v>4692.61644511264</v>
       </c>
       <c r="Y43" s="7" t="n">
         <f aca="false">MAX(Y42*Допущения!$C$51,Y17*Допущения!$C$52)</f>
-        <v>4758.94498807535</v>
+        <v>4977.52466444548</v>
       </c>
       <c r="Z43" s="8" t="s">
         <v>308</v>
@@ -12214,87 +12214,87 @@
       </c>
       <c r="E44" s="15" t="n">
         <f aca="false">E41+E43</f>
-        <v>367.074527625</v>
+        <v>379.324527625</v>
       </c>
       <c r="F44" s="15" t="n">
         <f aca="false">F41+F43</f>
-        <v>600.4149304295</v>
+        <v>624.710763762833</v>
       </c>
       <c r="G44" s="15" t="n">
         <f aca="false">G41+G43</f>
-        <v>820.037436323054</v>
+        <v>856.178339100832</v>
       </c>
       <c r="H44" s="15" t="n">
         <f aca="false">H41+H43</f>
-        <v>1027.33553823085</v>
+        <v>1075.12409262899</v>
       </c>
       <c r="I44" s="15" t="n">
         <f aca="false">I41+I43</f>
-        <v>1223.54024930221</v>
+        <v>1282.78232779372</v>
       </c>
       <c r="J44" s="15" t="n">
         <f aca="false">J41+J43</f>
-        <v>1439.07732547124</v>
+        <v>1509.58203598789</v>
       </c>
       <c r="K44" s="15" t="n">
         <f aca="false">K41+K43</f>
-        <v>1642.79560865531</v>
+        <v>1724.37524066335</v>
       </c>
       <c r="L44" s="15" t="n">
         <f aca="false">L41+L43</f>
-        <v>1835.85971427373</v>
+        <v>1928.3296857483</v>
       </c>
       <c r="M44" s="15" t="n">
         <f aca="false">M41+M43</f>
-        <v>2048.50325955249</v>
+        <v>2151.68206483582</v>
       </c>
       <c r="N44" s="15" t="n">
         <f aca="false">N41+N43</f>
-        <v>2249.75668622629</v>
+        <v>2363.4658447549</v>
       </c>
       <c r="O44" s="15" t="n">
         <f aca="false">O41+O43</f>
-        <v>2440.72875707555</v>
+        <v>2564.79276296202</v>
       </c>
       <c r="P44" s="15" t="n">
         <f aca="false">P41+P43</f>
-        <v>2651.47001222359</v>
+        <v>2785.71628467861</v>
       </c>
       <c r="Q44" s="15" t="n">
         <f aca="false">Q41+Q43</f>
-        <v>2851.19954766286</v>
+        <v>2995.45838224364</v>
       </c>
       <c r="R44" s="15" t="n">
         <f aca="false">R41+R43</f>
-        <v>3069.95158121312</v>
+        <v>3224.05610188422</v>
       </c>
       <c r="S44" s="15" t="n">
         <f aca="false">S41+S43</f>
-        <v>3277.16440320543</v>
+        <v>3440.95051519867</v>
       </c>
       <c r="T44" s="15" t="n">
         <f aca="false">T41+T43</f>
-        <v>3502.83280452716</v>
+        <v>3676.13914798718</v>
       </c>
       <c r="U44" s="15" t="n">
         <f aca="false">U41+U43</f>
-        <v>3745.43148643353</v>
+        <v>3928.09939083589</v>
       </c>
       <c r="V44" s="15" t="n">
         <f aca="false">V41+V43</f>
-        <v>3974.82566315671</v>
+        <v>4166.69910248569</v>
       </c>
       <c r="W44" s="15" t="n">
         <f aca="false">W41+W43</f>
-        <v>4221.03991017849</v>
+        <v>4421.96545885199</v>
       </c>
       <c r="X44" s="15" t="n">
         <f aca="false">X41+X43</f>
-        <v>4482.7896555837</v>
+        <v>4692.61644511264</v>
       </c>
       <c r="Y44" s="15" t="n">
         <f aca="false">Y41+Y43</f>
-        <v>4758.94498807535</v>
+        <v>4977.52466444548</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12344,87 +12344,87 @@
       </c>
       <c r="E46" s="15" t="n">
         <f aca="false">E17-E38</f>
-        <v>-139898.137898458</v>
+        <v>-139636.804565125</v>
       </c>
       <c r="F46" s="15" t="n">
         <f aca="false">F17-F38</f>
-        <v>-132710.04076678</v>
+        <v>-132047.179655668</v>
       </c>
       <c r="G46" s="15" t="n">
         <f aca="false">G17-G38</f>
-        <v>-125956.096691651</v>
+        <v>-124898.399932391</v>
       </c>
       <c r="H46" s="15" t="n">
         <f aca="false">H17-H38</f>
-        <v>-119591.86198688</v>
+        <v>-118145.910173608</v>
       </c>
       <c r="I46" s="15" t="n">
         <f aca="false">I17-I38</f>
-        <v>-113578.082320253</v>
+        <v>-111750.346370536</v>
       </c>
       <c r="J46" s="15" t="n">
         <f aca="false">J17-J38</f>
-        <v>-106981.598654851</v>
+        <v>-104778.441637629</v>
       </c>
       <c r="K46" s="15" t="n">
         <f aca="false">K17-K38</f>
-        <v>-100725.507662287</v>
+        <v>-98153.1865953526</v>
       </c>
       <c r="L46" s="15" t="n">
         <f aca="false">L17-L38</f>
-        <v>-94806.0249751471</v>
+        <v>-91870.6925926612</v>
       </c>
       <c r="M46" s="15" t="n">
         <f aca="false">M17-M38</f>
-        <v>-88310.4735624933</v>
+        <v>-85018.1800530489</v>
       </c>
       <c r="N46" s="15" t="n">
         <f aca="false">N17-N38</f>
-        <v>-132127.504848441</v>
+        <v>-128484.199564154</v>
       </c>
       <c r="O46" s="15" t="n">
         <f aca="false">O17-O38</f>
-        <v>-126269.410126972</v>
+        <v>-122280.94326409</v>
       </c>
       <c r="P46" s="15" t="n">
         <f aca="false">P17-P38</f>
-        <v>-119843.704981542</v>
+        <v>-115515.829233041</v>
       </c>
       <c r="Q46" s="15" t="n">
         <f aca="false">Q17-Q38</f>
-        <v>-113704.370624604</v>
+        <v>-109042.742805245</v>
       </c>
       <c r="R46" s="15" t="n">
         <f aca="false">R17-R38</f>
-        <v>-107030.944640449</v>
+        <v>-102041.127284746</v>
       </c>
       <c r="S46" s="15" t="n">
         <f aca="false">S17-S38</f>
-        <v>-100651.311332376</v>
+        <v>-95338.7742659347</v>
       </c>
       <c r="T46" s="15" t="n">
         <f aca="false">T17-T38</f>
-        <v>-93765.3602496582</v>
+        <v>-88135.4821343241</v>
       </c>
       <c r="U46" s="15" t="n">
         <f aca="false">U17-U38</f>
-        <v>-86345.637362262</v>
+        <v>-80403.7072155168</v>
       </c>
       <c r="V46" s="15" t="n">
         <f aca="false">V17-V38</f>
-        <v>-79258.742800811</v>
+        <v>-73009.9614898449</v>
       </c>
       <c r="W46" s="15" t="n">
         <f aca="false">W17-W38</f>
-        <v>-71732.2546544061</v>
+        <v>-65181.7363652894</v>
       </c>
       <c r="X46" s="15" t="n">
         <f aca="false">X17-X38</f>
-        <v>-63716.7344283059</v>
+        <v>-56869.5081106745</v>
       </c>
       <c r="Y46" s="15" t="n">
         <f aca="false">Y17-Y38</f>
-        <v>-55248.3267586464</v>
+        <v>-48109.3375463089</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12445,87 +12445,87 @@
       </c>
       <c r="E47" s="15" t="n">
         <f aca="false">E46-E44</f>
-        <v>-140265.212426083</v>
+        <v>-140016.12909275</v>
       </c>
       <c r="F47" s="15" t="n">
         <f aca="false">F46-F44</f>
-        <v>-133310.455697209</v>
+        <v>-132671.890419431</v>
       </c>
       <c r="G47" s="15" t="n">
         <f aca="false">G46-G44</f>
-        <v>-126776.134127974</v>
+        <v>-125754.578271492</v>
       </c>
       <c r="H47" s="15" t="n">
         <f aca="false">H46-H44</f>
-        <v>-120619.197525111</v>
+        <v>-119221.034266237</v>
       </c>
       <c r="I47" s="15" t="n">
         <f aca="false">I46-I44</f>
-        <v>-114801.622569555</v>
+        <v>-113033.12869833</v>
       </c>
       <c r="J47" s="15" t="n">
         <f aca="false">J46-J44</f>
-        <v>-108420.675980322</v>
+        <v>-106288.023673617</v>
       </c>
       <c r="K47" s="15" t="n">
         <f aca="false">K46-K44</f>
-        <v>-102368.303270943</v>
+        <v>-99877.5618360159</v>
       </c>
       <c r="L47" s="15" t="n">
         <f aca="false">L46-L44</f>
-        <v>-96641.8846894208</v>
+        <v>-93799.0222784095</v>
       </c>
       <c r="M47" s="15" t="n">
         <f aca="false">M46-M44</f>
-        <v>-90358.9768220458</v>
+        <v>-87169.8621178847</v>
       </c>
       <c r="N47" s="15" t="n">
         <f aca="false">N46-N44</f>
-        <v>-134377.261534667</v>
+        <v>-130847.665408909</v>
       </c>
       <c r="O47" s="15" t="n">
         <f aca="false">O46-O44</f>
-        <v>-128710.138884048</v>
+        <v>-124845.736027052</v>
       </c>
       <c r="P47" s="15" t="n">
         <f aca="false">P46-P44</f>
-        <v>-122495.174993765</v>
+        <v>-118301.545517719</v>
       </c>
       <c r="Q47" s="15" t="n">
         <f aca="false">Q46-Q44</f>
-        <v>-116555.570172267</v>
+        <v>-112038.201187488</v>
       </c>
       <c r="R47" s="15" t="n">
         <f aca="false">R46-R44</f>
-        <v>-110100.896221662</v>
+        <v>-105265.18338663</v>
       </c>
       <c r="S47" s="15" t="n">
         <f aca="false">S46-S44</f>
-        <v>-103928.475735582</v>
+        <v>-98779.7247811333</v>
       </c>
       <c r="T47" s="15" t="n">
         <f aca="false">T46-T44</f>
-        <v>-97268.1930541854</v>
+        <v>-91811.6212823113</v>
       </c>
       <c r="U47" s="15" t="n">
         <f aca="false">U46-U44</f>
-        <v>-90091.0688486956</v>
+        <v>-84331.8066063527</v>
       </c>
       <c r="V47" s="15" t="n">
         <f aca="false">V46-V44</f>
-        <v>-83233.5684639678</v>
+        <v>-77176.6605923306</v>
       </c>
       <c r="W47" s="15" t="n">
         <f aca="false">W46-W44</f>
-        <v>-75953.2945645846</v>
+        <v>-69603.7018241414</v>
       </c>
       <c r="X47" s="15" t="n">
         <f aca="false">X46-X44</f>
-        <v>-68199.5240838896</v>
+        <v>-61562.1245557872</v>
       </c>
       <c r="Y47" s="15" t="n">
         <f aca="false">Y46-Y44</f>
-        <v>-60007.2717467218</v>
+        <v>-53086.8622107544</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12546,87 +12546,87 @@
       </c>
       <c r="E48" s="15" t="n">
         <f aca="false">E19-E38-E44</f>
-        <v>-97767.3999260833</v>
+        <v>-93026.6499260833</v>
       </c>
       <c r="F48" s="15" t="n">
         <f aca="false">F19-F38-F44</f>
-        <v>-94084.205697209</v>
+        <v>-89355.5015305423</v>
       </c>
       <c r="G48" s="15" t="n">
         <f aca="false">G19-G38-G44</f>
-        <v>-90759.9882946404</v>
+        <v>-86043.1291974182</v>
       </c>
       <c r="H48" s="15" t="n">
         <f aca="false">H19-H38-H44</f>
-        <v>-87752.7218306664</v>
+        <v>-83047.5103850645</v>
       </c>
       <c r="I48" s="15" t="n">
         <f aca="false">I19-I38-I44</f>
-        <v>-85025.3902200183</v>
+        <v>-80331.6322985098</v>
       </c>
       <c r="J48" s="15" t="n">
         <f aca="false">J19-J38-J44</f>
-        <v>-81010.7506282773</v>
+        <v>-76328.2553387939</v>
       </c>
       <c r="K48" s="15" t="n">
         <f aca="false">K19-K38-K44</f>
-        <v>-77849.5350080986</v>
+        <v>-73178.1146401067</v>
       </c>
       <c r="L48" s="15" t="n">
         <f aca="false">L19-L38-L44</f>
-        <v>-74957.7688142908</v>
+        <v>-70297.2387857654</v>
       </c>
       <c r="M48" s="15" t="n">
         <f aca="false">M19-M38-M44</f>
-        <v>-70538.887878168</v>
+        <v>-65889.0666834514</v>
       </c>
       <c r="N48" s="15" t="n">
         <f aca="false">N19-N38-N44</f>
-        <v>-117198.437614854</v>
+        <v>-112559.146773383</v>
       </c>
       <c r="O48" s="15" t="n">
         <f aca="false">O19-O38-O44</f>
-        <v>-114118.853696231</v>
+        <v>-109489.917702118</v>
       </c>
       <c r="P48" s="15" t="n">
         <f aca="false">P19-P38-P44</f>
-        <v>-109273.972684079</v>
+        <v>-104655.218956534</v>
       </c>
       <c r="Q48" s="15" t="n">
         <f aca="false">Q19-Q38-Q44</f>
-        <v>-105733.937901075</v>
+        <v>-101125.196735656</v>
       </c>
       <c r="R48" s="15" t="n">
         <f aca="false">R19-R38-R44</f>
-        <v>-100296.749488324</v>
+        <v>-95697.854008995</v>
       </c>
       <c r="S48" s="15" t="n">
         <f aca="false">S19-S38-S44</f>
-        <v>-96339.3939477991</v>
+        <v>-91750.1800597924</v>
       </c>
       <c r="T48" s="15" t="n">
         <f aca="false">T19-T38-T44</f>
-        <v>-90347.405337866</v>
+        <v>-85767.711681326</v>
       </c>
       <c r="U48" s="15" t="n">
         <f aca="false">U19-U38-U44</f>
-        <v>-83623.6275943148</v>
+        <v>-79053.2954987172</v>
       </c>
       <c r="V48" s="15" t="n">
         <f aca="false">V19-V38-V44</f>
-        <v>-78669.0856054934</v>
+        <v>-74107.9590448224</v>
       </c>
       <c r="W48" s="15" t="n">
         <f aca="false">W19-W38-W44</f>
-        <v>-71497.8655870848</v>
+        <v>-66945.7911357583</v>
       </c>
       <c r="X48" s="15" t="n">
         <f aca="false">X19-X38-X44</f>
-        <v>-63640.5897560148</v>
+        <v>-59097.4165455438</v>
       </c>
       <c r="Y48" s="15" t="n">
         <f aca="false">Y19-Y38-Y44</f>
-        <v>-55133.0425743116</v>
+        <v>-50598.6222506817</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12647,87 +12647,87 @@
       </c>
       <c r="E49" s="15" t="n">
         <f aca="false">D49+E48</f>
-        <v>106659.261073917</v>
+        <v>111400.011073917</v>
       </c>
       <c r="F49" s="15" t="n">
         <f aca="false">E49+F48</f>
-        <v>12575.0553767077</v>
+        <v>22044.5095433743</v>
       </c>
       <c r="G49" s="15" t="n">
         <f aca="false">F49+G48</f>
-        <v>-78184.9329179328</v>
+        <v>-63998.6196540439</v>
       </c>
       <c r="H49" s="15" t="n">
         <f aca="false">G49+H48</f>
-        <v>-165937.654748599</v>
+        <v>-147046.130039108</v>
       </c>
       <c r="I49" s="15" t="n">
         <f aca="false">H49+I48</f>
-        <v>-250963.044968617</v>
+        <v>-227377.762337618</v>
       </c>
       <c r="J49" s="15" t="n">
         <f aca="false">I49+J48</f>
-        <v>-331973.795596895</v>
+        <v>-303706.017676412</v>
       </c>
       <c r="K49" s="15" t="n">
         <f aca="false">J49+K48</f>
-        <v>-409823.330604993</v>
+        <v>-376884.132316519</v>
       </c>
       <c r="L49" s="15" t="n">
         <f aca="false">K49+L48</f>
-        <v>-484781.099419284</v>
+        <v>-447181.371102284</v>
       </c>
       <c r="M49" s="15" t="n">
         <f aca="false">L49+M48</f>
-        <v>-555319.987297452</v>
+        <v>-513070.437785736</v>
       </c>
       <c r="N49" s="15" t="n">
         <f aca="false">M49+N48</f>
-        <v>-672518.424912306</v>
+        <v>-625629.584559118</v>
       </c>
       <c r="O49" s="15" t="n">
         <f aca="false">N49+O48</f>
-        <v>-786637.278608538</v>
+        <v>-735119.502261236</v>
       </c>
       <c r="P49" s="15" t="n">
         <f aca="false">O49+P48</f>
-        <v>-895911.251292617</v>
+        <v>-839774.72121777</v>
       </c>
       <c r="Q49" s="15" t="n">
         <f aca="false">P49+Q48</f>
-        <v>-1001645.18919369</v>
+        <v>-940899.917953427</v>
       </c>
       <c r="R49" s="15" t="n">
         <f aca="false">Q49+R48</f>
-        <v>-1101941.93868202</v>
+        <v>-1036597.77196242</v>
       </c>
       <c r="S49" s="15" t="n">
         <f aca="false">R49+S48</f>
-        <v>-1198281.33262982</v>
+        <v>-1128347.95202221</v>
       </c>
       <c r="T49" s="15" t="n">
         <f aca="false">S49+T48</f>
-        <v>-1288628.73796768</v>
+        <v>-1214115.66370354</v>
       </c>
       <c r="U49" s="15" t="n">
         <f aca="false">T49+U48</f>
-        <v>-1372252.365562</v>
+        <v>-1293168.95920226</v>
       </c>
       <c r="V49" s="15" t="n">
         <f aca="false">U49+V48</f>
-        <v>-1450921.45116749</v>
+        <v>-1367276.91824708</v>
       </c>
       <c r="W49" s="15" t="n">
         <f aca="false">V49+W48</f>
-        <v>-1522419.31675457</v>
+        <v>-1434222.70938284</v>
       </c>
       <c r="X49" s="15" t="n">
         <f aca="false">W49+X48</f>
-        <v>-1586059.90651059</v>
+        <v>-1493320.12592838</v>
       </c>
       <c r="Y49" s="15" t="n">
         <f aca="false">X49+Y48</f>
-        <v>-1641192.9490849</v>
+        <v>-1543918.74817906</v>
       </c>
       <c r="Z49" s="8" t="s">
         <v>315</v>
@@ -13775,87 +13775,87 @@
       </c>
       <c r="E15" s="7" t="n">
         <f aca="false">E13*Допущения!$D$23/12</f>
-        <v>7500</v>
+        <v>8316.66666666667</v>
       </c>
       <c r="F15" s="7" t="n">
         <f aca="false">F13*Допущения!$D$23/12</f>
-        <v>14875</v>
+        <v>16494.7222222222</v>
       </c>
       <c r="G15" s="7" t="n">
         <f aca="false">G13*Допущения!$D$23/12</f>
-        <v>22127.0833333333</v>
+        <v>24536.4768518519</v>
       </c>
       <c r="H15" s="7" t="n">
         <f aca="false">H13*Допущения!$D$23/12</f>
-        <v>29258.2986111111</v>
+        <v>32444.2022376543</v>
       </c>
       <c r="I15" s="7" t="n">
         <f aca="false">I13*Допущения!$D$23/12</f>
-        <v>36270.6603009259</v>
+        <v>40220.1322003601</v>
       </c>
       <c r="J15" s="7" t="n">
         <f aca="false">J13*Допущения!$D$23/12</f>
-        <v>43166.1492959105</v>
+        <v>47866.4633303541</v>
       </c>
       <c r="K15" s="7" t="n">
         <f aca="false">K13*Допущения!$D$23/12</f>
-        <v>49946.713474312</v>
+        <v>55385.3556081815</v>
       </c>
       <c r="L15" s="7" t="n">
         <f aca="false">L13*Допущения!$D$23/12</f>
-        <v>56614.2682497401</v>
+        <v>62778.9330147118</v>
       </c>
       <c r="M15" s="7" t="n">
         <f aca="false">M13*Допущения!$D$23/12</f>
-        <v>63170.6971122444</v>
+        <v>70049.2841311333</v>
       </c>
       <c r="N15" s="7" t="n">
         <f aca="false">N13*Допущения!$D$23/12</f>
-        <v>69617.8521603737</v>
+        <v>77198.4627289477</v>
       </c>
       <c r="O15" s="7" t="n">
         <f aca="false">O13*Допущения!$D$23/12</f>
-        <v>75957.5546243675</v>
+        <v>84228.4883501319</v>
       </c>
       <c r="P15" s="7" t="n">
         <f aca="false">P13*Допущения!$D$23/12</f>
-        <v>82191.595380628</v>
+        <v>91141.3468776297</v>
       </c>
       <c r="Q15" s="7" t="n">
         <f aca="false">Q13*Допущения!$D$23/12</f>
-        <v>88321.7354576175</v>
+        <v>97938.9910963359</v>
       </c>
       <c r="R15" s="7" t="n">
         <f aca="false">R13*Допущения!$D$23/12</f>
-        <v>94349.7065333239</v>
+        <v>104623.34124473</v>
       </c>
       <c r="S15" s="7" t="n">
         <f aca="false">S13*Допущения!$D$23/12</f>
-        <v>100277.211424435</v>
+        <v>111196.285557318</v>
       </c>
       <c r="T15" s="7" t="n">
         <f aca="false">T13*Допущения!$D$23/12</f>
-        <v>106105.924567361</v>
+        <v>117659.680798029</v>
       </c>
       <c r="U15" s="7" t="n">
         <f aca="false">U13*Допущения!$D$23/12</f>
-        <v>111837.492491239</v>
+        <v>124015.352784729</v>
       </c>
       <c r="V15" s="7" t="n">
         <f aca="false">V13*Допущения!$D$23/12</f>
-        <v>117473.534283051</v>
+        <v>130265.096904983</v>
       </c>
       <c r="W15" s="7" t="n">
         <f aca="false">W13*Допущения!$D$23/12</f>
-        <v>123015.642045</v>
+        <v>136410.678623234</v>
       </c>
       <c r="X15" s="7" t="n">
         <f aca="false">X13*Допущения!$D$23/12</f>
-        <v>128465.38134425</v>
+        <v>142453.833979513</v>
       </c>
       <c r="Y15" s="7" t="n">
         <f aca="false">Y13*Допущения!$D$23/12</f>
-        <v>133824.29165518</v>
+        <v>148396.270079855</v>
       </c>
       <c r="Z15" s="8" t="s">
         <v>275</v>
@@ -13983,87 +13983,87 @@
       </c>
       <c r="E17" s="15" t="n">
         <f aca="false">E16+E15</f>
-        <v>15985.8175875</v>
+        <v>16802.4842541667</v>
       </c>
       <c r="F17" s="15" t="n">
         <f aca="false">F16+F15</f>
-        <v>27451.3310143167</v>
+        <v>29071.0532365389</v>
       </c>
       <c r="G17" s="15" t="n">
         <f aca="false">G16+G15</f>
-        <v>38398.1228774352</v>
+        <v>40807.5163959537</v>
       </c>
       <c r="H17" s="15" t="n">
         <f aca="false">H16+H15</f>
-        <v>48873.6672465838</v>
+        <v>52059.570873127</v>
       </c>
       <c r="I17" s="15" t="n">
         <f aca="false">I16+I15</f>
-        <v>58920.0051272034</v>
+        <v>62869.4770266375</v>
       </c>
       <c r="J17" s="15" t="n">
         <f aca="false">J16+J15</f>
-        <v>69552.3188303299</v>
+        <v>74252.6328647735</v>
       </c>
       <c r="K17" s="15" t="n">
         <f aca="false">K16+K15</f>
-        <v>79733.2103589996</v>
+        <v>85171.8524928691</v>
       </c>
       <c r="L17" s="15" t="n">
         <f aca="false">L16+L15</f>
-        <v>89502.4579339943</v>
+        <v>95667.122698966</v>
       </c>
       <c r="M17" s="15" t="n">
         <f aca="false">M16+M15</f>
-        <v>99868.7905412052</v>
+        <v>106747.377560094</v>
       </c>
       <c r="N17" s="15" t="n">
         <f aca="false">N16+N15</f>
-        <v>109800.815621063</v>
+        <v>117381.426189637</v>
       </c>
       <c r="O17" s="15" t="n">
         <f aca="false">O16+O15</f>
-        <v>119336.402548036</v>
+        <v>127607.3362738</v>
       </c>
       <c r="P17" s="15" t="n">
         <f aca="false">P16+P15</f>
-        <v>129478.1314311</v>
+        <v>138427.882928102</v>
       </c>
       <c r="Q17" s="15" t="n">
         <f aca="false">Q16+Q15</f>
-        <v>139200.852650904</v>
+        <v>148818.108289622</v>
       </c>
       <c r="R17" s="15" t="n">
         <f aca="false">R16+R15</f>
-        <v>149506.572640433</v>
+        <v>159780.207351839</v>
       </c>
       <c r="S17" s="15" t="n">
         <f aca="false">S16+S15</f>
-        <v>159377.419152398</v>
+        <v>170296.493285281</v>
       </c>
       <c r="T17" s="15" t="n">
         <f aca="false">T16+T15</f>
-        <v>169814.055767919</v>
+        <v>181367.811998588</v>
       </c>
       <c r="U17" s="15" t="n">
         <f aca="false">U16+U15</f>
-        <v>180766.46246007</v>
+        <v>192944.322753561</v>
       </c>
       <c r="V17" s="15" t="n">
         <f aca="false">V16+V15</f>
-        <v>191230.955913416</v>
+        <v>204022.518535348</v>
       </c>
       <c r="W17" s="15" t="n">
         <f aca="false">W16+W15</f>
-        <v>202209.151361783</v>
+        <v>215604.187940017</v>
       </c>
       <c r="X17" s="15" t="n">
         <f aca="false">X16+X15</f>
-        <v>213659.012524915</v>
+        <v>227647.465160178</v>
       </c>
       <c r="Y17" s="15" t="n">
         <f aca="false">Y16+Y15</f>
-        <v>225543.645430102</v>
+        <v>240115.623854777</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14188,87 +14188,87 @@
       </c>
       <c r="E19" s="7" t="n">
         <f aca="false">E16+E18-E9*Допущения!$D$10*3/24*Допущения!$D$9/12+E12*Допущения!$D$23</f>
-        <v>99733.6300875</v>
+        <v>109533.6300875</v>
       </c>
       <c r="F19" s="7" t="n">
         <f aca="false">F16+F18-F9*Допущения!$D$10*4/24*Допущения!$D$9/12+F12*Допущения!$D$23</f>
-        <v>104240.081014317</v>
+        <v>114040.081014317</v>
       </c>
       <c r="G19" s="7" t="n">
         <f aca="false">G16+G18-G9*Допущения!$D$10*5/24*Допущения!$D$9/12+G12*Допущения!$D$23</f>
-        <v>108350.727044102</v>
+        <v>118150.727044102</v>
       </c>
       <c r="H19" s="7" t="n">
         <f aca="false">H16+H18-H9*Допущения!$D$10*6/24*Допущения!$D$9/12+H12*Допущения!$D$23</f>
-        <v>112110.993635473</v>
+        <v>121910.993635473</v>
       </c>
       <c r="I19" s="7" t="n">
         <f aca="false">I16+I18-I9*Допущения!$D$10*7/24*Допущения!$D$9/12+I12*Допущения!$D$23</f>
-        <v>115560.907326277</v>
+        <v>125360.907326277</v>
       </c>
       <c r="J19" s="7" t="n">
         <f aca="false">J16+J18-J9*Допущения!$D$10*8/24*Допущения!$D$9/12+J12*Допущения!$D$23</f>
-        <v>120379.169534419</v>
+        <v>130179.169534419</v>
       </c>
       <c r="K19" s="7" t="n">
         <f aca="false">K16+K18-K9*Допущения!$D$10*9/24*Допущения!$D$9/12+K12*Допущения!$D$23</f>
-        <v>124278.621884688</v>
+        <v>134078.621884688</v>
       </c>
       <c r="L19" s="7" t="n">
         <f aca="false">L16+L18-L9*Допущения!$D$10*10/24*Допущения!$D$9/12+L12*Допущения!$D$23</f>
-        <v>127879.439684254</v>
+        <v>137679.439684254</v>
       </c>
       <c r="M19" s="7" t="n">
         <f aca="false">M16+M18-M9*Допущения!$D$10*11/24*Допущения!$D$9/12+M12*Допущения!$D$23</f>
-        <v>133103.530928961</v>
+        <v>142903.530928961</v>
       </c>
       <c r="N19" s="7" t="n">
         <f aca="false">N16+N18-N9*Допущения!$D$10*12/24*Допущения!$D$9/12+N12*Допущения!$D$23</f>
-        <v>137170.713460689</v>
+        <v>146970.713460689</v>
       </c>
       <c r="O19" s="7" t="n">
         <f aca="false">O16+O18-O9*Допущения!$D$10*13/24*Допущения!$D$9/12+O12*Допущения!$D$23</f>
-        <v>140948.910423668</v>
+        <v>150748.910423668</v>
       </c>
       <c r="P19" s="7" t="n">
         <f aca="false">P16+P18-P9*Допущения!$D$10*14/24*Допущения!$D$9/12+P12*Допущения!$D$23</f>
-        <v>146603.536050472</v>
+        <v>156403.536050472</v>
       </c>
       <c r="Q19" s="7" t="n">
         <f aca="false">Q16+Q18-Q9*Допущения!$D$10*15/24*Допущения!$D$9/12+Q12*Допущения!$D$23</f>
-        <v>150861.617193287</v>
+        <v>160661.617193287</v>
       </c>
       <c r="R19" s="7" t="n">
         <f aca="false">R16+R18-R9*Допущения!$D$10*16/24*Допущения!$D$9/12+R12*Допущения!$D$23</f>
-        <v>157135.866107109</v>
+        <v>166935.866107109</v>
       </c>
       <c r="S19" s="7" t="n">
         <f aca="false">S16+S18-S9*Допущения!$D$10*17/24*Допущения!$D$9/12+S12*Допущения!$D$23</f>
-        <v>161827.895227963</v>
+        <v>171627.895227963</v>
       </c>
       <c r="T19" s="7" t="n">
         <f aca="false">T16+T18-T9*Допущения!$D$10*18/24*Допущения!$D$9/12+T12*Допущения!$D$23</f>
-        <v>168681.881200558</v>
+        <v>178481.881200558</v>
       </c>
       <c r="U19" s="7" t="n">
         <f aca="false">U16+U18-U9*Допущения!$D$10*19/24*Допущения!$D$9/12+U12*Допущения!$D$23</f>
-        <v>176315.157468832</v>
+        <v>186115.157468832</v>
       </c>
       <c r="V19" s="7" t="n">
         <f aca="false">V16+V18-V9*Допущения!$D$10*20/24*Допущения!$D$9/12+V12*Допущения!$D$23</f>
-        <v>182058.671630365</v>
+        <v>191858.671630365</v>
       </c>
       <c r="W19" s="7" t="n">
         <f aca="false">W16+W18-W9*Допущения!$D$10*21/24*Допущения!$D$9/12+W12*Допущения!$D$23</f>
-        <v>190156.759316783</v>
+        <v>199956.759316783</v>
       </c>
       <c r="X19" s="7" t="n">
         <f aca="false">X16+X18-X9*Допущения!$D$10*22/24*Допущения!$D$9/12+X12*Допущения!$D$23</f>
-        <v>198985.256180665</v>
+        <v>208785.256180665</v>
       </c>
       <c r="Y19" s="7" t="n">
         <f aca="false">Y16+Y18-Y9*Допущения!$D$10*23/24*Допущения!$D$9/12+Y12*Допущения!$D$23</f>
-        <v>208505.728774922</v>
+        <v>218305.728774922</v>
       </c>
       <c r="Z19" s="8" t="s">
         <v>282</v>
@@ -15441,87 +15441,87 @@
       </c>
       <c r="E32" s="7" t="n">
         <f aca="false">E19*Допущения!$D$58</f>
-        <v>2992.008902625</v>
+        <v>3286.008902625</v>
       </c>
       <c r="F32" s="7" t="n">
         <f aca="false">F19*Допущения!$D$58</f>
-        <v>3127.2024304295</v>
+        <v>3421.2024304295</v>
       </c>
       <c r="G32" s="7" t="n">
         <f aca="false">G19*Допущения!$D$58</f>
-        <v>3250.52181132305</v>
+        <v>3544.52181132305</v>
       </c>
       <c r="H32" s="7" t="n">
         <f aca="false">H19*Допущения!$D$58</f>
-        <v>3363.32980906418</v>
+        <v>3657.32980906418</v>
       </c>
       <c r="I32" s="7" t="n">
         <f aca="false">I19*Допущения!$D$58</f>
-        <v>3466.82721978832</v>
+        <v>3760.82721978832</v>
       </c>
       <c r="J32" s="7" t="n">
         <f aca="false">J19*Допущения!$D$58</f>
-        <v>3611.37508603258</v>
+        <v>3905.37508603258</v>
       </c>
       <c r="K32" s="7" t="n">
         <f aca="false">K19*Допущения!$D$58</f>
-        <v>3728.35865654063</v>
+        <v>4022.35865654063</v>
       </c>
       <c r="L32" s="7" t="n">
         <f aca="false">L19*Допущения!$D$58</f>
-        <v>3836.38319052763</v>
+        <v>4130.38319052763</v>
       </c>
       <c r="M32" s="7" t="n">
         <f aca="false">M19*Допущения!$D$58</f>
-        <v>3993.10592786882</v>
+        <v>4287.10592786882</v>
       </c>
       <c r="N32" s="7" t="n">
         <f aca="false">N19*Допущения!$D$58</f>
-        <v>4115.12140382068</v>
+        <v>4409.12140382068</v>
       </c>
       <c r="O32" s="7" t="n">
         <f aca="false">O19*Допущения!$D$58</f>
-        <v>4228.46731271004</v>
+        <v>4522.46731271004</v>
       </c>
       <c r="P32" s="7" t="n">
         <f aca="false">P19*Допущения!$D$58</f>
-        <v>4398.10608151417</v>
+        <v>4692.10608151417</v>
       </c>
       <c r="Q32" s="7" t="n">
         <f aca="false">Q19*Допущения!$D$58</f>
-        <v>4525.8485157986</v>
+        <v>4819.8485157986</v>
       </c>
       <c r="R32" s="7" t="n">
         <f aca="false">R19*Допущения!$D$58</f>
-        <v>4714.07598321326</v>
+        <v>5008.07598321326</v>
       </c>
       <c r="S32" s="7" t="n">
         <f aca="false">S19*Допущения!$D$58</f>
-        <v>4854.8368568389</v>
+        <v>5148.8368568389</v>
       </c>
       <c r="T32" s="7" t="n">
         <f aca="false">T19*Допущения!$D$58</f>
-        <v>5060.45643601674</v>
+        <v>5354.45643601674</v>
       </c>
       <c r="U32" s="7" t="n">
         <f aca="false">U19*Допущения!$D$58</f>
-        <v>5289.45472406495</v>
+        <v>5583.45472406495</v>
       </c>
       <c r="V32" s="7" t="n">
         <f aca="false">V19*Допущения!$D$58</f>
-        <v>5461.76014891094</v>
+        <v>5755.76014891094</v>
       </c>
       <c r="W32" s="7" t="n">
         <f aca="false">W19*Допущения!$D$58</f>
-        <v>5704.70277950349</v>
+        <v>5998.70277950349</v>
       </c>
       <c r="X32" s="7" t="n">
         <f aca="false">X19*Допущения!$D$58</f>
-        <v>5969.55768541994</v>
+        <v>6263.55768541994</v>
       </c>
       <c r="Y32" s="7" t="n">
         <f aca="false">Y19*Допущения!$D$58</f>
-        <v>6255.17186324766</v>
+        <v>6549.17186324766</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16056,87 +16056,87 @@
       </c>
       <c r="E38" s="15" t="n">
         <f aca="false">SUM(E21:E37)</f>
-        <v>153883.955485958</v>
+        <v>154177.955485958</v>
       </c>
       <c r="F38" s="15" t="n">
         <f aca="false">SUM(F21:F37)</f>
-        <v>154867.20511443</v>
+        <v>155161.20511443</v>
       </c>
       <c r="G38" s="15" t="n">
         <f aca="false">SUM(G21:G37)</f>
-        <v>155820.78901353</v>
+        <v>156114.78901353</v>
       </c>
       <c r="H38" s="15" t="n">
         <f aca="false">SUM(H21:H37)</f>
-        <v>156746.822520501</v>
+        <v>157040.822520501</v>
       </c>
       <c r="I38" s="15" t="n">
         <f aca="false">SUM(I21:I37)</f>
-        <v>157647.192513043</v>
+        <v>157941.192513043</v>
       </c>
       <c r="J38" s="15" t="n">
         <f aca="false">SUM(J21:J37)</f>
-        <v>158603.037466341</v>
+        <v>158897.037466341</v>
       </c>
       <c r="K38" s="15" t="n">
         <f aca="false">SUM(K21:K37)</f>
-        <v>159499.186002761</v>
+        <v>159793.186002761</v>
       </c>
       <c r="L38" s="15" t="n">
         <f aca="false">SUM(L21:L37)</f>
-        <v>160370.776424257</v>
+        <v>160664.776424257</v>
       </c>
       <c r="M38" s="15" t="n">
         <f aca="false">SUM(M21:M37)</f>
-        <v>161313.019393563</v>
+        <v>161607.019393563</v>
       </c>
       <c r="N38" s="15" t="n">
         <f aca="false">SUM(N21:N37)</f>
-        <v>212182.346504537</v>
+        <v>212476.346504537</v>
       </c>
       <c r="O38" s="15" t="n">
         <f aca="false">SUM(O21:O37)</f>
-        <v>213028.10494279</v>
+        <v>213322.10494279</v>
       </c>
       <c r="P38" s="15" t="n">
         <f aca="false">SUM(P21:P37)</f>
-        <v>213959.590475961</v>
+        <v>214253.590475961</v>
       </c>
       <c r="Q38" s="15" t="n">
         <f aca="false">SUM(Q21:Q37)</f>
-        <v>214804.848104439</v>
+        <v>215098.848104439</v>
       </c>
       <c r="R38" s="15" t="n">
         <f aca="false">SUM(R21:R37)</f>
-        <v>215744.648362663</v>
+        <v>216038.648362663</v>
       </c>
       <c r="S38" s="15" t="n">
         <f aca="false">SUM(S21:S37)</f>
-        <v>216588.242715194</v>
+        <v>216882.242715194</v>
       </c>
       <c r="T38" s="15" t="n">
         <f aca="false">SUM(T21:T37)</f>
-        <v>217535.43637749</v>
+        <v>217829.43637749</v>
       </c>
       <c r="U38" s="15" t="n">
         <f aca="false">SUM(U21:U37)</f>
-        <v>218508.019842913</v>
+        <v>218802.019842913</v>
       </c>
       <c r="V38" s="15" t="n">
         <f aca="false">SUM(V21:V37)</f>
-        <v>219368.186734464</v>
+        <v>219662.186734464</v>
       </c>
       <c r="W38" s="15" t="n">
         <f aca="false">SUM(W21:W37)</f>
-        <v>220344.419236089</v>
+        <v>220638.419236089</v>
       </c>
       <c r="X38" s="15" t="n">
         <f aca="false">SUM(X21:X37)</f>
-        <v>221344.543286122</v>
+        <v>221638.543286122</v>
       </c>
       <c r="Y38" s="15" t="n">
         <f aca="false">SUM(Y21:Y37)</f>
-        <v>222367.121916101</v>
+        <v>222661.121916101</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16186,87 +16186,87 @@
       </c>
       <c r="E40" s="7" t="n">
         <f aca="false">SUM($E$17:E17)</f>
-        <v>15985.8175875</v>
+        <v>16802.4842541667</v>
       </c>
       <c r="F40" s="7" t="n">
         <f aca="false">SUM($E$17:F17)</f>
-        <v>43437.1486018167</v>
+        <v>45873.5374907056</v>
       </c>
       <c r="G40" s="7" t="n">
         <f aca="false">SUM($E$17:G17)</f>
-        <v>81835.2714792518</v>
+        <v>86681.0538866592</v>
       </c>
       <c r="H40" s="7" t="n">
         <f aca="false">SUM($E$17:H17)</f>
-        <v>130708.938725836</v>
+        <v>138740.624759786</v>
       </c>
       <c r="I40" s="7" t="n">
         <f aca="false">SUM($E$17:I17)</f>
-        <v>189628.943853039</v>
+        <v>201610.101786424</v>
       </c>
       <c r="J40" s="7" t="n">
         <f aca="false">SUM($E$17:J17)</f>
-        <v>259181.262683369</v>
+        <v>275862.734651197</v>
       </c>
       <c r="K40" s="7" t="n">
         <f aca="false">SUM($E$17:K17)</f>
-        <v>338914.473042369</v>
+        <v>361034.587144066</v>
       </c>
       <c r="L40" s="7" t="n">
         <f aca="false">SUM($E$17:L17)</f>
-        <v>428416.930976363</v>
+        <v>456701.709843032</v>
       </c>
       <c r="M40" s="7" t="n">
         <f aca="false">SUM($E$17:M17)</f>
-        <v>528285.721517568</v>
+        <v>563449.087403126</v>
       </c>
       <c r="N40" s="7" t="n">
         <f aca="false">SUM($E$17:N17)</f>
-        <v>638086.537138631</v>
+        <v>680830.513592764</v>
       </c>
       <c r="O40" s="7" t="n">
         <f aca="false">SUM($E$17:O17)</f>
-        <v>757422.939686667</v>
+        <v>808437.849866564</v>
       </c>
       <c r="P40" s="7" t="n">
         <f aca="false">SUM($E$17:P17)</f>
-        <v>886901.071117767</v>
+        <v>946865.732794665</v>
       </c>
       <c r="Q40" s="7" t="n">
         <f aca="false">SUM($E$17:Q17)</f>
-        <v>1026101.92376867</v>
+        <v>1095683.84108429</v>
       </c>
       <c r="R40" s="7" t="n">
         <f aca="false">SUM($E$17:R17)</f>
-        <v>1175608.4964091</v>
+        <v>1255464.04843613</v>
       </c>
       <c r="S40" s="7" t="n">
         <f aca="false">SUM($E$17:S17)</f>
-        <v>1334985.9155615</v>
+        <v>1425760.54172141</v>
       </c>
       <c r="T40" s="7" t="n">
         <f aca="false">SUM($E$17:T17)</f>
-        <v>1504799.97132942</v>
+        <v>1607128.35372</v>
       </c>
       <c r="U40" s="7" t="n">
         <f aca="false">SUM($E$17:U17)</f>
-        <v>1685566.43378949</v>
+        <v>1800072.67647356</v>
       </c>
       <c r="V40" s="7" t="n">
         <f aca="false">SUM($E$17:V17)</f>
-        <v>1876797.38970291</v>
+        <v>2004095.1950089</v>
       </c>
       <c r="W40" s="7" t="n">
         <f aca="false">SUM($E$17:W17)</f>
-        <v>2079006.54106469</v>
+        <v>2219699.38294892</v>
       </c>
       <c r="X40" s="7" t="n">
         <f aca="false">SUM($E$17:X17)</f>
-        <v>2292665.55358961</v>
+        <v>2447346.8481091</v>
       </c>
       <c r="Y40" s="7" t="n">
         <f aca="false">SUM($E$17:Y17)</f>
-        <v>2518209.19901971</v>
+        <v>2687462.47196388</v>
       </c>
       <c r="Z40" s="8" t="s">
         <v>303</v>
@@ -16394,87 +16394,87 @@
       </c>
       <c r="E42" s="7" t="n">
         <f aca="false">E17-E38-E41</f>
-        <v>-137898.137898458</v>
+        <v>-137375.471231792</v>
       </c>
       <c r="F42" s="7" t="n">
         <f aca="false">F17-F38-F41</f>
-        <v>-127415.874100113</v>
+        <v>-126090.151877891</v>
       </c>
       <c r="G42" s="7" t="n">
         <f aca="false">G17-G38-G41</f>
-        <v>-117422.666136095</v>
+        <v>-115307.272617577</v>
       </c>
       <c r="H42" s="7" t="n">
         <f aca="false">H17-H38-H41</f>
-        <v>-107873.155273917</v>
+        <v>-104981.251647374</v>
       </c>
       <c r="I42" s="7" t="n">
         <f aca="false">I17-I38-I41</f>
-        <v>-98727.1873858396</v>
+        <v>-95071.7154864054</v>
       </c>
       <c r="J42" s="7" t="n">
         <f aca="false">J17-J38-J41</f>
-        <v>-89050.7186360107</v>
+        <v>-84644.4046015672</v>
       </c>
       <c r="K42" s="7" t="n">
         <f aca="false">K17-K38-K41</f>
-        <v>-79765.9756437613</v>
+        <v>-74621.3335098918</v>
       </c>
       <c r="L42" s="7" t="n">
         <f aca="false">L17-L38-L41</f>
-        <v>-70868.3184902632</v>
+        <v>-64997.6537252915</v>
       </c>
       <c r="M42" s="7" t="n">
         <f aca="false">M17-M38-M41</f>
-        <v>-61444.2288523575</v>
+        <v>-54859.6418334686</v>
       </c>
       <c r="N42" s="7" t="n">
         <f aca="false">N17-N38-N41</f>
-        <v>-102381.530883474</v>
+        <v>-95094.9203149001</v>
       </c>
       <c r="O42" s="7" t="n">
         <f aca="false">O17-O38-O41</f>
-        <v>-93691.7023947545</v>
+        <v>-85714.7686689901</v>
       </c>
       <c r="P42" s="7" t="n">
         <f aca="false">P17-P38-P41</f>
-        <v>-84481.4590448611</v>
+        <v>-75825.7075478594</v>
       </c>
       <c r="Q42" s="7" t="n">
         <f aca="false">Q17-Q38-Q41</f>
-        <v>-75603.9954535346</v>
+        <v>-66280.7398148163</v>
       </c>
       <c r="R42" s="7" t="n">
         <f aca="false">R17-R38-R41</f>
-        <v>-66238.0757222308</v>
+        <v>-56258.4410108244</v>
       </c>
       <c r="S42" s="7" t="n">
         <f aca="false">S17-S38-S41</f>
-        <v>-57210.8235627951</v>
+        <v>-46585.7494299122</v>
       </c>
       <c r="T42" s="7" t="n">
         <f aca="false">T17-T38-T41</f>
-        <v>-47721.3806095702</v>
+        <v>-36461.624378902</v>
       </c>
       <c r="U42" s="7" t="n">
         <f aca="false">U17-U38-U41</f>
-        <v>-37741.5573828422</v>
+        <v>-25857.6970893518</v>
       </c>
       <c r="V42" s="7" t="n">
         <f aca="false">V17-V38-V41</f>
-        <v>-28137.2308210482</v>
+        <v>-15639.6681991159</v>
       </c>
       <c r="W42" s="7" t="n">
         <f aca="false">W17-W38-W41</f>
-        <v>-18135.267874306</v>
+        <v>-5034.23129607257</v>
       </c>
       <c r="X42" s="7" t="n">
         <f aca="false">X17-X38-X41</f>
-        <v>-7685.53076120748</v>
+        <v>6008.92187405538</v>
       </c>
       <c r="Y42" s="7" t="n">
         <f aca="false">Y17-Y38-Y41</f>
-        <v>3176.52351400041</v>
+        <v>17454.5019386755</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16495,87 +16495,87 @@
       </c>
       <c r="E43" s="7" t="n">
         <f aca="false">MAX(E42*Допущения!$D$51,E17*Допущения!$D$52)</f>
-        <v>479.574527625</v>
+        <v>504.074527625</v>
       </c>
       <c r="F43" s="7" t="n">
         <f aca="false">MAX(F42*Допущения!$D$51,F17*Допущения!$D$52)</f>
-        <v>823.5399304295</v>
+        <v>872.131597096167</v>
       </c>
       <c r="G43" s="7" t="n">
         <f aca="false">MAX(G42*Допущения!$D$51,G17*Допущения!$D$52)</f>
-        <v>1151.94368632305</v>
+        <v>1224.22549187861</v>
       </c>
       <c r="H43" s="7" t="n">
         <f aca="false">MAX(H42*Допущения!$D$51,H17*Допущения!$D$52)</f>
-        <v>1466.21001739751</v>
+        <v>1561.78712619381</v>
       </c>
       <c r="I43" s="7" t="n">
         <f aca="false">MAX(I42*Допущения!$D$51,I17*Допущения!$D$52)</f>
-        <v>1767.6001538161</v>
+        <v>1886.08431079913</v>
       </c>
       <c r="J43" s="7" t="n">
         <f aca="false">MAX(J42*Допущения!$D$51,J17*Допущения!$D$52)</f>
-        <v>2086.5695649099</v>
+        <v>2227.57898594321</v>
       </c>
       <c r="K43" s="7" t="n">
         <f aca="false">MAX(K42*Допущения!$D$51,K17*Допущения!$D$52)</f>
-        <v>2391.99631076999</v>
+        <v>2555.15557478607</v>
       </c>
       <c r="L43" s="7" t="n">
         <f aca="false">MAX(L42*Допущения!$D$51,L17*Допущения!$D$52)</f>
-        <v>2685.07373801983</v>
+        <v>2870.01368096898</v>
       </c>
       <c r="M43" s="7" t="n">
         <f aca="false">MAX(M42*Допущения!$D$51,M17*Допущения!$D$52)</f>
-        <v>2996.06371623615</v>
+        <v>3202.42132680282</v>
       </c>
       <c r="N43" s="7" t="n">
         <f aca="false">MAX(N42*Допущения!$D$51,N17*Допущения!$D$52)</f>
-        <v>3294.02446863189</v>
+        <v>3521.44278568911</v>
       </c>
       <c r="O43" s="7" t="n">
         <f aca="false">MAX(O42*Допущения!$D$51,O17*Допущения!$D$52)</f>
-        <v>3580.09207644107</v>
+        <v>3828.220088214</v>
       </c>
       <c r="P43" s="7" t="n">
         <f aca="false">MAX(P42*Допущения!$D$51,P17*Допущения!$D$52)</f>
-        <v>3884.34394293301</v>
+        <v>4152.83648784306</v>
       </c>
       <c r="Q43" s="7" t="n">
         <f aca="false">MAX(Q42*Допущения!$D$51,Q17*Допущения!$D$52)</f>
-        <v>4176.02557952712</v>
+        <v>4464.54324868867</v>
       </c>
       <c r="R43" s="7" t="n">
         <f aca="false">MAX(R42*Допущения!$D$51,R17*Допущения!$D$52)</f>
-        <v>4485.19717921298</v>
+        <v>4793.40622055517</v>
       </c>
       <c r="S43" s="7" t="n">
         <f aca="false">MAX(S42*Допущения!$D$51,S17*Допущения!$D$52)</f>
-        <v>4781.32257457195</v>
+        <v>5108.89479855844</v>
       </c>
       <c r="T43" s="7" t="n">
         <f aca="false">MAX(T42*Допущения!$D$51,T17*Допущения!$D$52)</f>
-        <v>5094.42167303758</v>
+        <v>5441.03435995763</v>
       </c>
       <c r="U43" s="7" t="n">
         <f aca="false">MAX(U42*Допущения!$D$51,U17*Допущения!$D$52)</f>
-        <v>5422.99387380211</v>
+        <v>5788.32968260682</v>
       </c>
       <c r="V43" s="7" t="n">
         <f aca="false">MAX(V42*Допущения!$D$51,V17*Допущения!$D$52)</f>
-        <v>5736.92867740248</v>
+        <v>6120.67555606044</v>
       </c>
       <c r="W43" s="7" t="n">
         <f aca="false">MAX(W42*Допущения!$D$51,W17*Допущения!$D$52)</f>
-        <v>6066.2745408535</v>
+        <v>6468.1256382005</v>
       </c>
       <c r="X43" s="7" t="n">
         <f aca="false">MAX(X42*Допущения!$D$51,X17*Допущения!$D$52)</f>
-        <v>6409.77037574745</v>
+        <v>6829.42395480534</v>
       </c>
       <c r="Y43" s="7" t="n">
         <f aca="false">MAX(Y42*Допущения!$D$51,Y17*Допущения!$D$52)</f>
-        <v>6766.30936290305</v>
+        <v>7203.4687156433</v>
       </c>
       <c r="Z43" s="8" t="s">
         <v>308</v>
@@ -16599,87 +16599,87 @@
       </c>
       <c r="E44" s="15" t="n">
         <f aca="false">E41+E43</f>
-        <v>479.574527625</v>
+        <v>504.074527625</v>
       </c>
       <c r="F44" s="15" t="n">
         <f aca="false">F41+F43</f>
-        <v>823.5399304295</v>
+        <v>872.131597096167</v>
       </c>
       <c r="G44" s="15" t="n">
         <f aca="false">G41+G43</f>
-        <v>1151.94368632305</v>
+        <v>1224.22549187861</v>
       </c>
       <c r="H44" s="15" t="n">
         <f aca="false">H41+H43</f>
-        <v>1466.21001739751</v>
+        <v>1561.78712619381</v>
       </c>
       <c r="I44" s="15" t="n">
         <f aca="false">I41+I43</f>
-        <v>1767.6001538161</v>
+        <v>1886.08431079913</v>
       </c>
       <c r="J44" s="15" t="n">
         <f aca="false">J41+J43</f>
-        <v>2086.5695649099</v>
+        <v>2227.57898594321</v>
       </c>
       <c r="K44" s="15" t="n">
         <f aca="false">K41+K43</f>
-        <v>2391.99631076999</v>
+        <v>2555.15557478607</v>
       </c>
       <c r="L44" s="15" t="n">
         <f aca="false">L41+L43</f>
-        <v>2685.07373801983</v>
+        <v>2870.01368096898</v>
       </c>
       <c r="M44" s="15" t="n">
         <f aca="false">M41+M43</f>
-        <v>2996.06371623615</v>
+        <v>3202.42132680282</v>
       </c>
       <c r="N44" s="15" t="n">
         <f aca="false">N41+N43</f>
-        <v>3294.02446863189</v>
+        <v>3521.44278568911</v>
       </c>
       <c r="O44" s="15" t="n">
         <f aca="false">O41+O43</f>
-        <v>3580.09207644107</v>
+        <v>3828.220088214</v>
       </c>
       <c r="P44" s="15" t="n">
         <f aca="false">P41+P43</f>
-        <v>3884.34394293301</v>
+        <v>4152.83648784306</v>
       </c>
       <c r="Q44" s="15" t="n">
         <f aca="false">Q41+Q43</f>
-        <v>4176.02557952712</v>
+        <v>4464.54324868867</v>
       </c>
       <c r="R44" s="15" t="n">
         <f aca="false">R41+R43</f>
-        <v>4485.19717921298</v>
+        <v>4793.40622055517</v>
       </c>
       <c r="S44" s="15" t="n">
         <f aca="false">S41+S43</f>
-        <v>4781.32257457195</v>
+        <v>5108.89479855844</v>
       </c>
       <c r="T44" s="15" t="n">
         <f aca="false">T41+T43</f>
-        <v>5094.42167303758</v>
+        <v>5441.03435995763</v>
       </c>
       <c r="U44" s="15" t="n">
         <f aca="false">U41+U43</f>
-        <v>5422.99387380211</v>
+        <v>5788.32968260682</v>
       </c>
       <c r="V44" s="15" t="n">
         <f aca="false">V41+V43</f>
-        <v>5736.92867740248</v>
+        <v>6120.67555606044</v>
       </c>
       <c r="W44" s="15" t="n">
         <f aca="false">W41+W43</f>
-        <v>6066.2745408535</v>
+        <v>6468.1256382005</v>
       </c>
       <c r="X44" s="15" t="n">
         <f aca="false">X41+X43</f>
-        <v>6409.77037574745</v>
+        <v>6829.42395480534</v>
       </c>
       <c r="Y44" s="15" t="n">
         <f aca="false">Y41+Y43</f>
-        <v>6766.30936290305</v>
+        <v>7203.4687156433</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16729,87 +16729,87 @@
       </c>
       <c r="E46" s="15" t="n">
         <f aca="false">E17-E38</f>
-        <v>-137898.137898458</v>
+        <v>-137375.471231792</v>
       </c>
       <c r="F46" s="15" t="n">
         <f aca="false">F17-F38</f>
-        <v>-127415.874100113</v>
+        <v>-126090.151877891</v>
       </c>
       <c r="G46" s="15" t="n">
         <f aca="false">G17-G38</f>
-        <v>-117422.666136095</v>
+        <v>-115307.272617577</v>
       </c>
       <c r="H46" s="15" t="n">
         <f aca="false">H17-H38</f>
-        <v>-107873.155273917</v>
+        <v>-104981.251647374</v>
       </c>
       <c r="I46" s="15" t="n">
         <f aca="false">I17-I38</f>
-        <v>-98727.1873858396</v>
+        <v>-95071.7154864054</v>
       </c>
       <c r="J46" s="15" t="n">
         <f aca="false">J17-J38</f>
-        <v>-89050.7186360107</v>
+        <v>-84644.4046015672</v>
       </c>
       <c r="K46" s="15" t="n">
         <f aca="false">K17-K38</f>
-        <v>-79765.9756437613</v>
+        <v>-74621.3335098918</v>
       </c>
       <c r="L46" s="15" t="n">
         <f aca="false">L17-L38</f>
-        <v>-70868.3184902632</v>
+        <v>-64997.6537252915</v>
       </c>
       <c r="M46" s="15" t="n">
         <f aca="false">M17-M38</f>
-        <v>-61444.2288523575</v>
+        <v>-54859.6418334686</v>
       </c>
       <c r="N46" s="15" t="n">
         <f aca="false">N17-N38</f>
-        <v>-102381.530883474</v>
+        <v>-95094.9203149001</v>
       </c>
       <c r="O46" s="15" t="n">
         <f aca="false">O17-O38</f>
-        <v>-93691.7023947545</v>
+        <v>-85714.7686689901</v>
       </c>
       <c r="P46" s="15" t="n">
         <f aca="false">P17-P38</f>
-        <v>-84481.4590448611</v>
+        <v>-75825.7075478594</v>
       </c>
       <c r="Q46" s="15" t="n">
         <f aca="false">Q17-Q38</f>
-        <v>-75603.9954535346</v>
+        <v>-66280.7398148163</v>
       </c>
       <c r="R46" s="15" t="n">
         <f aca="false">R17-R38</f>
-        <v>-66238.0757222308</v>
+        <v>-56258.4410108244</v>
       </c>
       <c r="S46" s="15" t="n">
         <f aca="false">S17-S38</f>
-        <v>-57210.8235627951</v>
+        <v>-46585.7494299122</v>
       </c>
       <c r="T46" s="15" t="n">
         <f aca="false">T17-T38</f>
-        <v>-47721.3806095702</v>
+        <v>-36461.624378902</v>
       </c>
       <c r="U46" s="15" t="n">
         <f aca="false">U17-U38</f>
-        <v>-37741.5573828422</v>
+        <v>-25857.6970893518</v>
       </c>
       <c r="V46" s="15" t="n">
         <f aca="false">V17-V38</f>
-        <v>-28137.2308210482</v>
+        <v>-15639.6681991159</v>
       </c>
       <c r="W46" s="15" t="n">
         <f aca="false">W17-W38</f>
-        <v>-18135.267874306</v>
+        <v>-5034.23129607257</v>
       </c>
       <c r="X46" s="15" t="n">
         <f aca="false">X17-X38</f>
-        <v>-7685.53076120748</v>
+        <v>6008.92187405538</v>
       </c>
       <c r="Y46" s="15" t="n">
         <f aca="false">Y17-Y38</f>
-        <v>3176.52351400041</v>
+        <v>17454.5019386755</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16830,87 +16830,87 @@
       </c>
       <c r="E47" s="15" t="n">
         <f aca="false">E46-E44</f>
-        <v>-138377.712426083</v>
+        <v>-137879.545759417</v>
       </c>
       <c r="F47" s="15" t="n">
         <f aca="false">F46-F44</f>
-        <v>-128239.414030542</v>
+        <v>-126962.283474987</v>
       </c>
       <c r="G47" s="15" t="n">
         <f aca="false">G46-G44</f>
-        <v>-118574.609822418</v>
+        <v>-116531.498109455</v>
       </c>
       <c r="H47" s="15" t="n">
         <f aca="false">H46-H44</f>
-        <v>-109339.365291315</v>
+        <v>-106543.038773568</v>
       </c>
       <c r="I47" s="15" t="n">
         <f aca="false">I46-I44</f>
-        <v>-100494.787539656</v>
+        <v>-96957.7997972045</v>
       </c>
       <c r="J47" s="15" t="n">
         <f aca="false">J46-J44</f>
-        <v>-91137.2882009206</v>
+        <v>-86871.9835875104</v>
       </c>
       <c r="K47" s="15" t="n">
         <f aca="false">K46-K44</f>
-        <v>-82157.9719545313</v>
+        <v>-77176.4890846779</v>
       </c>
       <c r="L47" s="15" t="n">
         <f aca="false">L46-L44</f>
-        <v>-73553.392228283</v>
+        <v>-67867.6674062604</v>
       </c>
       <c r="M47" s="15" t="n">
         <f aca="false">M46-M44</f>
-        <v>-64440.2925685936</v>
+        <v>-58062.0631602715</v>
       </c>
       <c r="N47" s="15" t="n">
         <f aca="false">N46-N44</f>
-        <v>-105675.555352106</v>
+        <v>-98616.3631005892</v>
       </c>
       <c r="O47" s="15" t="n">
         <f aca="false">O46-O44</f>
-        <v>-97271.7944711956</v>
+        <v>-89542.9887572041</v>
       </c>
       <c r="P47" s="15" t="n">
         <f aca="false">P46-P44</f>
-        <v>-88365.8029877941</v>
+        <v>-79978.5440357025</v>
       </c>
       <c r="Q47" s="15" t="n">
         <f aca="false">Q46-Q44</f>
-        <v>-79780.0210330617</v>
+        <v>-70745.2830635049</v>
       </c>
       <c r="R47" s="15" t="n">
         <f aca="false">R46-R44</f>
-        <v>-70723.2729014438</v>
+        <v>-61051.8472313796</v>
       </c>
       <c r="S47" s="15" t="n">
         <f aca="false">S46-S44</f>
-        <v>-61992.146137367</v>
+        <v>-51694.6442284706</v>
       </c>
       <c r="T47" s="15" t="n">
         <f aca="false">T46-T44</f>
-        <v>-52815.8022826078</v>
+        <v>-41902.6587388596</v>
       </c>
       <c r="U47" s="15" t="n">
         <f aca="false">U46-U44</f>
-        <v>-43164.5512566443</v>
+        <v>-31646.0267719586</v>
       </c>
       <c r="V47" s="15" t="n">
         <f aca="false">V46-V44</f>
-        <v>-33874.1594984507</v>
+        <v>-21760.3437551764</v>
       </c>
       <c r="W47" s="15" t="n">
         <f aca="false">W46-W44</f>
-        <v>-24201.5424151595</v>
+        <v>-11502.3569342731</v>
       </c>
       <c r="X47" s="15" t="n">
         <f aca="false">X46-X44</f>
-        <v>-14095.3011369549</v>
+        <v>-820.502080749958</v>
       </c>
       <c r="Y47" s="15" t="n">
         <f aca="false">Y46-Y44</f>
-        <v>-3589.78584890264</v>
+        <v>10251.0332230322</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16931,87 +16931,87 @@
       </c>
       <c r="E48" s="15" t="n">
         <f aca="false">E19-E38-E44</f>
-        <v>-54629.8999260833</v>
+        <v>-45148.3999260833</v>
       </c>
       <c r="F48" s="15" t="n">
         <f aca="false">F19-F38-F44</f>
-        <v>-51450.6640305423</v>
+        <v>-41993.255697209</v>
       </c>
       <c r="G48" s="15" t="n">
         <f aca="false">G19-G38-G44</f>
-        <v>-48622.0056557515</v>
+        <v>-39188.2874613071</v>
       </c>
       <c r="H48" s="15" t="n">
         <f aca="false">H19-H38-H44</f>
-        <v>-46102.0389024257</v>
+        <v>-36691.6160112219</v>
       </c>
       <c r="I48" s="15" t="n">
         <f aca="false">I19-I38-I44</f>
-        <v>-43853.8853405816</v>
+        <v>-34466.3694975646</v>
       </c>
       <c r="J48" s="15" t="n">
         <f aca="false">J19-J38-J44</f>
-        <v>-40310.4374968311</v>
+        <v>-30945.4469178644</v>
       </c>
       <c r="K48" s="15" t="n">
         <f aca="false">K19-K38-K44</f>
-        <v>-37612.5604288433</v>
+        <v>-28269.7196928594</v>
       </c>
       <c r="L48" s="15" t="n">
         <f aca="false">L19-L38-L44</f>
-        <v>-35176.4104780231</v>
+        <v>-25855.3504209722</v>
       </c>
       <c r="M48" s="15" t="n">
         <f aca="false">M19-M38-M44</f>
-        <v>-31205.5521808381</v>
+        <v>-21905.9097914047</v>
       </c>
       <c r="N48" s="15" t="n">
         <f aca="false">N19-N38-N44</f>
-        <v>-78305.6575124797</v>
+        <v>-69027.0758295369</v>
       </c>
       <c r="O48" s="15" t="n">
         <f aca="false">O19-O38-O44</f>
-        <v>-75659.2865955631</v>
+        <v>-66401.414607336</v>
       </c>
       <c r="P48" s="15" t="n">
         <f aca="false">P19-P38-P44</f>
-        <v>-71240.3983684221</v>
+        <v>-62002.8909133322</v>
       </c>
       <c r="Q48" s="15" t="n">
         <f aca="false">Q19-Q38-Q44</f>
-        <v>-68119.2564906792</v>
+        <v>-58901.7741598408</v>
       </c>
       <c r="R48" s="15" t="n">
         <f aca="false">R19-R38-R44</f>
-        <v>-63093.9794347677</v>
+        <v>-53896.1884761099</v>
       </c>
       <c r="S48" s="15" t="n">
         <f aca="false">S19-S38-S44</f>
-        <v>-59541.6700618022</v>
+        <v>-50363.2422857887</v>
       </c>
       <c r="T48" s="15" t="n">
         <f aca="false">T19-T38-T44</f>
-        <v>-53947.976849969</v>
+        <v>-44788.589536889</v>
       </c>
       <c r="U48" s="15" t="n">
         <f aca="false">U19-U38-U44</f>
-        <v>-47615.8562478828</v>
+        <v>-38475.1920566875</v>
       </c>
       <c r="V48" s="15" t="n">
         <f aca="false">V19-V38-V44</f>
-        <v>-43046.4437815019</v>
+        <v>-33924.1906601598</v>
       </c>
       <c r="W48" s="15" t="n">
         <f aca="false">W19-W38-W44</f>
-        <v>-36253.9344601598</v>
+        <v>-27149.7855575068</v>
       </c>
       <c r="X48" s="15" t="n">
         <f aca="false">X19-X38-X44</f>
-        <v>-28769.0574812053</v>
+        <v>-19682.7110602632</v>
       </c>
       <c r="Y48" s="15" t="n">
         <f aca="false">Y19-Y38-Y44</f>
-        <v>-20627.7025040822</v>
+        <v>-11558.8618568224</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17032,87 +17032,87 @@
       </c>
       <c r="E49" s="15" t="n">
         <f aca="false">D49+E48</f>
-        <v>149796.761073917</v>
+        <v>159278.261073917</v>
       </c>
       <c r="F49" s="15" t="n">
         <f aca="false">E49+F48</f>
-        <v>98346.0970433744</v>
+        <v>117285.005376708</v>
       </c>
       <c r="G49" s="15" t="n">
         <f aca="false">F49+G48</f>
-        <v>49724.0913876228</v>
+        <v>78096.7179154006</v>
       </c>
       <c r="H49" s="15" t="n">
         <f aca="false">G49+H48</f>
-        <v>3622.05248519719</v>
+        <v>41405.1019041787</v>
       </c>
       <c r="I49" s="15" t="n">
         <f aca="false">H49+I48</f>
-        <v>-40231.8328553844</v>
+        <v>6938.73240661406</v>
       </c>
       <c r="J49" s="15" t="n">
         <f aca="false">I49+J48</f>
-        <v>-80542.2703522155</v>
+        <v>-24006.7145112504</v>
       </c>
       <c r="K49" s="15" t="n">
         <f aca="false">J49+K48</f>
-        <v>-118154.830781059</v>
+        <v>-52276.4342041097</v>
       </c>
       <c r="L49" s="15" t="n">
         <f aca="false">K49+L48</f>
-        <v>-153331.241259082</v>
+        <v>-78131.784625082</v>
       </c>
       <c r="M49" s="15" t="n">
         <f aca="false">L49+M48</f>
-        <v>-184536.79343992</v>
+        <v>-100037.694416487</v>
       </c>
       <c r="N49" s="15" t="n">
         <f aca="false">M49+N48</f>
-        <v>-262842.4509524</v>
+        <v>-169064.770246024</v>
       </c>
       <c r="O49" s="15" t="n">
         <f aca="false">N49+O48</f>
-        <v>-338501.737547963</v>
+        <v>-235466.18485336</v>
       </c>
       <c r="P49" s="15" t="n">
         <f aca="false">O49+P48</f>
-        <v>-409742.135916385</v>
+        <v>-297469.075766692</v>
       </c>
       <c r="Q49" s="15" t="n">
         <f aca="false">P49+Q48</f>
-        <v>-477861.392407064</v>
+        <v>-356370.849926533</v>
       </c>
       <c r="R49" s="15" t="n">
         <f aca="false">Q49+R48</f>
-        <v>-540955.371841832</v>
+        <v>-410267.038402642</v>
       </c>
       <c r="S49" s="15" t="n">
         <f aca="false">R49+S48</f>
-        <v>-600497.041903634</v>
+        <v>-460630.280688431</v>
       </c>
       <c r="T49" s="15" t="n">
         <f aca="false">S49+T48</f>
-        <v>-654445.018753603</v>
+        <v>-505418.87022532</v>
       </c>
       <c r="U49" s="15" t="n">
         <f aca="false">T49+U48</f>
-        <v>-702060.875001486</v>
+        <v>-543894.062282008</v>
       </c>
       <c r="V49" s="15" t="n">
         <f aca="false">U49+V48</f>
-        <v>-745107.318782988</v>
+        <v>-577818.252942168</v>
       </c>
       <c r="W49" s="15" t="n">
         <f aca="false">V49+W48</f>
-        <v>-781361.253243147</v>
+        <v>-604968.038499674</v>
       </c>
       <c r="X49" s="15" t="n">
         <f aca="false">W49+X48</f>
-        <v>-810130.310724353</v>
+        <v>-624650.749559938</v>
       </c>
       <c r="Y49" s="15" t="n">
         <f aca="false">X49+Y48</f>
-        <v>-830758.013228435</v>
+        <v>-636209.61141676</v>
       </c>
       <c r="Z49" s="8" t="s">
         <v>315</v>

--- a/finance/Компас_финмодель_24м.xlsx
+++ b/finance/Компас_финмодель_24м.xlsx
@@ -455,7 +455,7 @@
     <t xml:space="preserve">Первый этап — по какой месяц включительно</t>
   </si>
   <si>
-    <t xml:space="preserve">Месяцы с 4-го по 12-й.</t>
+    <t xml:space="preserve">Месяцы с 7-го по 12-й.</t>
   </si>
   <si>
     <t xml:space="preserve">Разработчик, ₽ в месяц — с 13-го месяца</t>
@@ -704,7 +704,7 @@
     <t xml:space="preserve">Разработчик</t>
   </si>
   <si>
-    <t xml:space="preserve">Три месяца без разработчика, девять по 50 тыс, дальше по 100 тыс.</t>
+    <t xml:space="preserve">Шесть месяцев без разработчика, шесть по 50 тыс, дальше по 100 тыс.</t>
   </si>
   <si>
     <t xml:space="preserve">Взнос на травматизм</t>
@@ -794,7 +794,7 @@
     <t xml:space="preserve">Выплачено разработчику за 24 месяца</t>
   </si>
   <si>
-    <t xml:space="preserve">Девять месяцев по первой ставке и двенадцать по второй.</t>
+    <t xml:space="preserve">Шесть месяцев по первой ставке и двенадцать по второй.</t>
   </si>
   <si>
     <t xml:space="preserve">Взносы, если признают работником</t>
@@ -1408,7 +1408,7 @@
       </c>
       <c r="B6" s="6" t="n">
         <f aca="false">IFERROR(MATCH(TRUE(),INDEX('По месяцам'!$B$47:$Y$47&lt;0,0),0),"не кончаются")</f>
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="C6" s="7"/>
     </row>
@@ -1418,7 +1418,7 @@
       </c>
       <c r="B7" s="9" t="n">
         <f aca="false">MAX(0,-MIN('По месяцам'!B47:Y47))</f>
-        <v>636209.61141676</v>
+        <v>486209.61141676</v>
       </c>
       <c r="C7" s="7" t="s">
         <v>7</v>
@@ -1487,7 +1487,7 @@
       </c>
       <c r="B14" s="14" t="n">
         <f aca="false">SUM('По месяцам'!B38:Y38)</f>
-        <v>4330769.79443315</v>
+        <v>4180769.79443315</v>
       </c>
       <c r="C14" s="7"/>
     </row>
@@ -1507,7 +1507,7 @@
       </c>
       <c r="B16" s="13" t="n">
         <f aca="false">SUM('По месяцам'!B45:Y45)</f>
-        <v>-1720101.73362819</v>
+        <v>-1570101.73362819</v>
       </c>
       <c r="C16" s="7"/>
     </row>
@@ -2338,7 +2338,7 @@
         <v>139</v>
       </c>
       <c r="B43" s="25" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C43" s="7" t="s">
         <v>72</v>
@@ -5591,15 +5591,15 @@
       </c>
       <c r="E36" s="14" t="n">
         <f aca="false">IF(4&lt;=Допущения!$B$43,0,IF(4&lt;=Допущения!$B$45,Допущения!$B$44,Допущения!$B$46))</f>
-        <v>50000</v>
+        <v>0</v>
       </c>
       <c r="F36" s="14" t="n">
         <f aca="false">IF(5&lt;=Допущения!$B$43,0,IF(5&lt;=Допущения!$B$45,Допущения!$B$44,Допущения!$B$46))</f>
-        <v>50000</v>
+        <v>0</v>
       </c>
       <c r="G36" s="14" t="n">
         <f aca="false">IF(6&lt;=Допущения!$B$43,0,IF(6&lt;=Допущения!$B$45,Допущения!$B$44,Допущения!$B$46))</f>
-        <v>50000</v>
+        <v>0</v>
       </c>
       <c r="H36" s="14" t="n">
         <f aca="false">IF(7&lt;=Допущения!$B$43,0,IF(7&lt;=Допущения!$B$45,Допущения!$B$44,Допущения!$B$46))</f>
@@ -5796,15 +5796,15 @@
       </c>
       <c r="E38" s="13" t="n">
         <f aca="false">SUM(E21:E37)</f>
-        <v>154177.955485958</v>
+        <v>104177.955485958</v>
       </c>
       <c r="F38" s="13" t="n">
         <f aca="false">SUM(F21:F37)</f>
-        <v>155161.20511443</v>
+        <v>105161.20511443</v>
       </c>
       <c r="G38" s="13" t="n">
         <f aca="false">SUM(G21:G37)</f>
-        <v>156114.78901353</v>
+        <v>106114.78901353</v>
       </c>
       <c r="H38" s="13" t="n">
         <f aca="false">SUM(H21:H37)</f>
@@ -6368,15 +6368,15 @@
       </c>
       <c r="E45" s="13" t="n">
         <f aca="false">E17-E38-E43</f>
-        <v>-137879.545759417</v>
+        <v>-87879.5457594167</v>
       </c>
       <c r="F45" s="13" t="n">
         <f aca="false">F17-F38-F43</f>
-        <v>-126962.283474987</v>
+        <v>-76962.2834749868</v>
       </c>
       <c r="G45" s="13" t="n">
         <f aca="false">G17-G38-G43</f>
-        <v>-116531.498109455</v>
+        <v>-66531.4981094552</v>
       </c>
       <c r="H45" s="13" t="n">
         <f aca="false">H17-H38-H43</f>
@@ -6469,15 +6469,15 @@
       </c>
       <c r="E46" s="13" t="n">
         <f aca="false">E19-E38-E43</f>
-        <v>-45148.3999260833</v>
+        <v>4851.60007391667</v>
       </c>
       <c r="F46" s="13" t="n">
         <f aca="false">F19-F38-F43</f>
-        <v>-41993.255697209</v>
+        <v>8006.74430279101</v>
       </c>
       <c r="G46" s="13" t="n">
         <f aca="false">G19-G38-G43</f>
-        <v>-39188.2874613071</v>
+        <v>10811.7125386929</v>
       </c>
       <c r="H46" s="13" t="n">
         <f aca="false">H19-H38-H43</f>
@@ -6570,87 +6570,87 @@
       </c>
       <c r="E47" s="13" t="n">
         <f aca="false">D47+E46</f>
-        <v>159278.261073917</v>
+        <v>209278.261073917</v>
       </c>
       <c r="F47" s="13" t="n">
         <f aca="false">E47+F46</f>
-        <v>117285.005376708</v>
+        <v>217285.005376708</v>
       </c>
       <c r="G47" s="13" t="n">
         <f aca="false">F47+G46</f>
-        <v>78096.7179154006</v>
+        <v>228096.717915401</v>
       </c>
       <c r="H47" s="13" t="n">
         <f aca="false">G47+H46</f>
-        <v>41405.1019041787</v>
+        <v>191405.101904179</v>
       </c>
       <c r="I47" s="13" t="n">
         <f aca="false">H47+I46</f>
-        <v>6938.73240661406</v>
+        <v>156938.732406614</v>
       </c>
       <c r="J47" s="13" t="n">
         <f aca="false">I47+J46</f>
-        <v>-24006.7145112504</v>
+        <v>125993.28548875</v>
       </c>
       <c r="K47" s="13" t="n">
         <f aca="false">J47+K46</f>
-        <v>-52276.4342041097</v>
+        <v>97723.5657958903</v>
       </c>
       <c r="L47" s="13" t="n">
         <f aca="false">K47+L46</f>
-        <v>-78131.784625082</v>
+        <v>71868.215374918</v>
       </c>
       <c r="M47" s="13" t="n">
         <f aca="false">L47+M46</f>
-        <v>-100037.694416487</v>
+        <v>49962.3055835133</v>
       </c>
       <c r="N47" s="13" t="n">
         <f aca="false">M47+N46</f>
-        <v>-169064.770246024</v>
+        <v>-19064.7702460236</v>
       </c>
       <c r="O47" s="13" t="n">
         <f aca="false">N47+O46</f>
-        <v>-235466.18485336</v>
+        <v>-85466.1848533596</v>
       </c>
       <c r="P47" s="13" t="n">
         <f aca="false">O47+P46</f>
-        <v>-297469.075766692</v>
+        <v>-147469.075766692</v>
       </c>
       <c r="Q47" s="13" t="n">
         <f aca="false">P47+Q46</f>
-        <v>-356370.849926533</v>
+        <v>-206370.849926533</v>
       </c>
       <c r="R47" s="13" t="n">
         <f aca="false">Q47+R46</f>
-        <v>-410267.038402642</v>
+        <v>-260267.038402642</v>
       </c>
       <c r="S47" s="13" t="n">
         <f aca="false">R47+S46</f>
-        <v>-460630.280688431</v>
+        <v>-310630.280688431</v>
       </c>
       <c r="T47" s="13" t="n">
         <f aca="false">S47+T46</f>
-        <v>-505418.87022532</v>
+        <v>-355418.87022532</v>
       </c>
       <c r="U47" s="13" t="n">
         <f aca="false">T47+U46</f>
-        <v>-543894.062282008</v>
+        <v>-393894.062282008</v>
       </c>
       <c r="V47" s="13" t="n">
         <f aca="false">U47+V46</f>
-        <v>-577818.252942168</v>
+        <v>-427818.252942167</v>
       </c>
       <c r="W47" s="13" t="n">
         <f aca="false">V47+W46</f>
-        <v>-604968.038499674</v>
+        <v>-454968.038499674</v>
       </c>
       <c r="X47" s="13" t="n">
         <f aca="false">W47+X46</f>
-        <v>-624650.749559938</v>
+        <v>-474650.749559937</v>
       </c>
       <c r="Y47" s="13" t="n">
         <f aca="false">X47+Y46</f>
-        <v>-636209.61141676</v>
+        <v>-486209.61141676</v>
       </c>
       <c r="Z47" s="7" t="s">
         <v>241</v>
@@ -6784,8 +6784,8 @@
         <v>255</v>
       </c>
       <c r="B17" s="9" t="n">
-        <f aca="false">(Допущения!$B$44*9+Допущения!$B$46*12)</f>
-        <v>1650000</v>
+        <f aca="false">(Допущения!$B$44*6+Допущения!$B$46*12)</f>
+        <v>1500000</v>
       </c>
       <c r="C17" s="7" t="s">
         <v>256</v>
@@ -6796,8 +6796,8 @@
         <v>257</v>
       </c>
       <c r="B18" s="9" t="n">
-        <f aca="false">(Допущения!$B$44*9+Допущения!$B$46*12)*Допущения!$B$53</f>
-        <v>495000</v>
+        <f aca="false">(Допущения!$B$44*6+Допущения!$B$46*12)*Допущения!$B$53</f>
+        <v>450000</v>
       </c>
       <c r="C18" s="7" t="s">
         <v>258</v>
@@ -6808,8 +6808,8 @@
         <v>259</v>
       </c>
       <c r="B19" s="9" t="n">
-        <f aca="false">(Допущения!$B$44*9+Допущения!$B$46*12)*Допущения!$B$53*0.2</f>
-        <v>99000</v>
+        <f aca="false">(Допущения!$B$44*6+Допущения!$B$46*12)*Допущения!$B$53*0.2</f>
+        <v>90000</v>
       </c>
       <c r="C19" s="7" t="s">
         <v>260</v>
@@ -6820,8 +6820,8 @@
         <v>261</v>
       </c>
       <c r="B20" s="9" t="n">
-        <f aca="false">(Допущения!$B$44*9+Допущения!$B$46*12)*Допущения!$B$53*1.2</f>
-        <v>594000</v>
+        <f aca="false">(Допущения!$B$44*6+Допущения!$B$46*12)*Допущения!$B$53*1.2</f>
+        <v>540000</v>
       </c>
       <c r="C20" s="7" t="s">
         <v>262</v>
